--- a/app/templates/Template,GE_FINO.xlsx
+++ b/app/templates/Template,GE_FINO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\Sistemas-suelos\Sistema-agregado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3557EE1F-83D8-4D76-A39F-1D13806B337C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CEACF1-3468-4FEC-BB44-8DBD06E40C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="723" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="96" r:id="rId1"/>
@@ -876,9 +876,6 @@
     <t>f</t>
   </si>
   <si>
-    <t>2*RAIZ(0.00181+0.0000000000818xR2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calibración </t>
   </si>
   <si>
@@ -1270,6 +1267,9 @@
   </si>
   <si>
     <t>FACTOR DE PRECISION DEL OPERADOR</t>
+  </si>
+  <si>
+    <t>2*RAIZ(0.00181+0.000000000215xR2)</t>
   </si>
 </sst>
 </file>
@@ -3148,14 +3148,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3282,9 +3276,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3816,6 +3807,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -5833,22 +5833,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>17318</xdr:colOff>
+      <xdr:colOff>268432</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>112569</xdr:rowOff>
+      <xdr:rowOff>129887</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>486742</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>71044</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>138546</xdr:rowOff>
+      <xdr:rowOff>62428</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9396F598-8604-5FDE-19B6-95FB07928B5D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32A3207F-36B6-5313-5E23-438A0F97D308}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5864,8 +5864,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17318" y="112569"/>
-          <a:ext cx="5431083" cy="684068"/>
+          <a:off x="268432" y="129887"/>
+          <a:ext cx="6487430" cy="590632"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7920,802 +7920,802 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABE1059-A774-42C5-B9E8-ED8B238CAF69}">
   <dimension ref="A1:M59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="311" customWidth="1"/>
-    <col min="2" max="2" width="5" style="311" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" style="311" customWidth="1"/>
-    <col min="4" max="5" width="24.33203125" style="311" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="311" customWidth="1"/>
-    <col min="7" max="8" width="13.6640625" style="311" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" style="311" customWidth="1"/>
-    <col min="10" max="10" width="6.44140625" style="311" customWidth="1"/>
-    <col min="11" max="16384" width="10.33203125" style="311"/>
+    <col min="1" max="1" width="2.5703125" style="308" customWidth="1"/>
+    <col min="2" max="2" width="5" style="308" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="308" customWidth="1"/>
+    <col min="4" max="5" width="24.28515625" style="308" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="308" customWidth="1"/>
+    <col min="7" max="8" width="13.7109375" style="308" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" style="308" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" style="308" customWidth="1"/>
+    <col min="11" max="16384" width="10.28515625" style="308"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="307"/>
-      <c r="B1" s="308"/>
-      <c r="C1" s="308"/>
-      <c r="D1" s="309"/>
-      <c r="E1" s="309"/>
-      <c r="F1" s="309"/>
-      <c r="G1" s="309"/>
-      <c r="H1" s="309"/>
-      <c r="I1" s="310"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="312"/>
-      <c r="B2" s="313"/>
-      <c r="C2" s="313"/>
-      <c r="D2" s="314"/>
-      <c r="E2" s="314"/>
-      <c r="F2" s="314"/>
-      <c r="G2" s="314"/>
-      <c r="H2" s="314"/>
-      <c r="I2" s="315"/>
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="304"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="305"/>
+      <c r="D1" s="306"/>
+      <c r="E1" s="306"/>
+      <c r="F1" s="306"/>
+      <c r="G1" s="306"/>
+      <c r="H1" s="306"/>
+      <c r="I1" s="307"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="309"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="311"/>
+      <c r="I2" s="312"/>
       <c r="L2" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="369"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="312"/>
-      <c r="B3" s="313"/>
-      <c r="C3" s="313"/>
-      <c r="D3" s="314"/>
-      <c r="E3" s="314"/>
-      <c r="F3" s="314"/>
-      <c r="G3" s="314"/>
-      <c r="H3" s="314"/>
-      <c r="I3" s="315"/>
+      <c r="M2" s="366"/>
+    </row>
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="309"/>
+      <c r="B3" s="310"/>
+      <c r="C3" s="310"/>
+      <c r="D3" s="311"/>
+      <c r="E3" s="311"/>
+      <c r="F3" s="311"/>
+      <c r="G3" s="311"/>
+      <c r="H3" s="311"/>
+      <c r="I3" s="312"/>
       <c r="L3" s="191" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="370"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="312"/>
-      <c r="B4" s="313"/>
-      <c r="C4" s="313"/>
-      <c r="D4" s="314"/>
-      <c r="E4" s="314"/>
-      <c r="F4" s="314"/>
-      <c r="G4" s="314"/>
-      <c r="H4" s="314"/>
-      <c r="I4" s="315"/>
+      <c r="M3" s="367"/>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="309"/>
+      <c r="B4" s="310"/>
+      <c r="C4" s="310"/>
+      <c r="D4" s="311"/>
+      <c r="E4" s="311"/>
+      <c r="F4" s="311"/>
+      <c r="G4" s="311"/>
+      <c r="H4" s="311"/>
+      <c r="I4" s="312"/>
       <c r="L4" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="370"/>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="316"/>
-      <c r="B5" s="317"/>
-      <c r="C5" s="317"/>
-      <c r="D5" s="317"/>
-      <c r="E5" s="317"/>
-      <c r="F5" s="317"/>
-      <c r="G5" s="317"/>
-      <c r="H5" s="317"/>
-      <c r="I5" s="318"/>
+      <c r="M4" s="367"/>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="313"/>
+      <c r="B5" s="314"/>
+      <c r="C5" s="314"/>
+      <c r="D5" s="314"/>
+      <c r="E5" s="314"/>
+      <c r="F5" s="314"/>
+      <c r="G5" s="314"/>
+      <c r="H5" s="314"/>
+      <c r="I5" s="315"/>
       <c r="L5" s="191" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="370"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="319"/>
-      <c r="B6" s="319"/>
-      <c r="C6" s="319"/>
-      <c r="D6" s="319"/>
-      <c r="E6" s="319"/>
-      <c r="F6" s="319"/>
-      <c r="G6" s="319"/>
-      <c r="H6" s="319"/>
-      <c r="I6" s="319"/>
-      <c r="L6" s="371"/>
-      <c r="M6" s="372"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="385" t="s">
+      <c r="M5" s="367"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="316"/>
+      <c r="B6" s="316"/>
+      <c r="C6" s="316"/>
+      <c r="D6" s="316"/>
+      <c r="E6" s="316"/>
+      <c r="F6" s="316"/>
+      <c r="G6" s="316"/>
+      <c r="H6" s="316"/>
+      <c r="I6" s="316"/>
+      <c r="L6" s="368"/>
+      <c r="M6" s="369"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="382" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="385"/>
-      <c r="C7" s="385"/>
-      <c r="D7" s="385"/>
-      <c r="E7" s="385"/>
-      <c r="F7" s="385"/>
-      <c r="G7" s="385"/>
-      <c r="H7" s="385"/>
-      <c r="I7" s="385"/>
+      <c r="B7" s="382"/>
+      <c r="C7" s="382"/>
+      <c r="D7" s="382"/>
+      <c r="E7" s="382"/>
+      <c r="F7" s="382"/>
+      <c r="G7" s="382"/>
+      <c r="H7" s="382"/>
+      <c r="I7" s="382"/>
       <c r="L7" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="M7" s="372"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="386" t="s">
+      <c r="M7" s="369"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="383" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="383"/>
+      <c r="C8" s="383"/>
+      <c r="D8" s="383"/>
+      <c r="E8" s="383"/>
+      <c r="F8" s="383"/>
+      <c r="G8" s="383"/>
+      <c r="H8" s="383"/>
+      <c r="I8" s="383"/>
+      <c r="L8" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="M8" s="370"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="317"/>
+      <c r="B9" s="317"/>
+      <c r="C9" s="317"/>
+      <c r="D9" s="317"/>
+      <c r="E9" s="317"/>
+      <c r="F9" s="317"/>
+      <c r="G9" s="317"/>
+      <c r="H9" s="317"/>
+      <c r="I9" s="317"/>
+      <c r="L9" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="M9" s="369"/>
+    </row>
+    <row r="10" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="318" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="386"/>
-      <c r="C8" s="386"/>
-      <c r="D8" s="386"/>
-      <c r="E8" s="386"/>
-      <c r="F8" s="386"/>
-      <c r="G8" s="386"/>
-      <c r="H8" s="386"/>
-      <c r="I8" s="386"/>
-      <c r="L8" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="M8" s="373"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="320"/>
-      <c r="B9" s="320"/>
-      <c r="C9" s="320"/>
-      <c r="D9" s="320"/>
-      <c r="E9" s="320"/>
-      <c r="F9" s="320"/>
-      <c r="G9" s="320"/>
-      <c r="H9" s="320"/>
-      <c r="I9" s="320"/>
-      <c r="L9" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="M9" s="372"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="321" t="s">
+      <c r="D10" s="318" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="321" t="s">
+      <c r="E10" s="318" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="321" t="s">
+      <c r="F10" s="384" t="s">
         <v>185</v>
       </c>
-      <c r="F10" s="387" t="s">
-        <v>186</v>
-      </c>
-      <c r="G10" s="387"/>
-      <c r="H10" s="322"/>
-      <c r="I10" s="322"/>
-      <c r="J10" s="323"/>
-      <c r="L10" s="371"/>
-      <c r="M10" s="372"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="322"/>
-      <c r="C11" s="364"/>
-      <c r="D11" s="364"/>
-      <c r="E11" s="365"/>
-      <c r="F11" s="366"/>
-      <c r="G11" s="367"/>
-      <c r="H11" s="322"/>
-      <c r="I11" s="322"/>
-      <c r="J11" s="323"/>
+      <c r="G10" s="384"/>
+      <c r="H10" s="319"/>
+      <c r="I10" s="319"/>
+      <c r="J10" s="320"/>
+      <c r="L10" s="368"/>
+      <c r="M10" s="369"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="319"/>
+      <c r="C11" s="361"/>
+      <c r="D11" s="361"/>
+      <c r="E11" s="362"/>
+      <c r="F11" s="363"/>
+      <c r="G11" s="364"/>
+      <c r="H11" s="319"/>
+      <c r="I11" s="319"/>
+      <c r="J11" s="320"/>
       <c r="L11" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="372"/>
-    </row>
-    <row r="12" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="322"/>
-      <c r="B12" s="322"/>
-      <c r="C12" s="324"/>
-      <c r="D12" s="324"/>
-      <c r="E12" s="324"/>
-      <c r="F12" s="324"/>
-      <c r="G12" s="324"/>
-      <c r="H12" s="324"/>
-      <c r="I12" s="324"/>
-      <c r="J12" s="323"/>
+      <c r="M11" s="369"/>
+    </row>
+    <row r="12" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="319"/>
+      <c r="B12" s="319"/>
+      <c r="C12" s="321"/>
+      <c r="D12" s="321"/>
+      <c r="E12" s="321"/>
+      <c r="F12" s="321"/>
+      <c r="G12" s="321"/>
+      <c r="H12" s="321"/>
+      <c r="I12" s="321"/>
+      <c r="J12" s="320"/>
       <c r="L12" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="373"/>
-    </row>
-    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="388" t="s">
+      <c r="M12" s="370"/>
+    </row>
+    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="385" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="389"/>
-      <c r="C13" s="389"/>
-      <c r="D13" s="389"/>
-      <c r="E13" s="389"/>
-      <c r="F13" s="389"/>
-      <c r="G13" s="389"/>
-      <c r="H13" s="389"/>
-      <c r="I13" s="390"/>
-      <c r="J13" s="323"/>
+      <c r="B13" s="386"/>
+      <c r="C13" s="386"/>
+      <c r="D13" s="386"/>
+      <c r="E13" s="386"/>
+      <c r="F13" s="386"/>
+      <c r="G13" s="386"/>
+      <c r="H13" s="386"/>
+      <c r="I13" s="387"/>
+      <c r="J13" s="320"/>
       <c r="L13" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="373"/>
-    </row>
-    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="391" t="s">
-        <v>180</v>
-      </c>
-      <c r="B14" s="392"/>
-      <c r="C14" s="392"/>
-      <c r="D14" s="392"/>
-      <c r="E14" s="392"/>
-      <c r="F14" s="392"/>
-      <c r="G14" s="392"/>
-      <c r="H14" s="392"/>
-      <c r="I14" s="393"/>
-      <c r="J14" s="323"/>
-      <c r="L14" s="371"/>
-      <c r="M14" s="372"/>
-    </row>
-    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="325"/>
-      <c r="B15" s="326" t="s">
-        <v>187</v>
-      </c>
-      <c r="C15" s="327"/>
-      <c r="D15" s="327"/>
-      <c r="E15" s="327"/>
-      <c r="F15" s="327"/>
-      <c r="G15" s="327"/>
-      <c r="H15" s="327"/>
-      <c r="I15" s="328"/>
-      <c r="J15" s="323"/>
+      <c r="M13" s="370"/>
+    </row>
+    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="388" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="389"/>
+      <c r="C14" s="389"/>
+      <c r="D14" s="389"/>
+      <c r="E14" s="389"/>
+      <c r="F14" s="389"/>
+      <c r="G14" s="389"/>
+      <c r="H14" s="389"/>
+      <c r="I14" s="390"/>
+      <c r="J14" s="320"/>
+      <c r="L14" s="368"/>
+      <c r="M14" s="369"/>
+    </row>
+    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="322"/>
+      <c r="B15" s="323" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" s="324"/>
+      <c r="D15" s="324"/>
+      <c r="E15" s="324"/>
+      <c r="F15" s="324"/>
+      <c r="G15" s="324"/>
+      <c r="H15" s="324"/>
+      <c r="I15" s="325"/>
+      <c r="J15" s="320"/>
       <c r="L15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="374"/>
-    </row>
-    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="329"/>
-      <c r="B16" s="330" t="s">
+      <c r="M15" s="371"/>
+    </row>
+    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="326"/>
+      <c r="B16" s="327" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="328"/>
+      <c r="D16" s="329"/>
+      <c r="E16" s="327" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="331"/>
-      <c r="D16" s="332"/>
-      <c r="E16" s="330" t="s">
-        <v>189</v>
-      </c>
-      <c r="F16" s="331"/>
-      <c r="G16" s="394"/>
-      <c r="H16" s="395"/>
-      <c r="I16" s="333"/>
-      <c r="J16" s="323"/>
+      <c r="F16" s="328"/>
+      <c r="G16" s="391"/>
+      <c r="H16" s="392"/>
+      <c r="I16" s="330"/>
+      <c r="J16" s="320"/>
       <c r="L16" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="M16" s="374"/>
-    </row>
-    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="329"/>
-      <c r="B17" s="330" t="s">
+      <c r="M16" s="371"/>
+    </row>
+    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="326"/>
+      <c r="B17" s="327" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="328"/>
+      <c r="D17" s="329"/>
+      <c r="E17" s="327" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="331"/>
-      <c r="D17" s="332"/>
-      <c r="E17" s="330" t="s">
+      <c r="G17" s="391"/>
+      <c r="H17" s="392"/>
+      <c r="I17" s="330"/>
+      <c r="J17" s="320"/>
+      <c r="L17" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="M17" s="372"/>
+    </row>
+    <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="331"/>
+      <c r="B18" s="327" t="s">
         <v>191</v>
       </c>
-      <c r="G17" s="394"/>
-      <c r="H17" s="395"/>
-      <c r="I17" s="333"/>
-      <c r="J17" s="323"/>
-      <c r="L17" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="M17" s="375"/>
-    </row>
-    <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="334"/>
-      <c r="B18" s="330" t="s">
+      <c r="C18" s="327"/>
+      <c r="D18" s="334"/>
+      <c r="E18" s="327" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="330"/>
-      <c r="D18" s="337"/>
-      <c r="E18" s="330" t="s">
+      <c r="F18" s="328"/>
+      <c r="G18" s="391"/>
+      <c r="H18" s="392"/>
+      <c r="I18" s="332"/>
+      <c r="J18" s="320"/>
+    </row>
+    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="331"/>
+      <c r="B19" s="327"/>
+      <c r="C19" s="327"/>
+      <c r="D19" s="327"/>
+      <c r="E19" s="327" t="s">
         <v>193</v>
       </c>
-      <c r="F18" s="331"/>
-      <c r="G18" s="394"/>
-      <c r="H18" s="395"/>
-      <c r="I18" s="335"/>
-      <c r="J18" s="323"/>
-    </row>
-    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="334"/>
-      <c r="B19" s="330"/>
-      <c r="C19" s="330"/>
-      <c r="D19" s="330"/>
-      <c r="E19" s="330" t="s">
+      <c r="F19" s="327"/>
+      <c r="G19" s="391"/>
+      <c r="H19" s="392"/>
+      <c r="I19" s="332"/>
+      <c r="J19" s="320"/>
+    </row>
+    <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="331"/>
+      <c r="B20" s="333" t="s">
         <v>194</v>
       </c>
-      <c r="F19" s="330"/>
-      <c r="G19" s="394"/>
-      <c r="H19" s="395"/>
-      <c r="I19" s="335"/>
-      <c r="J19" s="323"/>
-    </row>
-    <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="334"/>
-      <c r="B20" s="336" t="s">
+      <c r="C20" s="327"/>
+      <c r="D20" s="327"/>
+      <c r="E20" s="327"/>
+      <c r="F20" s="327"/>
+      <c r="G20" s="327"/>
+      <c r="H20" s="327"/>
+      <c r="I20" s="332"/>
+      <c r="J20" s="320"/>
+    </row>
+    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="331"/>
+      <c r="B21" s="333" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="330"/>
-      <c r="D20" s="330"/>
-      <c r="E20" s="330"/>
-      <c r="F20" s="330"/>
-      <c r="G20" s="330"/>
-      <c r="H20" s="330"/>
-      <c r="I20" s="335"/>
-      <c r="J20" s="323"/>
-    </row>
-    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="334"/>
-      <c r="B21" s="336" t="s">
+      <c r="C21" s="327"/>
+      <c r="D21" s="327"/>
+      <c r="E21" s="327"/>
+      <c r="F21" s="327"/>
+      <c r="G21" s="327"/>
+      <c r="H21" s="327"/>
+      <c r="I21" s="332"/>
+      <c r="J21" s="320"/>
+    </row>
+    <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="331"/>
+      <c r="B22" s="393" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="393"/>
+      <c r="D22" s="393"/>
+      <c r="E22" s="394"/>
+      <c r="F22" s="334" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="393" t="s">
         <v>196</v>
       </c>
-      <c r="C21" s="330"/>
-      <c r="D21" s="330"/>
-      <c r="E21" s="330"/>
-      <c r="F21" s="330"/>
-      <c r="G21" s="330"/>
-      <c r="H21" s="330"/>
-      <c r="I21" s="335"/>
-      <c r="J21" s="323"/>
-    </row>
-    <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="334"/>
-      <c r="B22" s="396" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="396"/>
-      <c r="D22" s="396"/>
-      <c r="E22" s="397"/>
-      <c r="F22" s="337" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="396" t="s">
+      <c r="H22" s="393"/>
+      <c r="I22" s="332"/>
+      <c r="J22" s="320"/>
+    </row>
+    <row r="23" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="331"/>
+      <c r="B23" s="283" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="284" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="335"/>
+      <c r="E23" s="336"/>
+      <c r="F23" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="285"/>
+      <c r="H23" s="336"/>
+      <c r="I23" s="332"/>
+      <c r="J23" s="320"/>
+    </row>
+    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="331"/>
+      <c r="B24" s="283" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="285" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="335"/>
+      <c r="E24" s="336"/>
+      <c r="F24" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="285"/>
+      <c r="H24" s="336"/>
+      <c r="I24" s="337"/>
+      <c r="J24" s="320"/>
+    </row>
+    <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="331"/>
+      <c r="B25" s="283" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="284" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="335"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="285"/>
+      <c r="H25" s="336"/>
+      <c r="I25" s="337"/>
+      <c r="J25" s="320"/>
+    </row>
+    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="331"/>
+      <c r="B26" s="283" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="284" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" s="335"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="285"/>
+      <c r="H26" s="336"/>
+      <c r="I26" s="337"/>
+      <c r="J26" s="320"/>
+    </row>
+    <row r="27" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="331"/>
+      <c r="B27" s="283" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="284" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="335"/>
+      <c r="E27" s="336"/>
+      <c r="F27" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="285"/>
+      <c r="H27" s="336"/>
+      <c r="I27" s="337"/>
+      <c r="J27" s="338"/>
+    </row>
+    <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="331"/>
+      <c r="B28" s="283" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="284" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="335"/>
+      <c r="E28" s="336"/>
+      <c r="F28" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="285"/>
+      <c r="H28" s="336"/>
+      <c r="I28" s="337"/>
+      <c r="J28" s="320"/>
+    </row>
+    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="331"/>
+      <c r="B29" s="283" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="284" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="335"/>
+      <c r="E29" s="336"/>
+      <c r="F29" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="285"/>
+      <c r="H29" s="336"/>
+      <c r="I29" s="337"/>
+      <c r="J29" s="320"/>
+    </row>
+    <row r="30" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="331"/>
+      <c r="B30" s="283" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="284" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="335"/>
+      <c r="E30" s="336"/>
+      <c r="F30" s="286" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="285"/>
+      <c r="H30" s="336"/>
+      <c r="I30" s="337"/>
+      <c r="J30" s="320"/>
+    </row>
+    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="331"/>
+      <c r="B31" s="283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="284" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="286" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="285"/>
+      <c r="H31" s="336"/>
+      <c r="I31" s="337"/>
+      <c r="J31" s="320"/>
+    </row>
+    <row r="32" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="331"/>
+      <c r="B32" s="283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="284" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" s="335"/>
+      <c r="E32" s="336"/>
+      <c r="F32" s="286" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="285"/>
+      <c r="H32" s="336"/>
+      <c r="I32" s="337"/>
+      <c r="J32" s="320"/>
+    </row>
+    <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="331"/>
+      <c r="B33" s="283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="284" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" s="335"/>
+      <c r="E33" s="336"/>
+      <c r="F33" s="286" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="285"/>
+      <c r="H33" s="336"/>
+      <c r="I33" s="337"/>
+      <c r="J33" s="320"/>
+    </row>
+    <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="339"/>
+      <c r="B34" s="283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="284" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" s="340"/>
+      <c r="E34" s="341"/>
+      <c r="F34" s="286" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="285"/>
+      <c r="H34" s="336"/>
+      <c r="I34" s="339"/>
+      <c r="J34" s="320"/>
+    </row>
+    <row r="35" spans="1:10" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="342"/>
+      <c r="B35" s="343"/>
+      <c r="C35" s="344"/>
+      <c r="D35" s="340"/>
+      <c r="E35" s="340"/>
+      <c r="F35" s="345"/>
+      <c r="G35" s="335"/>
+      <c r="H35" s="335"/>
+      <c r="I35" s="346"/>
+      <c r="J35" s="320"/>
+    </row>
+    <row r="36" spans="1:10" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="347"/>
+      <c r="B36" s="347"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
+      <c r="G36" s="348"/>
+      <c r="H36" s="348"/>
+      <c r="I36" s="348"/>
+      <c r="J36" s="320"/>
+    </row>
+    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="349" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="350"/>
+      <c r="G37" s="351"/>
+      <c r="J37" s="320"/>
+    </row>
+    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="352" t="s">
         <v>197</v>
       </c>
-      <c r="H22" s="396"/>
-      <c r="I22" s="335"/>
-      <c r="J22" s="323"/>
-    </row>
-    <row r="23" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="334"/>
-      <c r="B23" s="285" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="286" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="338"/>
-      <c r="E23" s="339"/>
-      <c r="F23" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="287"/>
-      <c r="H23" s="339"/>
-      <c r="I23" s="335"/>
-      <c r="J23" s="323"/>
-    </row>
-    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="334"/>
-      <c r="B24" s="285" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="287" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="338"/>
-      <c r="E24" s="339"/>
-      <c r="F24" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="287"/>
-      <c r="H24" s="339"/>
-      <c r="I24" s="340"/>
-      <c r="J24" s="323"/>
-    </row>
-    <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="334"/>
-      <c r="B25" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="286" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="338"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="287"/>
-      <c r="H25" s="339"/>
-      <c r="I25" s="340"/>
-      <c r="J25" s="323"/>
-    </row>
-    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="334"/>
-      <c r="B26" s="285" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="286" t="s">
-        <v>161</v>
-      </c>
-      <c r="D26" s="338"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="287"/>
-      <c r="H26" s="339"/>
-      <c r="I26" s="340"/>
-      <c r="J26" s="323"/>
-    </row>
-    <row r="27" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="334"/>
-      <c r="B27" s="285" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" s="286" t="s">
-        <v>162</v>
-      </c>
-      <c r="D27" s="338"/>
-      <c r="E27" s="339"/>
-      <c r="F27" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="287"/>
-      <c r="H27" s="339"/>
-      <c r="I27" s="340"/>
-      <c r="J27" s="341"/>
-    </row>
-    <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="334"/>
-      <c r="B28" s="285" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28" s="286" t="s">
-        <v>163</v>
-      </c>
-      <c r="D28" s="338"/>
-      <c r="E28" s="339"/>
-      <c r="F28" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="287"/>
-      <c r="H28" s="339"/>
-      <c r="I28" s="340"/>
-      <c r="J28" s="323"/>
-    </row>
-    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="334"/>
-      <c r="B29" s="285" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="286" t="s">
-        <v>164</v>
-      </c>
-      <c r="D29" s="338"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="287"/>
-      <c r="H29" s="339"/>
-      <c r="I29" s="340"/>
-      <c r="J29" s="323"/>
-    </row>
-    <row r="30" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="334"/>
-      <c r="B30" s="285" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="286" t="s">
-        <v>170</v>
-      </c>
-      <c r="D30" s="338"/>
-      <c r="E30" s="339"/>
-      <c r="F30" s="288" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="287"/>
-      <c r="H30" s="339"/>
-      <c r="I30" s="340"/>
-      <c r="J30" s="323"/>
-    </row>
-    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="334"/>
-      <c r="B31" s="285" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="286" t="s">
-        <v>171</v>
-      </c>
-      <c r="D31" s="338"/>
-      <c r="E31" s="339"/>
-      <c r="F31" s="288" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="287"/>
-      <c r="H31" s="339"/>
-      <c r="I31" s="340"/>
-      <c r="J31" s="323"/>
-    </row>
-    <row r="32" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="334"/>
-      <c r="B32" s="285" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="286" t="s">
-        <v>172</v>
-      </c>
-      <c r="D32" s="338"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="288" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="287"/>
-      <c r="H32" s="339"/>
-      <c r="I32" s="340"/>
-      <c r="J32" s="323"/>
-    </row>
-    <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="334"/>
-      <c r="B33" s="285" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="286" t="s">
-        <v>173</v>
-      </c>
-      <c r="D33" s="338"/>
-      <c r="E33" s="339"/>
-      <c r="F33" s="288" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="287"/>
-      <c r="H33" s="339"/>
-      <c r="I33" s="340"/>
-      <c r="J33" s="323"/>
-    </row>
-    <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="342"/>
-      <c r="B34" s="285" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="286" t="s">
-        <v>174</v>
-      </c>
-      <c r="D34" s="343"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="288" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" s="287"/>
-      <c r="H34" s="339"/>
-      <c r="I34" s="342"/>
-      <c r="J34" s="323"/>
-    </row>
-    <row r="35" spans="1:10" ht="6.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="345"/>
-      <c r="B35" s="346"/>
-      <c r="C35" s="347"/>
-      <c r="D35" s="343"/>
-      <c r="E35" s="343"/>
-      <c r="F35" s="348"/>
-      <c r="G35" s="338"/>
-      <c r="H35" s="338"/>
-      <c r="I35" s="349"/>
-      <c r="J35" s="323"/>
-    </row>
-    <row r="36" spans="1:10" ht="6.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="350"/>
-      <c r="B36" s="350"/>
-      <c r="C36" s="351"/>
-      <c r="D36" s="351"/>
-      <c r="E36" s="351"/>
-      <c r="F36" s="351"/>
-      <c r="G36" s="351"/>
-      <c r="H36" s="351"/>
-      <c r="I36" s="351"/>
-      <c r="J36" s="323"/>
-    </row>
-    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="352" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" s="353"/>
-      <c r="G37" s="354"/>
-      <c r="J37" s="323"/>
-    </row>
-    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="355" t="s">
+      <c r="B38" s="87"/>
+      <c r="G38" s="353"/>
+      <c r="J38" s="320"/>
+    </row>
+    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="350"/>
+      <c r="B39" s="350"/>
+      <c r="J39" s="320"/>
+    </row>
+    <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="354" t="s">
         <v>198</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="G38" s="356"/>
-      <c r="J38" s="323"/>
-    </row>
-    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="353"/>
-      <c r="B39" s="353"/>
-      <c r="J39" s="323"/>
-    </row>
-    <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="357" t="s">
+      <c r="E40" s="380" t="s">
         <v>199</v>
       </c>
-      <c r="E40" s="383" t="s">
+      <c r="F40" s="381"/>
+      <c r="J40" s="320"/>
+    </row>
+    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="355" t="s">
         <v>200</v>
       </c>
-      <c r="F40" s="384"/>
-      <c r="J40" s="323"/>
-    </row>
-    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="358" t="s">
+      <c r="E41" s="397"/>
+      <c r="F41" s="398"/>
+      <c r="J41" s="320"/>
+    </row>
+    <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D42" s="355" t="s">
         <v>201</v>
       </c>
-      <c r="E41" s="400"/>
-      <c r="F41" s="401"/>
-      <c r="J41" s="323"/>
-    </row>
-    <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="358" t="s">
+      <c r="E42" s="397"/>
+      <c r="F42" s="398"/>
+      <c r="J42" s="320"/>
+    </row>
+    <row r="43" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D43" s="355" t="s">
         <v>202</v>
       </c>
-      <c r="E42" s="400"/>
-      <c r="F42" s="401"/>
-      <c r="J42" s="323"/>
-    </row>
-    <row r="43" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="358" t="s">
+      <c r="E43" s="397"/>
+      <c r="F43" s="398"/>
+      <c r="J43" s="320"/>
+    </row>
+    <row r="44" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D44" s="355" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="397"/>
+      <c r="F44" s="398"/>
+      <c r="J44" s="320"/>
+    </row>
+    <row r="45" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D45" s="355" t="s">
         <v>203</v>
       </c>
-      <c r="E43" s="400"/>
-      <c r="F43" s="401"/>
-      <c r="J43" s="323"/>
-    </row>
-    <row r="44" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="358" t="s">
-        <v>73</v>
-      </c>
-      <c r="E44" s="400"/>
-      <c r="F44" s="401"/>
-      <c r="J44" s="323"/>
-    </row>
-    <row r="45" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="358" t="s">
+      <c r="E45" s="397"/>
+      <c r="F45" s="398"/>
+      <c r="J45" s="320"/>
+    </row>
+    <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D46" s="355" t="s">
         <v>204</v>
       </c>
-      <c r="E45" s="400"/>
-      <c r="F45" s="401"/>
-      <c r="J45" s="323"/>
-    </row>
-    <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D46" s="358" t="s">
+      <c r="E46" s="397"/>
+      <c r="F46" s="398"/>
+      <c r="J46" s="320"/>
+    </row>
+    <row r="47" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="356"/>
+      <c r="B47" s="356"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
+      <c r="J47" s="320"/>
+    </row>
+    <row r="48" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="357" t="s">
         <v>205</v>
       </c>
-      <c r="E46" s="400"/>
-      <c r="F46" s="401"/>
-      <c r="J46" s="323"/>
-    </row>
-    <row r="47" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="359"/>
-      <c r="B47" s="359"/>
-      <c r="C47" s="353"/>
-      <c r="D47" s="353"/>
-      <c r="E47" s="353"/>
-      <c r="F47" s="353"/>
-      <c r="J47" s="323"/>
-    </row>
-    <row r="48" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="360" t="s">
+      <c r="B48" s="356"/>
+      <c r="C48" s="350"/>
+      <c r="D48" s="350"/>
+      <c r="E48" s="350"/>
+      <c r="F48" s="350"/>
+      <c r="G48" s="356"/>
+      <c r="H48" s="356"/>
+      <c r="I48" s="358"/>
+      <c r="J48" s="320"/>
+    </row>
+    <row r="49" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="356"/>
+      <c r="B49" s="356"/>
+      <c r="C49" s="350"/>
+      <c r="D49" s="350"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
+      <c r="G49" s="350"/>
+      <c r="H49" s="350"/>
+      <c r="I49" s="350"/>
+      <c r="J49" s="320"/>
+    </row>
+    <row r="50" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="356"/>
+      <c r="B50" s="356"/>
+      <c r="J50" s="320"/>
+    </row>
+    <row r="51" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="356"/>
+      <c r="B51" s="356"/>
+      <c r="J51" s="320"/>
+    </row>
+    <row r="52" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="356"/>
+      <c r="B52" s="356"/>
+      <c r="C52" s="350"/>
+      <c r="D52" s="350"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="350"/>
+      <c r="G52" s="350"/>
+      <c r="H52" s="350"/>
+      <c r="I52" s="350"/>
+      <c r="J52" s="320"/>
+    </row>
+    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="399"/>
+      <c r="D53" s="399"/>
+      <c r="E53" s="399"/>
+      <c r="F53" s="399"/>
+      <c r="G53" s="399"/>
+      <c r="H53" s="359"/>
+      <c r="I53" s="359"/>
+      <c r="J53" s="320"/>
+    </row>
+    <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="360" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="360"/>
+      <c r="C54" s="350"/>
+      <c r="D54" s="350"/>
+      <c r="E54" s="350"/>
+      <c r="F54" s="350"/>
+      <c r="G54" s="350"/>
+      <c r="H54" s="350"/>
+      <c r="I54" s="350"/>
+      <c r="J54" s="320"/>
+    </row>
+    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="360" t="s">
         <v>206</v>
       </c>
-      <c r="B48" s="359"/>
-      <c r="C48" s="353"/>
-      <c r="D48" s="353"/>
-      <c r="E48" s="353"/>
-      <c r="F48" s="353"/>
-      <c r="G48" s="359"/>
-      <c r="H48" s="359"/>
-      <c r="I48" s="361"/>
-      <c r="J48" s="323"/>
-    </row>
-    <row r="49" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="359"/>
-      <c r="B49" s="359"/>
-      <c r="C49" s="353"/>
-      <c r="D49" s="353"/>
-      <c r="E49" s="353"/>
-      <c r="F49" s="353"/>
-      <c r="G49" s="353"/>
-      <c r="H49" s="353"/>
-      <c r="I49" s="353"/>
-      <c r="J49" s="323"/>
-    </row>
-    <row r="50" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="359"/>
-      <c r="B50" s="359"/>
-      <c r="J50" s="323"/>
-    </row>
-    <row r="51" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="359"/>
-      <c r="B51" s="359"/>
-      <c r="J51" s="323"/>
-    </row>
-    <row r="52" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="359"/>
-      <c r="B52" s="359"/>
-      <c r="C52" s="353"/>
-      <c r="D52" s="353"/>
-      <c r="E52" s="353"/>
-      <c r="F52" s="353"/>
-      <c r="G52" s="353"/>
-      <c r="H52" s="353"/>
-      <c r="I52" s="353"/>
-      <c r="J52" s="323"/>
-    </row>
-    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="402"/>
-      <c r="D53" s="402"/>
-      <c r="E53" s="402"/>
-      <c r="F53" s="402"/>
-      <c r="G53" s="402"/>
-      <c r="H53" s="362"/>
-      <c r="I53" s="362"/>
-      <c r="J53" s="323"/>
-    </row>
-    <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="363" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="363"/>
-      <c r="C54" s="353"/>
-      <c r="D54" s="353"/>
-      <c r="E54" s="353"/>
-      <c r="F54" s="353"/>
-      <c r="G54" s="353"/>
-      <c r="H54" s="353"/>
-      <c r="I54" s="353"/>
-      <c r="J54" s="323"/>
-    </row>
-    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="363" t="s">
+      <c r="B55" s="360"/>
+      <c r="C55" s="350"/>
+      <c r="D55" s="395" t="s">
         <v>207</v>
       </c>
-      <c r="B55" s="363"/>
-      <c r="C55" s="353"/>
-      <c r="D55" s="398" t="s">
+      <c r="E55" s="395"/>
+      <c r="F55" s="395"/>
+      <c r="G55" s="395"/>
+      <c r="H55" s="395"/>
+      <c r="I55" s="395"/>
+      <c r="J55" s="320"/>
+    </row>
+    <row r="56" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="396" t="s">
         <v>208</v>
       </c>
-      <c r="E55" s="398"/>
-      <c r="F55" s="398"/>
-      <c r="G55" s="398"/>
-      <c r="H55" s="398"/>
-      <c r="I55" s="398"/>
-      <c r="J55" s="323"/>
-    </row>
-    <row r="56" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="399" t="s">
-        <v>209</v>
-      </c>
-      <c r="B57" s="399"/>
-      <c r="C57" s="399"/>
-      <c r="D57" s="399"/>
-      <c r="E57" s="399"/>
-      <c r="F57" s="399"/>
-      <c r="G57" s="399"/>
-      <c r="H57" s="399"/>
-      <c r="I57" s="399"/>
-    </row>
-    <row r="58" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B57" s="396"/>
+      <c r="C57" s="396"/>
+      <c r="D57" s="396"/>
+      <c r="E57" s="396"/>
+      <c r="F57" s="396"/>
+      <c r="G57" s="396"/>
+      <c r="H57" s="396"/>
+      <c r="I57" s="396"/>
+    </row>
+    <row r="58" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <protectedRanges>
@@ -8758,24 +8758,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:O50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" style="27" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="27" customWidth="1"/>
     <col min="2" max="2" width="2" style="27" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="1.109375" style="27" customWidth="1"/>
-    <col min="5" max="6" width="10.6640625" style="27" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" style="27" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" style="27" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" style="27" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="27" customWidth="1"/>
-    <col min="11" max="11" width="1.5546875" style="27" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="27" customWidth="1"/>
-    <col min="13" max="13" width="6.44140625" style="27" customWidth="1"/>
-    <col min="14" max="16384" width="10.33203125" style="27"/>
+    <col min="3" max="3" width="4.28515625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="1.140625" style="27" customWidth="1"/>
+    <col min="5" max="6" width="10.7109375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="27" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="27" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" style="27" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="27" customWidth="1"/>
+    <col min="11" max="11" width="1.5703125" style="27" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="27" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" style="27" customWidth="1"/>
+    <col min="14" max="16384" width="10.28515625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="25"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -8786,7 +8786,7 @@
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="37"/>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -8800,7 +8800,7 @@
       <c r="K2" s="39"/>
       <c r="L2" s="39"/>
     </row>
-    <row r="3" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="40"/>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -8814,56 +8814,56 @@
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
     </row>
-    <row r="4" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="411" t="s">
+    <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="411"/>
-      <c r="C4" s="411"/>
-      <c r="D4" s="411"/>
-      <c r="E4" s="411"/>
-      <c r="F4" s="411"/>
-      <c r="G4" s="411"/>
-      <c r="H4" s="411"/>
-      <c r="I4" s="411"/>
-      <c r="J4" s="411"/>
-      <c r="K4" s="411"/>
-      <c r="L4" s="411"/>
-    </row>
-    <row r="5" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="418">
+      <c r="B4" s="408"/>
+      <c r="C4" s="408"/>
+      <c r="D4" s="408"/>
+      <c r="E4" s="408"/>
+      <c r="F4" s="408"/>
+      <c r="G4" s="408"/>
+      <c r="H4" s="408"/>
+      <c r="I4" s="408"/>
+      <c r="J4" s="408"/>
+      <c r="K4" s="408"/>
+      <c r="L4" s="408"/>
+    </row>
+    <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="415">
         <v>0</v>
       </c>
-      <c r="B5" s="418"/>
-      <c r="C5" s="418"/>
-      <c r="D5" s="418"/>
-      <c r="E5" s="418"/>
-      <c r="F5" s="418"/>
-      <c r="G5" s="418"/>
-      <c r="H5" s="418"/>
-      <c r="I5" s="418"/>
-      <c r="J5" s="418"/>
-      <c r="K5" s="418"/>
-      <c r="L5" s="418"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="415"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="415"/>
+      <c r="E5" s="415"/>
+      <c r="F5" s="415"/>
+      <c r="G5" s="415"/>
+      <c r="H5" s="415"/>
+      <c r="I5" s="415"/>
+      <c r="J5" s="415"/>
+      <c r="K5" s="415"/>
+      <c r="L5" s="415"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="191" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="419">
+      <c r="C7" s="416">
         <f>+FORMATO!M2</f>
         <v>0</v>
       </c>
-      <c r="D7" s="419"/>
-      <c r="E7" s="419"/>
-      <c r="F7" s="419"/>
-      <c r="G7" s="419"/>
-      <c r="H7" s="419"/>
-      <c r="I7" s="419"/>
+      <c r="D7" s="416"/>
+      <c r="E7" s="416"/>
+      <c r="F7" s="416"/>
+      <c r="G7" s="416"/>
+      <c r="H7" s="416"/>
+      <c r="I7" s="416"/>
       <c r="J7" s="43" t="s">
         <v>3</v>
       </c>
@@ -8874,87 +8874,87 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="191" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="419">
+      <c r="C8" s="416">
         <f>+FORMATO!M3</f>
         <v>0</v>
       </c>
-      <c r="D8" s="419"/>
-      <c r="E8" s="419"/>
-      <c r="F8" s="419"/>
-      <c r="G8" s="419"/>
-      <c r="H8" s="419"/>
-      <c r="I8" s="419"/>
+      <c r="D8" s="416"/>
+      <c r="E8" s="416"/>
+      <c r="F8" s="416"/>
+      <c r="G8" s="416"/>
+      <c r="H8" s="416"/>
+      <c r="I8" s="416"/>
       <c r="J8" s="43" t="s">
         <v>159</v>
       </c>
       <c r="K8" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="305">
+      <c r="L8" s="302">
         <f>+FORMATO!M7</f>
         <v>0</v>
       </c>
       <c r="M8" s="28"/>
     </row>
-    <row r="9" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="191" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="419">
+      <c r="C9" s="416">
         <f>+FORMATO!M4</f>
         <v>0</v>
       </c>
-      <c r="D9" s="419"/>
-      <c r="E9" s="419"/>
-      <c r="F9" s="419"/>
-      <c r="G9" s="419"/>
-      <c r="H9" s="419"/>
-      <c r="I9" s="419"/>
-      <c r="J9" s="382" t="s">
+      <c r="D9" s="416"/>
+      <c r="E9" s="416"/>
+      <c r="F9" s="416"/>
+      <c r="G9" s="416"/>
+      <c r="H9" s="416"/>
+      <c r="I9" s="416"/>
+      <c r="J9" s="379" t="s">
         <v>7</v>
       </c>
       <c r="K9" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="293">
+      <c r="L9" s="291">
         <f>+FORMATO!M8</f>
         <v>0</v>
       </c>
       <c r="M9" s="28"/>
     </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="191" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="419">
+      <c r="C10" s="416">
         <f>+FORMATO!M5</f>
         <v>0</v>
       </c>
-      <c r="D10" s="419"/>
-      <c r="E10" s="419"/>
-      <c r="F10" s="419"/>
-      <c r="G10" s="419"/>
-      <c r="H10" s="419"/>
-      <c r="I10" s="419"/>
+      <c r="D10" s="416"/>
+      <c r="E10" s="416"/>
+      <c r="F10" s="416"/>
+      <c r="G10" s="416"/>
+      <c r="H10" s="416"/>
+      <c r="I10" s="416"/>
       <c r="J10" s="43"/>
       <c r="K10" s="41"/>
       <c r="L10" s="29"/>
       <c r="M10" s="28"/>
     </row>
-    <row r="11" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="178" t="s">
         <v>9</v>
       </c>
@@ -8971,7 +8971,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="28"/>
     </row>
-    <row r="12" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="178"/>
       <c r="B12" s="75"/>
       <c r="C12" s="75"/>
@@ -8986,41 +8986,41 @@
       <c r="L12" s="30"/>
       <c r="M12" s="28"/>
     </row>
-    <row r="13" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="412" t="s">
+    <row r="13" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="409" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="413"/>
-      <c r="C13" s="413"/>
-      <c r="D13" s="413"/>
-      <c r="E13" s="413"/>
-      <c r="F13" s="413"/>
-      <c r="G13" s="413"/>
-      <c r="H13" s="413"/>
-      <c r="I13" s="413"/>
-      <c r="J13" s="413"/>
-      <c r="K13" s="413"/>
-      <c r="L13" s="414"/>
+      <c r="B13" s="410"/>
+      <c r="C13" s="410"/>
+      <c r="D13" s="410"/>
+      <c r="E13" s="410"/>
+      <c r="F13" s="410"/>
+      <c r="G13" s="410"/>
+      <c r="H13" s="410"/>
+      <c r="I13" s="410"/>
+      <c r="J13" s="410"/>
+      <c r="K13" s="410"/>
+      <c r="L13" s="411"/>
       <c r="M13" s="28"/>
     </row>
-    <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="415" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" s="416"/>
-      <c r="C14" s="416"/>
-      <c r="D14" s="416"/>
-      <c r="E14" s="416"/>
-      <c r="F14" s="416"/>
-      <c r="G14" s="416"/>
-      <c r="H14" s="416"/>
-      <c r="I14" s="416"/>
-      <c r="J14" s="416"/>
-      <c r="K14" s="416"/>
-      <c r="L14" s="417"/>
+    <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="412" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="413"/>
+      <c r="C14" s="413"/>
+      <c r="D14" s="413"/>
+      <c r="E14" s="413"/>
+      <c r="F14" s="413"/>
+      <c r="G14" s="413"/>
+      <c r="H14" s="413"/>
+      <c r="I14" s="413"/>
+      <c r="J14" s="413"/>
+      <c r="K14" s="413"/>
+      <c r="L14" s="414"/>
       <c r="M14" s="28"/>
     </row>
-    <row r="15" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="46"/>
       <c r="B15" s="47"/>
       <c r="C15" s="47"/>
@@ -9035,112 +9035,112 @@
       <c r="L15" s="51"/>
       <c r="M15" s="28"/>
     </row>
-    <row r="16" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="294"/>
-      <c r="C16" s="294"/>
-      <c r="D16" s="294"/>
-      <c r="E16" s="295"/>
-      <c r="F16" s="295"/>
-      <c r="G16" s="295"/>
-      <c r="H16" s="295"/>
-      <c r="I16" s="295"/>
-      <c r="J16" s="296"/>
-      <c r="K16" s="297"/>
+      <c r="B16" s="292"/>
+      <c r="C16" s="292"/>
+      <c r="D16" s="292"/>
+      <c r="E16" s="293"/>
+      <c r="F16" s="293"/>
+      <c r="G16" s="293"/>
+      <c r="H16" s="293"/>
+      <c r="I16" s="293"/>
+      <c r="J16" s="294"/>
+      <c r="K16" s="295"/>
       <c r="L16" s="53"/>
     </row>
-    <row r="17" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="298"/>
-      <c r="C17" s="298"/>
-      <c r="D17" s="299" t="s">
+      <c r="B17" s="296"/>
+      <c r="C17" s="296"/>
+      <c r="D17" s="297" t="s">
         <v>2</v>
       </c>
       <c r="E17" s="221">
         <f>+FORMATO!M15</f>
         <v>0</v>
       </c>
-      <c r="F17" s="300"/>
-      <c r="G17" s="301"/>
+      <c r="F17" s="298"/>
+      <c r="G17" s="299"/>
       <c r="H17" s="15"/>
-      <c r="I17" s="297"/>
-      <c r="J17" s="296" t="s">
+      <c r="I17" s="295"/>
+      <c r="J17" s="294" t="s">
         <v>14</v>
       </c>
-      <c r="K17" s="297" t="s">
+      <c r="K17" s="295" t="s">
         <v>2</v>
       </c>
-      <c r="L17" s="306">
+      <c r="L17" s="303">
         <f>+FORMATO!M11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="298"/>
-      <c r="C18" s="298"/>
-      <c r="D18" s="299" t="s">
+      <c r="B18" s="296"/>
+      <c r="C18" s="296"/>
+      <c r="D18" s="297" t="s">
         <v>2</v>
       </c>
       <c r="E18" s="221">
         <f>+FORMATO!M16</f>
         <v>0</v>
       </c>
-      <c r="F18" s="300"/>
-      <c r="G18" s="301"/>
+      <c r="F18" s="298"/>
+      <c r="G18" s="299"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="297"/>
-      <c r="J18" s="296" t="s">
+      <c r="I18" s="295"/>
+      <c r="J18" s="294" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="297" t="s">
+      <c r="K18" s="295" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="302">
+      <c r="L18" s="300">
         <f>+FORMATO!M12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="B19" s="298"/>
-      <c r="C19" s="298"/>
-      <c r="D19" s="299" t="s">
+      <c r="B19" s="296"/>
+      <c r="C19" s="296"/>
+      <c r="D19" s="297" t="s">
         <v>2</v>
       </c>
       <c r="E19" s="221">
         <f>+FORMATO!M17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="300"/>
-      <c r="G19" s="301"/>
+      <c r="F19" s="298"/>
+      <c r="G19" s="299"/>
       <c r="H19" s="15"/>
-      <c r="I19" s="297"/>
-      <c r="J19" s="296" t="s">
+      <c r="I19" s="295"/>
+      <c r="J19" s="294" t="s">
         <v>17</v>
       </c>
-      <c r="K19" s="297" t="s">
+      <c r="K19" s="295" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="302">
+      <c r="L19" s="300">
         <f>+FORMATO!M13</f>
         <v>0</v>
       </c>
-      <c r="M19" s="403">
+      <c r="M19" s="400">
         <f>+FORMATO!E11</f>
         <v>0</v>
       </c>
-      <c r="N19" s="404"/>
-    </row>
-    <row r="20" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N19" s="401"/>
+    </row>
+    <row r="20" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="55" t="s">
         <v>18</v>
       </c>
@@ -9160,7 +9160,7 @@
       <c r="K20" s="57"/>
       <c r="L20" s="32"/>
     </row>
-    <row r="21" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="58"/>
       <c r="B21" s="59"/>
       <c r="C21" s="59"/>
@@ -9175,17 +9175,17 @@
       <c r="L21" s="60"/>
       <c r="M21" s="33"/>
     </row>
-    <row r="22" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="61"/>
-      <c r="B22" s="406" t="s">
+      <c r="B22" s="403" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="407"/>
-      <c r="D22" s="407"/>
-      <c r="E22" s="407"/>
-      <c r="F22" s="407"/>
-      <c r="G22" s="407"/>
-      <c r="H22" s="408"/>
+      <c r="C22" s="404"/>
+      <c r="D22" s="404"/>
+      <c r="E22" s="404"/>
+      <c r="F22" s="404"/>
+      <c r="G22" s="404"/>
+      <c r="H22" s="405"/>
       <c r="I22" s="183" t="s">
         <v>20</v>
       </c>
@@ -9196,7 +9196,7 @@
       <c r="L22" s="63"/>
       <c r="M22" s="33"/>
     </row>
-    <row r="23" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="61"/>
       <c r="B23" s="224" t="s">
         <v>22</v>
@@ -9218,7 +9218,7 @@
       <c r="L23" s="63"/>
       <c r="M23" s="33"/>
     </row>
-    <row r="24" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="61"/>
       <c r="B24" s="225" t="s">
         <v>24</v>
@@ -9240,7 +9240,7 @@
       <c r="L24" s="65"/>
       <c r="M24" s="33"/>
     </row>
-    <row r="25" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="61"/>
       <c r="B25" s="226" t="s">
         <v>25</v>
@@ -9261,7 +9261,7 @@
       <c r="L25" s="63"/>
       <c r="M25" s="34"/>
     </row>
-    <row r="26" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="61"/>
       <c r="B26" s="225" t="s">
         <v>26</v>
@@ -9283,39 +9283,39 @@
       <c r="L26" s="63"/>
       <c r="M26" s="33"/>
     </row>
-    <row r="27" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="61"/>
       <c r="B27" s="62"/>
       <c r="C27" s="62"/>
       <c r="D27" s="92"/>
-      <c r="E27" s="410"/>
-      <c r="F27" s="410"/>
-      <c r="G27" s="410"/>
-      <c r="H27" s="410"/>
+      <c r="E27" s="407"/>
+      <c r="F27" s="407"/>
+      <c r="G27" s="407"/>
+      <c r="H27" s="407"/>
       <c r="I27" s="39"/>
       <c r="J27" s="62"/>
       <c r="K27" s="62"/>
       <c r="L27" s="63"/>
       <c r="M27" s="33"/>
     </row>
-    <row r="28" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="61"/>
-      <c r="B28" s="406" t="s">
+      <c r="B28" s="403" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="407"/>
-      <c r="D28" s="407"/>
-      <c r="E28" s="407"/>
-      <c r="F28" s="407"/>
-      <c r="G28" s="407"/>
-      <c r="H28" s="407"/>
-      <c r="I28" s="407"/>
-      <c r="J28" s="408"/>
+      <c r="C28" s="404"/>
+      <c r="D28" s="404"/>
+      <c r="E28" s="404"/>
+      <c r="F28" s="404"/>
+      <c r="G28" s="404"/>
+      <c r="H28" s="404"/>
+      <c r="I28" s="404"/>
+      <c r="J28" s="405"/>
       <c r="K28" s="62"/>
       <c r="L28" s="63"/>
       <c r="M28" s="33"/>
     </row>
-    <row r="29" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="61"/>
       <c r="B29" s="224" t="s">
         <v>28</v>
@@ -9337,7 +9337,7 @@
       <c r="L29" s="63"/>
       <c r="M29" s="33"/>
     </row>
-    <row r="30" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="61"/>
       <c r="B30" s="225" t="s">
         <v>29</v>
@@ -9359,7 +9359,7 @@
       <c r="L30" s="63"/>
       <c r="M30" s="33"/>
     </row>
-    <row r="31" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="61"/>
       <c r="B31" s="225" t="s">
         <v>30</v>
@@ -9381,7 +9381,7 @@
       <c r="L31" s="63"/>
       <c r="M31" s="33"/>
     </row>
-    <row r="32" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="61"/>
       <c r="B32" s="227" t="s">
         <v>31</v>
@@ -9403,7 +9403,7 @@
       <c r="L32" s="63"/>
       <c r="M32" s="33"/>
     </row>
-    <row r="33" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="68"/>
       <c r="B33" s="70"/>
       <c r="C33" s="70"/>
@@ -9418,7 +9418,7 @@
       <c r="L33" s="71"/>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="77"/>
       <c r="B34" s="77"/>
       <c r="C34" s="77"/>
@@ -9433,7 +9433,7 @@
       <c r="L34" s="78"/>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="179" t="s">
         <v>33</v>
       </c>
@@ -9450,7 +9450,7 @@
       <c r="L35" s="182"/>
       <c r="M35" s="15"/>
     </row>
-    <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="201" t="s">
         <v>34</v>
       </c>
@@ -9469,7 +9469,7 @@
       <c r="L36" s="72"/>
       <c r="M36" s="28"/>
     </row>
-    <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="179" t="s">
         <v>35</v>
       </c>
@@ -9484,7 +9484,7 @@
       <c r="L37" s="72"/>
       <c r="M37" s="28"/>
     </row>
-    <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="79" t="s">
         <v>36</v>
       </c>
@@ -9501,7 +9501,7 @@
       <c r="L38" s="45"/>
       <c r="M38" s="28"/>
     </row>
-    <row r="39" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="79" t="s">
         <v>37</v>
       </c>
@@ -9518,24 +9518,24 @@
       <c r="L39" s="45"/>
       <c r="M39" s="28"/>
     </row>
-    <row r="40" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="409" t="s">
+    <row r="40" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="406" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="409"/>
-      <c r="C40" s="409"/>
-      <c r="D40" s="409"/>
-      <c r="E40" s="409"/>
-      <c r="F40" s="409"/>
-      <c r="G40" s="409"/>
-      <c r="H40" s="409"/>
-      <c r="I40" s="409"/>
-      <c r="J40" s="409"/>
-      <c r="K40" s="409"/>
-      <c r="L40" s="409"/>
+      <c r="B40" s="406"/>
+      <c r="C40" s="406"/>
+      <c r="D40" s="406"/>
+      <c r="E40" s="406"/>
+      <c r="F40" s="406"/>
+      <c r="G40" s="406"/>
+      <c r="H40" s="406"/>
+      <c r="I40" s="406"/>
+      <c r="J40" s="406"/>
+      <c r="K40" s="406"/>
+      <c r="L40" s="406"/>
       <c r="M40" s="28"/>
     </row>
-    <row r="41" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="79" t="s">
         <v>39</v>
       </c>
@@ -9552,21 +9552,21 @@
       <c r="L41" s="45"/>
       <c r="M41" s="28"/>
     </row>
-    <row r="42" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="405" t="s">
+    <row r="42" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="402" t="s">
         <v>158</v>
       </c>
-      <c r="B42" s="405"/>
-      <c r="C42" s="405"/>
-      <c r="D42" s="405"/>
-      <c r="E42" s="405"/>
-      <c r="F42" s="405"/>
-      <c r="G42" s="405"/>
-      <c r="H42" s="405"/>
-      <c r="I42" s="405"/>
-      <c r="J42" s="405"/>
-      <c r="K42" s="405"/>
-      <c r="L42" s="405"/>
+      <c r="B42" s="402"/>
+      <c r="C42" s="402"/>
+      <c r="D42" s="402"/>
+      <c r="E42" s="402"/>
+      <c r="F42" s="402"/>
+      <c r="G42" s="402"/>
+      <c r="H42" s="402"/>
+      <c r="I42" s="402"/>
+      <c r="J42" s="402"/>
+      <c r="K42" s="402"/>
+      <c r="L42" s="402"/>
       <c r="M42" s="28"/>
     </row>
     <row r="43" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9587,7 +9587,7 @@
       <c r="N43" s="180"/>
       <c r="O43" s="181"/>
     </row>
-    <row r="44" spans="1:15" ht="44.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="73"/>
       <c r="B44" s="73"/>
       <c r="C44" s="73"/>
@@ -9647,7 +9647,7 @@
       <c r="L47" s="80"/>
       <c r="M47" s="35"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="62" t="s">
         <v>42</v>
       </c>
@@ -9664,9 +9664,9 @@
       <c r="L48" s="39"/>
       <c r="M48" s="36"/>
     </row>
-    <row r="49" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="62"/>
       <c r="C49" s="62"/>
@@ -9682,7 +9682,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="hpLhcbzeW8a1H8jEKLXeKEw0t1DuTeENzT5umWkeiFBbl98SvIR8Sk/usafsXmHbIH1tTB69JwTANdx5TEF/kA==" saltValue="AAQ0pciYq6ntHE72ujH4+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
@@ -9719,62 +9719,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="33" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="33" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" style="33" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="33" customWidth="1"/>
     <col min="3" max="3" width="12" style="33" customWidth="1"/>
-    <col min="4" max="8" width="10.44140625" style="33" customWidth="1"/>
-    <col min="9" max="9" width="6.33203125" style="33" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" style="33" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="33" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" style="33" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" style="33" customWidth="1"/>
-    <col min="14" max="14" width="1.33203125" style="33" customWidth="1"/>
-    <col min="15" max="16384" width="10.33203125" style="33"/>
+    <col min="4" max="8" width="10.42578125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" style="33" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="33" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" style="33" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="33" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="33" customWidth="1"/>
+    <col min="14" max="14" width="1.28515625" style="33" customWidth="1"/>
+    <col min="15" max="16384" width="10.28515625" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="420" t="s">
+    <row r="1" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:16" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="417" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="421"/>
-      <c r="D2" s="421"/>
-      <c r="E2" s="421"/>
-      <c r="F2" s="421"/>
-      <c r="G2" s="421"/>
-      <c r="H2" s="421"/>
-      <c r="I2" s="421"/>
-      <c r="J2" s="421"/>
-      <c r="K2" s="422"/>
+      <c r="C2" s="418"/>
+      <c r="D2" s="418"/>
+      <c r="E2" s="418"/>
+      <c r="F2" s="418"/>
+      <c r="G2" s="418"/>
+      <c r="H2" s="418"/>
+      <c r="I2" s="418"/>
+      <c r="J2" s="418"/>
+      <c r="K2" s="419"/>
       <c r="L2" s="86"/>
       <c r="M2" s="86"/>
       <c r="N2" s="86"/>
       <c r="O2" s="86"/>
       <c r="P2" s="86"/>
     </row>
-    <row r="3" spans="2:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="423" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="424"/>
-      <c r="D3" s="424"/>
-      <c r="E3" s="424"/>
-      <c r="F3" s="424"/>
-      <c r="G3" s="424"/>
-      <c r="H3" s="424"/>
-      <c r="I3" s="424"/>
-      <c r="J3" s="424"/>
-      <c r="K3" s="425"/>
+    <row r="3" spans="2:16" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="420" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="421"/>
+      <c r="D3" s="421"/>
+      <c r="E3" s="421"/>
+      <c r="F3" s="421"/>
+      <c r="G3" s="421"/>
+      <c r="H3" s="421"/>
+      <c r="I3" s="421"/>
+      <c r="J3" s="421"/>
+      <c r="K3" s="422"/>
       <c r="L3" s="86"/>
       <c r="M3" s="86"/>
       <c r="N3" s="86"/>
       <c r="O3" s="86"/>
       <c r="P3" s="86"/>
     </row>
-    <row r="4" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:16" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="2:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="205" t="s">
         <v>43</v>
       </c>
@@ -9794,7 +9794,7 @@
       <c r="N5" s="87"/>
       <c r="O5" s="87"/>
     </row>
-    <row r="6" spans="2:16" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="206" t="s">
         <v>44</v>
       </c>
@@ -9809,7 +9809,7 @@
       <c r="K6" s="260" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="368">
+      <c r="L6" s="365">
         <f>+FORMATO!F11</f>
         <v>0</v>
       </c>
@@ -9817,14 +9817,14 @@
       <c r="N6" s="87"/>
       <c r="O6" s="87"/>
     </row>
-    <row r="7" spans="2:16" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="206" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="203"/>
-      <c r="D7" s="304">
+      <c r="D7" s="301">
         <f>+Balanza!C7</f>
-        <v>-2.4000000000000001E-5</v>
+        <v>-2.4600000000000002E-5</v>
       </c>
       <c r="E7" s="87"/>
       <c r="F7" s="87"/>
@@ -9838,7 +9838,7 @@
       <c r="N7" s="87"/>
       <c r="O7" s="87"/>
     </row>
-    <row r="8" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
         <v>46</v>
       </c>
@@ -9858,14 +9858,14 @@
       <c r="N8" s="87"/>
       <c r="O8" s="87"/>
     </row>
-    <row r="9" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="207" t="s">
         <v>47</v>
       </c>
       <c r="C9" s="204"/>
       <c r="D9" s="209">
         <f>+Balanza!C12</f>
-        <v>45799</v>
+        <v>46160</v>
       </c>
       <c r="E9" s="99"/>
       <c r="F9" s="99"/>
@@ -9879,22 +9879,22 @@
       <c r="N9" s="87"/>
       <c r="O9" s="87"/>
     </row>
-    <row r="10" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L10" s="87"/>
       <c r="M10" s="87"/>
       <c r="N10" s="87"/>
       <c r="O10" s="87"/>
     </row>
-    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="406" t="s">
+    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="403" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="407"/>
-      <c r="D11" s="407"/>
-      <c r="E11" s="407"/>
-      <c r="F11" s="407"/>
-      <c r="G11" s="407"/>
-      <c r="H11" s="408"/>
+      <c r="C11" s="404"/>
+      <c r="D11" s="404"/>
+      <c r="E11" s="404"/>
+      <c r="F11" s="404"/>
+      <c r="G11" s="404"/>
+      <c r="H11" s="405"/>
       <c r="I11" s="170" t="s">
         <v>48</v>
       </c>
@@ -9906,19 +9906,19 @@
       </c>
       <c r="L11" s="197"/>
     </row>
-    <row r="12" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="285" t="s">
+    <row r="12" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="283" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="286" t="s">
+      <c r="C12" s="284" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="289"/>
-      <c r="E12" s="289"/>
-      <c r="F12" s="289"/>
-      <c r="G12" s="289"/>
-      <c r="H12" s="290"/>
-      <c r="I12" s="288" t="s">
+      <c r="D12" s="287"/>
+      <c r="E12" s="287"/>
+      <c r="F12" s="287"/>
+      <c r="G12" s="287"/>
+      <c r="H12" s="288"/>
+      <c r="I12" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="84">
@@ -9934,19 +9934,19 @@
       <c r="N12" s="87"/>
       <c r="O12" s="87"/>
     </row>
-    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="285" t="s">
+    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="283" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="287" t="s">
+      <c r="C13" s="285" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="289"/>
-      <c r="E13" s="289"/>
-      <c r="F13" s="289"/>
-      <c r="G13" s="289"/>
-      <c r="H13" s="290"/>
-      <c r="I13" s="288" t="s">
+      <c r="D13" s="287"/>
+      <c r="E13" s="287"/>
+      <c r="F13" s="287"/>
+      <c r="G13" s="287"/>
+      <c r="H13" s="288"/>
+      <c r="I13" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="84">
@@ -9959,19 +9959,19 @@
       </c>
       <c r="L13" s="254"/>
     </row>
-    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="285" t="s">
+    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="283" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="286" t="s">
+      <c r="C14" s="284" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="289"/>
-      <c r="E14" s="289"/>
-      <c r="F14" s="289"/>
-      <c r="G14" s="289"/>
-      <c r="H14" s="290"/>
-      <c r="I14" s="288" t="s">
+      <c r="D14" s="287"/>
+      <c r="E14" s="287"/>
+      <c r="F14" s="287"/>
+      <c r="G14" s="287"/>
+      <c r="H14" s="288"/>
+      <c r="I14" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="84">
@@ -9987,19 +9987,19 @@
       <c r="N14" s="87"/>
       <c r="O14" s="87"/>
     </row>
-    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="285" t="s">
+    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="283" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="286" t="s">
+      <c r="C15" s="284" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="289"/>
-      <c r="E15" s="289"/>
-      <c r="F15" s="289"/>
-      <c r="G15" s="289"/>
-      <c r="H15" s="290"/>
-      <c r="I15" s="288" t="s">
+      <c r="D15" s="287"/>
+      <c r="E15" s="287"/>
+      <c r="F15" s="287"/>
+      <c r="G15" s="287"/>
+      <c r="H15" s="288"/>
+      <c r="I15" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="84">
@@ -10012,19 +10012,19 @@
       </c>
       <c r="L15" s="255"/>
     </row>
-    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="285" t="s">
+    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="283" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="286" t="s">
+      <c r="C16" s="284" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="289"/>
-      <c r="E16" s="289"/>
-      <c r="F16" s="289"/>
-      <c r="G16" s="289"/>
-      <c r="H16" s="290"/>
-      <c r="I16" s="288" t="s">
+      <c r="D16" s="287"/>
+      <c r="E16" s="287"/>
+      <c r="F16" s="287"/>
+      <c r="G16" s="287"/>
+      <c r="H16" s="288"/>
+      <c r="I16" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="84">
@@ -10039,19 +10039,19 @@
       <c r="M16" s="87"/>
       <c r="N16" s="87"/>
     </row>
-    <row r="17" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="285" t="s">
+    <row r="17" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="283" t="s">
         <v>176</v>
       </c>
-      <c r="C17" s="286" t="s">
+      <c r="C17" s="284" t="s">
         <v>163</v>
       </c>
-      <c r="D17" s="289"/>
-      <c r="E17" s="289"/>
-      <c r="F17" s="289"/>
-      <c r="G17" s="289"/>
-      <c r="H17" s="290"/>
-      <c r="I17" s="288" t="s">
+      <c r="D17" s="287"/>
+      <c r="E17" s="287"/>
+      <c r="F17" s="287"/>
+      <c r="G17" s="287"/>
+      <c r="H17" s="288"/>
+      <c r="I17" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J17" s="84">
@@ -10064,19 +10064,19 @@
       </c>
       <c r="L17" s="256"/>
     </row>
-    <row r="18" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="285" t="s">
+    <row r="18" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="283" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="286" t="s">
+      <c r="C18" s="284" t="s">
         <v>164</v>
       </c>
-      <c r="D18" s="289"/>
-      <c r="E18" s="289"/>
-      <c r="F18" s="289"/>
-      <c r="G18" s="289"/>
-      <c r="H18" s="290"/>
-      <c r="I18" s="288" t="s">
+      <c r="D18" s="287"/>
+      <c r="E18" s="287"/>
+      <c r="F18" s="287"/>
+      <c r="G18" s="287"/>
+      <c r="H18" s="288"/>
+      <c r="I18" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J18" s="84">
@@ -10092,19 +10092,19 @@
       <c r="N18" s="87"/>
       <c r="O18" s="87"/>
     </row>
-    <row r="19" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="285" t="s">
+    <row r="19" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="283" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="286" t="s">
+      <c r="C19" s="284" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="289"/>
-      <c r="E19" s="289"/>
-      <c r="F19" s="289"/>
-      <c r="G19" s="289"/>
-      <c r="H19" s="290"/>
-      <c r="I19" s="288" t="s">
+      <c r="D19" s="287"/>
+      <c r="E19" s="287"/>
+      <c r="F19" s="287"/>
+      <c r="G19" s="287"/>
+      <c r="H19" s="288"/>
+      <c r="I19" s="286" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="88">
@@ -10117,19 +10117,19 @@
       </c>
       <c r="L19" s="257"/>
     </row>
-    <row r="20" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="285" t="s">
+    <row r="20" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="283" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="286" t="s">
+      <c r="C20" s="284" t="s">
         <v>171</v>
       </c>
-      <c r="D20" s="289"/>
-      <c r="E20" s="289"/>
-      <c r="F20" s="289"/>
-      <c r="G20" s="289"/>
-      <c r="H20" s="290"/>
-      <c r="I20" s="288" t="s">
+      <c r="D20" s="287"/>
+      <c r="E20" s="287"/>
+      <c r="F20" s="287"/>
+      <c r="G20" s="287"/>
+      <c r="H20" s="288"/>
+      <c r="I20" s="286" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="83" t="e">
@@ -10144,19 +10144,19 @@
       <c r="N20" s="87"/>
       <c r="O20" s="87"/>
     </row>
-    <row r="21" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="285" t="s">
+    <row r="21" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="283" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="286" t="s">
+      <c r="C21" s="284" t="s">
         <v>172</v>
       </c>
-      <c r="D21" s="289"/>
-      <c r="E21" s="289"/>
-      <c r="F21" s="289"/>
-      <c r="G21" s="289"/>
-      <c r="H21" s="290"/>
-      <c r="I21" s="288" t="s">
+      <c r="D21" s="287"/>
+      <c r="E21" s="287"/>
+      <c r="F21" s="287"/>
+      <c r="G21" s="287"/>
+      <c r="H21" s="288"/>
+      <c r="I21" s="286" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="83" t="e">
@@ -10168,19 +10168,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="285" t="s">
+    <row r="22" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="283" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="286" t="s">
+      <c r="C22" s="284" t="s">
         <v>173</v>
       </c>
-      <c r="D22" s="289"/>
-      <c r="E22" s="289"/>
-      <c r="F22" s="289"/>
-      <c r="G22" s="289"/>
-      <c r="H22" s="290"/>
-      <c r="I22" s="288" t="s">
+      <c r="D22" s="287"/>
+      <c r="E22" s="287"/>
+      <c r="F22" s="287"/>
+      <c r="G22" s="287"/>
+      <c r="H22" s="288"/>
+      <c r="I22" s="286" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="83" t="e">
@@ -10192,19 +10192,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="285" t="s">
+    <row r="23" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="283" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="286" t="s">
+      <c r="C23" s="284" t="s">
         <v>174</v>
       </c>
-      <c r="D23" s="289"/>
-      <c r="E23" s="289"/>
-      <c r="F23" s="289"/>
-      <c r="G23" s="289"/>
-      <c r="H23" s="290"/>
-      <c r="I23" s="288" t="s">
+      <c r="D23" s="287"/>
+      <c r="E23" s="287"/>
+      <c r="F23" s="287"/>
+      <c r="G23" s="287"/>
+      <c r="H23" s="288"/>
+      <c r="I23" s="286" t="s">
         <v>32</v>
       </c>
       <c r="J23" s="85" t="e">
@@ -10216,30 +10216,30 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:15" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="81"/>
       <c r="B33" s="81"/>
       <c r="C33" s="81"/>
     </row>
-    <row r="34" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="89"/>
     </row>
-    <row r="40" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:K2"/>
@@ -10267,33 +10267,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="168" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="168" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="168" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="168" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="168" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="168" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="168" customWidth="1"/>
     <col min="5" max="6" width="14" style="168" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="168" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="168" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" style="168" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" style="168" customWidth="1"/>
-    <col min="11" max="11" width="17.44140625" style="168" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" style="168" customWidth="1"/>
-    <col min="13" max="16384" width="11.44140625" style="168"/>
+    <col min="7" max="7" width="13.7109375" style="168" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="168" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="168" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="168" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" style="168" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="168" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="168"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="426"/>
-      <c r="B1" s="429" t="s">
+    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="423"/>
+      <c r="B1" s="426" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="430"/>
-      <c r="D1" s="430"/>
-      <c r="E1" s="430"/>
-      <c r="F1" s="430"/>
-      <c r="G1" s="430"/>
-      <c r="H1" s="431"/>
+      <c r="C1" s="427"/>
+      <c r="D1" s="427"/>
+      <c r="E1" s="427"/>
+      <c r="F1" s="427"/>
+      <c r="G1" s="427"/>
+      <c r="H1" s="428"/>
       <c r="I1" s="104" t="s">
         <v>55</v>
       </c>
@@ -10301,15 +10301,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="427"/>
-      <c r="B2" s="432"/>
-      <c r="C2" s="433"/>
-      <c r="D2" s="433"/>
-      <c r="E2" s="433"/>
-      <c r="F2" s="433"/>
-      <c r="G2" s="433"/>
-      <c r="H2" s="434"/>
+    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="424"/>
+      <c r="B2" s="429"/>
+      <c r="C2" s="430"/>
+      <c r="D2" s="430"/>
+      <c r="E2" s="430"/>
+      <c r="F2" s="430"/>
+      <c r="G2" s="430"/>
+      <c r="H2" s="431"/>
       <c r="I2" s="104" t="s">
         <v>57</v>
       </c>
@@ -10317,31 +10317,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="427"/>
-      <c r="B3" s="432"/>
-      <c r="C3" s="433"/>
-      <c r="D3" s="433"/>
-      <c r="E3" s="433"/>
-      <c r="F3" s="433"/>
-      <c r="G3" s="433"/>
-      <c r="H3" s="434"/>
+    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="424"/>
+      <c r="B3" s="429"/>
+      <c r="C3" s="430"/>
+      <c r="D3" s="430"/>
+      <c r="E3" s="430"/>
+      <c r="F3" s="430"/>
+      <c r="G3" s="430"/>
+      <c r="H3" s="431"/>
       <c r="I3" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="376">
+      <c r="J3" s="373">
         <v>46146</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="428"/>
-      <c r="B4" s="435"/>
-      <c r="C4" s="436"/>
-      <c r="D4" s="436"/>
-      <c r="E4" s="436"/>
-      <c r="F4" s="436"/>
-      <c r="G4" s="436"/>
-      <c r="H4" s="437"/>
+    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="425"/>
+      <c r="B4" s="432"/>
+      <c r="C4" s="433"/>
+      <c r="D4" s="433"/>
+      <c r="E4" s="433"/>
+      <c r="F4" s="433"/>
+      <c r="G4" s="433"/>
+      <c r="H4" s="434"/>
       <c r="I4" s="104" t="s">
         <v>59</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="106" t="s">
         <v>61</v>
       </c>
@@ -10366,7 +10366,7 @@
       <c r="J6" s="236"/>
       <c r="L6" s="103"/>
     </row>
-    <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="106" t="s">
         <v>62</v>
       </c>
@@ -10383,7 +10383,7 @@
       <c r="J7" s="236"/>
       <c r="L7" s="258"/>
     </row>
-    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="106" t="s">
         <v>63</v>
       </c>
@@ -10399,9 +10399,9 @@
       <c r="I8" s="235"/>
       <c r="J8" s="236"/>
     </row>
-    <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="107" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>151</v>
@@ -10415,15 +10415,15 @@
       <c r="I9" s="235"/>
       <c r="J9" s="236"/>
     </row>
-    <row r="11" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="103" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="103"/>
     </row>
-    <row r="13" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="252" t="s">
         <v>65</v>
       </c>
@@ -10432,13 +10432,13 @@
       </c>
       <c r="I13" s="103"/>
     </row>
-    <row r="14" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F14" s="237"/>
       <c r="H14" s="237"/>
       <c r="K14" s="237"/>
       <c r="M14" s="237"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="251" t="s">
         <v>168</v>
       </c>
@@ -10450,7 +10450,7 @@
       <c r="G15" s="238"/>
       <c r="I15" s="103"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="251" t="s">
         <v>165</v>
       </c>
@@ -10462,7 +10462,7 @@
       <c r="H16" s="238"/>
       <c r="K16" s="238"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="251" t="s">
         <v>166</v>
       </c>
@@ -10473,32 +10473,32 @@
       <c r="I17" s="103"/>
       <c r="M17" s="238"/>
     </row>
-    <row r="18" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="440" t="s">
+    <row r="18" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="437" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="440"/>
-      <c r="C18" s="440"/>
-      <c r="D18" s="440"/>
-      <c r="E18" s="440"/>
-    </row>
-    <row r="19" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="437"/>
+      <c r="C18" s="437"/>
+      <c r="D18" s="437"/>
+      <c r="E18" s="437"/>
+    </row>
+    <row r="19" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F19" s="238"/>
       <c r="K19" s="238"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="252" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="238"/>
       <c r="H20" s="238"/>
-      <c r="I20" s="291"/>
+      <c r="I20" s="289"/>
       <c r="J20" s="238"/>
       <c r="K20" s="238"/>
       <c r="N20" s="238"/>
       <c r="S20" s="238"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="G21" s="238"/>
       <c r="H21" s="238"/>
       <c r="I21" s="238"/>
@@ -10507,7 +10507,7 @@
       <c r="N21" s="238"/>
       <c r="S21" s="238"/>
     </row>
-    <row r="22" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="251" t="s">
         <v>71</v>
       </c>
@@ -10524,7 +10524,7 @@
       <c r="Q22" s="103"/>
       <c r="R22" s="103"/>
     </row>
-    <row r="23" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="251" t="s">
         <v>72</v>
       </c>
@@ -10537,7 +10537,7 @@
       <c r="M23" s="238"/>
       <c r="R23" s="238"/>
     </row>
-    <row r="24" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="251" t="s">
         <v>73</v>
       </c>
@@ -10550,7 +10550,7 @@
       <c r="M24" s="238"/>
       <c r="R24" s="238"/>
     </row>
-    <row r="25" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G25" s="238"/>
       <c r="H25" s="238"/>
       <c r="I25" s="238"/>
@@ -10561,7 +10561,7 @@
       <c r="T25" s="171"/>
       <c r="U25" s="171"/>
     </row>
-    <row r="26" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="103" t="s">
         <v>74</v>
       </c>
@@ -10582,7 +10582,7 @@
       <c r="T26" s="171"/>
       <c r="U26" s="171"/>
     </row>
-    <row r="27" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G27" s="238"/>
       <c r="H27" s="238"/>
       <c r="I27" s="238"/>
@@ -10593,7 +10593,7 @@
       <c r="T27" s="171"/>
       <c r="U27" s="171"/>
     </row>
-    <row r="28" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G28" s="238"/>
       <c r="H28" s="238"/>
       <c r="I28" s="238"/>
@@ -10607,7 +10607,7 @@
       <c r="T28" s="171"/>
       <c r="U28" s="171"/>
     </row>
-    <row r="29" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G29" s="238"/>
       <c r="H29" s="238"/>
       <c r="I29" s="238"/>
@@ -10624,7 +10624,7 @@
       <c r="T29" s="171"/>
       <c r="U29" s="171"/>
     </row>
-    <row r="30" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G30" s="238"/>
       <c r="H30" s="238"/>
       <c r="I30" s="238"/>
@@ -10635,7 +10635,7 @@
       <c r="T30" s="171"/>
       <c r="U30" s="171"/>
     </row>
-    <row r="31" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G31" s="237"/>
       <c r="K31" s="237"/>
       <c r="N31" s="237"/>
@@ -10644,7 +10644,7 @@
       <c r="T31" s="171"/>
       <c r="U31" s="171"/>
     </row>
-    <row r="32" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G32" s="238"/>
       <c r="H32" s="238"/>
       <c r="I32" s="238"/>
@@ -10661,7 +10661,7 @@
       <c r="T32" s="171"/>
       <c r="U32" s="171"/>
     </row>
-    <row r="33" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G33" s="238"/>
       <c r="H33" s="238"/>
       <c r="I33" s="238"/>
@@ -10672,7 +10672,7 @@
       <c r="T33" s="171"/>
       <c r="U33" s="171"/>
     </row>
-    <row r="34" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G34" s="238"/>
       <c r="H34" s="238"/>
       <c r="I34" s="238"/>
@@ -10689,7 +10689,7 @@
       <c r="T34" s="172"/>
       <c r="U34" s="172"/>
     </row>
-    <row r="35" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G35" s="238"/>
       <c r="H35" s="238"/>
       <c r="I35" s="238"/>
@@ -10702,7 +10702,7 @@
       <c r="T35" s="177"/>
       <c r="U35" s="177"/>
     </row>
-    <row r="36" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G36" s="238"/>
       <c r="H36" s="238"/>
       <c r="I36" s="238"/>
@@ -10717,7 +10717,7 @@
       <c r="T36" s="177"/>
       <c r="U36" s="177"/>
     </row>
-    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G37" s="238"/>
       <c r="H37" s="238"/>
       <c r="I37" s="238"/>
@@ -10732,25 +10732,25 @@
       <c r="T37" s="177"/>
       <c r="U37" s="177"/>
     </row>
-    <row r="38" spans="1:21" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I38" s="108"/>
       <c r="J38" s="108"/>
     </row>
-    <row r="39" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="443" t="s">
+    <row r="39" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="440" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="444"/>
-      <c r="C39" s="444"/>
-      <c r="D39" s="444"/>
-      <c r="E39" s="444"/>
-      <c r="F39" s="444"/>
-      <c r="G39" s="444"/>
-      <c r="H39" s="445"/>
+      <c r="B39" s="441"/>
+      <c r="C39" s="441"/>
+      <c r="D39" s="441"/>
+      <c r="E39" s="441"/>
+      <c r="F39" s="441"/>
+      <c r="G39" s="441"/>
+      <c r="H39" s="442"/>
       <c r="I39" s="108"/>
       <c r="J39" s="108"/>
     </row>
-    <row r="40" spans="1:21" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="119" t="s">
         <v>75</v>
       </c>
@@ -10778,7 +10778,7 @@
       <c r="I40" s="108"/>
       <c r="J40" s="108"/>
     </row>
-    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="116" t="s">
         <v>83</v>
       </c>
@@ -10795,7 +10795,7 @@
       <c r="I41" s="108"/>
       <c r="J41" s="108"/>
     </row>
-    <row r="42" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="123" t="str">
         <f>Balanza!E25</f>
         <v>Peso material seco en estufa</v>
@@ -10813,9 +10813,9 @@
       <c r="E42" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="F42" s="127" t="e">
+      <c r="F42" s="127">
         <f>SQRT((F43*F43)+(F44*F44)+(F45*F45))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G42" s="126" t="e">
         <f>1/(B46+B54-B50)</f>
@@ -10829,7 +10829,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="109" t="s">
         <v>85</v>
       </c>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="I43" s="108"/>
     </row>
-    <row r="44" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="109" t="s">
         <v>87</v>
       </c>
@@ -10882,10 +10882,10 @@
         <v>84</v>
       </c>
       <c r="I44" s="108"/>
-      <c r="J44" s="438" t="s">
+      <c r="J44" s="435" t="s">
         <v>89</v>
       </c>
-      <c r="K44" s="439"/>
+      <c r="K44" s="436"/>
       <c r="L44" s="102" t="s">
         <v>76</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="109" t="s">
         <v>91</v>
       </c>
@@ -10908,9 +10908,9 @@
       <c r="E45" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F45" s="112" t="e">
+      <c r="F45" s="112">
         <f>C45/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G45" s="113" t="s">
         <v>84</v>
@@ -10933,7 +10933,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="46" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="123" t="str">
         <f>Balanza!E26</f>
         <v>Peso picnometro+agua</v>
@@ -10949,9 +10949,9 @@
       <c r="E46" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="127" t="e">
+      <c r="F46" s="127">
         <f>SQRT((F47*F47)+(F48*F48)+(F49*F49))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G46" s="125" t="e">
         <f>B42/POWER((B46+B54-B50),2)</f>
@@ -10978,7 +10978,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="47" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="109" t="s">
         <v>85</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="109" t="s">
         <v>87</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="109" t="s">
         <v>91</v>
       </c>
@@ -11073,9 +11073,9 @@
       <c r="E49" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="112" t="e">
+      <c r="F49" s="112">
         <f>C49/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G49" s="113" t="s">
         <v>84</v>
@@ -11098,7 +11098,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="123" t="str">
         <f>Balanza!E27</f>
         <v>Peso picnometro+material+agua</v>
@@ -11114,9 +11114,9 @@
       <c r="E50" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="127" t="e">
+      <c r="F50" s="127">
         <f>SQRT((F51*F51)+(F52*F52)+(F53*F53))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G50" s="131" t="e">
         <f>+B42/POWER((B46+B54-B50),2)</f>
@@ -11139,7 +11139,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="109" t="s">
         <v>85</v>
       </c>
@@ -11167,7 +11167,7 @@
       <c r="I51" s="108"/>
       <c r="J51" s="108"/>
     </row>
-    <row r="52" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="109" t="s">
         <v>87</v>
       </c>
@@ -11195,7 +11195,7 @@
       <c r="I52" s="108"/>
       <c r="J52" s="108"/>
     </row>
-    <row r="53" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="109" t="s">
         <v>91</v>
       </c>
@@ -11210,9 +11210,9 @@
       <c r="E53" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F53" s="112" t="e">
+      <c r="F53" s="112">
         <f>C53/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G53" s="113" t="s">
         <v>84</v>
@@ -11223,7 +11223,7 @@
       <c r="I53" s="108"/>
       <c r="J53" s="108"/>
     </row>
-    <row r="54" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="123" t="str">
         <f>Balanza!E28</f>
         <v>Peso material saturado sup. Seca</v>
@@ -11239,9 +11239,9 @@
       <c r="E54" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F54" s="127" t="e">
+      <c r="F54" s="127">
         <f>SQRT((F55*F55)+(F56*F56)+(F57*F57))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G54" s="131" t="e">
         <f>B42/POWER((B54+B46-B50),2)</f>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="J54" s="108"/>
     </row>
-    <row r="55" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="109" t="s">
         <v>85</v>
       </c>
@@ -11284,7 +11284,7 @@
       <c r="I55" s="108"/>
       <c r="J55" s="108"/>
     </row>
-    <row r="56" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="109" t="s">
         <v>87</v>
       </c>
@@ -11312,7 +11312,7 @@
       <c r="I56" s="108"/>
       <c r="J56" s="108"/>
     </row>
-    <row r="57" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="109" t="s">
         <v>91</v>
       </c>
@@ -11327,9 +11327,9 @@
       <c r="E57" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F57" s="112" t="e">
+      <c r="F57" s="112">
         <f>C57/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G57" s="113" t="s">
         <v>84</v>
@@ -11340,7 +11340,7 @@
       <c r="I57" s="108"/>
       <c r="J57" s="108"/>
     </row>
-    <row r="58" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="133" t="s">
         <v>94</v>
       </c>
@@ -11367,7 +11367,7 @@
       <c r="I58" s="108"/>
       <c r="J58" s="108"/>
     </row>
-    <row r="59" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="242"/>
       <c r="B59" s="243"/>
       <c r="C59" s="244" t="s">
@@ -11384,7 +11384,7 @@
       <c r="I59" s="108"/>
       <c r="J59" s="108"/>
     </row>
-    <row r="60" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="245"/>
       <c r="B60" s="246"/>
       <c r="C60" s="247" t="s">
@@ -11401,7 +11401,7 @@
       <c r="I60" s="108"/>
       <c r="J60" s="108"/>
     </row>
-    <row r="61" spans="1:13" s="239" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" s="239" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
@@ -11413,7 +11413,7 @@
       <c r="I61" s="108"/>
       <c r="J61" s="108"/>
     </row>
-    <row r="62" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="139"/>
       <c r="B62" s="140"/>
       <c r="C62" s="140"/>
@@ -11427,7 +11427,7 @@
       <c r="I62" s="108"/>
       <c r="J62" s="108"/>
     </row>
-    <row r="63" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="234" t="s">
         <v>98</v>
       </c>
@@ -11444,7 +11444,7 @@
       <c r="I63" s="108"/>
       <c r="J63" s="108"/>
     </row>
-    <row r="64" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="123" t="s">
         <v>99</v>
       </c>
@@ -11459,9 +11459,9 @@
       <c r="E64" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F64" s="127" t="e">
+      <c r="F64" s="127">
         <f>SQRT((F65*F65)+(F66*F66)+(F67*F67))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G64" s="131" t="e">
         <f>+ABS((B68-B72)/POWER((B64+B68-B72),2))</f>
@@ -11474,10 +11474,10 @@
       <c r="I64" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="J64" s="438" t="s">
+      <c r="J64" s="435" t="s">
         <v>89</v>
       </c>
-      <c r="K64" s="439"/>
+      <c r="K64" s="436"/>
       <c r="L64" s="102" t="s">
         <v>76</v>
       </c>
@@ -11485,7 +11485,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="109" t="s">
         <v>85</v>
       </c>
@@ -11524,7 +11524,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="66" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="109" t="s">
         <v>87</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="67" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="109" t="s">
         <v>91</v>
       </c>
@@ -11578,9 +11578,9 @@
       <c r="E67" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F67" s="112" t="e">
+      <c r="F67" s="112">
         <f>C67/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G67" s="113" t="s">
         <v>84</v>
@@ -11604,7 +11604,7 @@
       <c r="S67" s="108"/>
       <c r="T67" s="108"/>
     </row>
-    <row r="68" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="123" t="s">
         <v>101</v>
       </c>
@@ -11619,9 +11619,9 @@
       <c r="E68" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F68" s="127" t="e">
+      <c r="F68" s="127">
         <f>SQRT((F69*F69)+(F70*F70)+(F71*F71))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G68" s="125" t="e">
         <f>+B64/POWER((B68+B64-B72),2)</f>
@@ -11650,7 +11650,7 @@
       <c r="S68" s="108"/>
       <c r="T68" s="108"/>
     </row>
-    <row r="69" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" s="239" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="109" t="s">
         <v>85</v>
       </c>
@@ -11676,8 +11676,8 @@
         <v>84</v>
       </c>
       <c r="I69" s="108"/>
-      <c r="J69" s="441"/>
-      <c r="K69" s="442"/>
+      <c r="J69" s="438"/>
+      <c r="K69" s="439"/>
       <c r="L69" s="159" t="e">
         <f>SUM(L65:L68)</f>
         <v>#DIV/0!</v>
@@ -11689,7 +11689,7 @@
       <c r="S69" s="108"/>
       <c r="T69" s="108"/>
     </row>
-    <row r="70" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="109" t="s">
         <v>87</v>
       </c>
@@ -11725,7 +11725,7 @@
       <c r="S70" s="108"/>
       <c r="T70" s="108"/>
     </row>
-    <row r="71" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="109" t="s">
         <v>91</v>
       </c>
@@ -11740,9 +11740,9 @@
       <c r="E71" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F71" s="112" t="e">
+      <c r="F71" s="112">
         <f>C71/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G71" s="113" t="s">
         <v>84</v>
@@ -11762,7 +11762,7 @@
       <c r="S71" s="108"/>
       <c r="T71" s="108"/>
     </row>
-    <row r="72" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="123" t="s">
         <v>102</v>
       </c>
@@ -11777,9 +11777,9 @@
       <c r="E72" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F72" s="127" t="e">
+      <c r="F72" s="127">
         <f>SQRT((F73*F73)+(F74*F74)+(F75*F75))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G72" s="131" t="e">
         <f>+B64/POWER((B68+B64-B72),2)</f>
@@ -11803,7 +11803,7 @@
       <c r="S72" s="108"/>
       <c r="T72" s="108"/>
     </row>
-    <row r="73" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="109" t="s">
         <v>85</v>
       </c>
@@ -11838,7 +11838,7 @@
       <c r="S73" s="108"/>
       <c r="T73" s="108"/>
     </row>
-    <row r="74" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="109" t="s">
         <v>87</v>
       </c>
@@ -11873,7 +11873,7 @@
       <c r="S74" s="108"/>
       <c r="T74" s="108"/>
     </row>
-    <row r="75" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="109" t="s">
         <v>91</v>
       </c>
@@ -11888,9 +11888,9 @@
       <c r="E75" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F75" s="112" t="e">
+      <c r="F75" s="112">
         <f>C75/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G75" s="113" t="s">
         <v>84</v>
@@ -11908,7 +11908,7 @@
       <c r="S75" s="108"/>
       <c r="T75" s="108"/>
     </row>
-    <row r="76" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="151" t="s">
         <v>103</v>
       </c>
@@ -11944,7 +11944,7 @@
       <c r="S76" s="108"/>
       <c r="T76" s="108"/>
     </row>
-    <row r="77" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="242"/>
       <c r="B77" s="243"/>
       <c r="C77" s="244" t="s">
@@ -11970,7 +11970,7 @@
       <c r="S77" s="108"/>
       <c r="T77" s="108"/>
     </row>
-    <row r="78" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="245"/>
       <c r="B78" s="246"/>
       <c r="C78" s="247" t="s">
@@ -11993,7 +11993,7 @@
       <c r="Q78" s="108"/>
       <c r="R78" s="108"/>
     </row>
-    <row r="79" spans="1:20" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="K79" s="108"/>
       <c r="L79" s="108"/>
       <c r="M79" s="108"/>
@@ -12003,7 +12003,7 @@
       <c r="Q79" s="108"/>
       <c r="R79" s="108"/>
     </row>
-    <row r="80" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="139"/>
       <c r="B80" s="140"/>
       <c r="C80" s="140"/>
@@ -12023,7 +12023,7 @@
       <c r="Q80" s="108"/>
       <c r="R80" s="108"/>
     </row>
-    <row r="81" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="234" t="s">
         <v>105</v>
       </c>
@@ -12046,7 +12046,7 @@
       <c r="Q81" s="108"/>
       <c r="R81" s="108"/>
     </row>
-    <row r="82" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="123" t="s">
         <v>100</v>
       </c>
@@ -12063,9 +12063,9 @@
       <c r="E82" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="F82" s="127" t="e">
+      <c r="F82" s="127">
         <f>SQRT((F83*F83)+(F84*F84)+(F85*F85))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G82" s="126" t="e">
         <f>+ABS((B86-B90)/POWER((B86-B90+B82),2))</f>
@@ -12087,7 +12087,7 @@
       <c r="Q82" s="108"/>
       <c r="R82" s="108"/>
     </row>
-    <row r="83" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="109" t="s">
         <v>85</v>
       </c>
@@ -12122,7 +12122,7 @@
       <c r="Q83" s="108"/>
       <c r="R83" s="108"/>
     </row>
-    <row r="84" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="109" t="s">
         <v>87</v>
       </c>
@@ -12148,10 +12148,10 @@
         <v>84</v>
       </c>
       <c r="I84" s="108"/>
-      <c r="J84" s="438" t="s">
+      <c r="J84" s="435" t="s">
         <v>89</v>
       </c>
-      <c r="K84" s="439"/>
+      <c r="K84" s="436"/>
       <c r="L84" s="102" t="s">
         <v>76</v>
       </c>
@@ -12164,7 +12164,7 @@
       <c r="Q84" s="108"/>
       <c r="R84" s="108"/>
     </row>
-    <row r="85" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="109" t="s">
         <v>91</v>
       </c>
@@ -12179,9 +12179,9 @@
       <c r="E85" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F85" s="112" t="e">
+      <c r="F85" s="112">
         <f>C85/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G85" s="113" t="s">
         <v>84</v>
@@ -12208,7 +12208,7 @@
       <c r="Q85" s="108"/>
       <c r="R85" s="108"/>
     </row>
-    <row r="86" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="123" t="s">
         <v>101</v>
       </c>
@@ -12223,9 +12223,9 @@
       <c r="E86" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F86" s="127" t="e">
+      <c r="F86" s="127">
         <f>SQRT((F87*F87)+(F88*F88)+(F89*F89))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G86" s="125" t="e">
         <f>+B82/POWER((B86+B82-B90),2)</f>
@@ -12256,7 +12256,7 @@
       <c r="Q86" s="108"/>
       <c r="R86" s="108"/>
     </row>
-    <row r="87" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="109" t="s">
         <v>85</v>
       </c>
@@ -12300,7 +12300,7 @@
       <c r="Q87" s="108"/>
       <c r="R87" s="108"/>
     </row>
-    <row r="88" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="109" t="s">
         <v>87</v>
       </c>
@@ -12344,7 +12344,7 @@
       <c r="Q88" s="108"/>
       <c r="R88" s="108"/>
     </row>
-    <row r="89" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="109" t="s">
         <v>91</v>
       </c>
@@ -12359,9 +12359,9 @@
       <c r="E89" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F89" s="112" t="e">
+      <c r="F89" s="112">
         <f>C89/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G89" s="113" t="s">
         <v>84</v>
@@ -12385,7 +12385,7 @@
       <c r="Q89" s="108"/>
       <c r="R89" s="108"/>
     </row>
-    <row r="90" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="123" t="s">
         <v>102</v>
       </c>
@@ -12400,9 +12400,9 @@
       <c r="E90" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F90" s="127" t="e">
+      <c r="F90" s="127">
         <f>SQRT((F91*F91)+(F92*F92)+(F93*F93))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G90" s="131" t="e">
         <f>+B82/POWER((B86+B82-B90),2)</f>
@@ -12424,7 +12424,7 @@
       <c r="Q90" s="108"/>
       <c r="R90" s="108"/>
     </row>
-    <row r="91" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="109" t="s">
         <v>85</v>
       </c>
@@ -12459,7 +12459,7 @@
       <c r="Q91" s="108"/>
       <c r="R91" s="108"/>
     </row>
-    <row r="92" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="109" t="s">
         <v>87</v>
       </c>
@@ -12494,7 +12494,7 @@
       <c r="Q92" s="108"/>
       <c r="R92" s="108"/>
     </row>
-    <row r="93" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="109" t="s">
         <v>91</v>
       </c>
@@ -12509,9 +12509,9 @@
       <c r="E93" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F93" s="112" t="e">
+      <c r="F93" s="112">
         <f>C93/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G93" s="113" t="s">
         <v>84</v>
@@ -12529,7 +12529,7 @@
       <c r="Q93" s="108"/>
       <c r="R93" s="108"/>
     </row>
-    <row r="94" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="151" t="s">
         <v>106</v>
       </c>
@@ -12561,7 +12561,7 @@
       <c r="Q94" s="108"/>
       <c r="R94" s="108"/>
     </row>
-    <row r="95" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="242"/>
       <c r="B95" s="243"/>
       <c r="C95" s="244" t="s">
@@ -12583,7 +12583,7 @@
       <c r="Q95" s="108"/>
       <c r="R95" s="108"/>
     </row>
-    <row r="96" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="245"/>
       <c r="B96" s="246"/>
       <c r="C96" s="247" t="s">
@@ -12604,7 +12604,7 @@
       <c r="Q96" s="108"/>
       <c r="R96" s="108"/>
     </row>
-    <row r="97" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="K97" s="108"/>
       <c r="N97" s="108"/>
       <c r="O97" s="108"/>
@@ -12612,7 +12612,7 @@
       <c r="Q97" s="108"/>
       <c r="R97" s="108"/>
     </row>
-    <row r="98" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="139"/>
       <c r="B98" s="140"/>
       <c r="C98" s="140"/>
@@ -12630,7 +12630,7 @@
       <c r="Q98" s="108"/>
       <c r="R98" s="108"/>
     </row>
-    <row r="99" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="234" t="s">
         <v>109</v>
       </c>
@@ -12644,10 +12644,10 @@
       <c r="F99" s="148"/>
       <c r="G99" s="149"/>
       <c r="H99" s="150"/>
-      <c r="J99" s="438" t="s">
+      <c r="J99" s="435" t="s">
         <v>89</v>
       </c>
-      <c r="K99" s="439"/>
+      <c r="K99" s="436"/>
       <c r="L99" s="102" t="s">
         <v>76</v>
       </c>
@@ -12660,7 +12660,7 @@
       <c r="Q99" s="108"/>
       <c r="R99" s="108"/>
     </row>
-    <row r="100" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="123" t="s">
         <v>99</v>
       </c>
@@ -12675,9 +12675,9 @@
       <c r="E100" s="124" t="s">
         <v>84</v>
       </c>
-      <c r="F100" s="127" t="e">
+      <c r="F100" s="127">
         <f>SQRT((F101*F101)+(F102*F102)+(F103*F103))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G100" s="131" t="e">
         <f>100/B104</f>
@@ -12708,7 +12708,7 @@
       <c r="Q100" s="108"/>
       <c r="R100" s="108"/>
     </row>
-    <row r="101" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="109" t="s">
         <v>85</v>
       </c>
@@ -12752,7 +12752,7 @@
       <c r="Q101" s="108"/>
       <c r="R101" s="108"/>
     </row>
-    <row r="102" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="109" t="s">
         <v>87</v>
       </c>
@@ -12796,7 +12796,7 @@
       <c r="Q102" s="108"/>
       <c r="R102" s="108"/>
     </row>
-    <row r="103" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="109" t="s">
         <v>91</v>
       </c>
@@ -12811,9 +12811,9 @@
       <c r="E103" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F103" s="112" t="e">
+      <c r="F103" s="112">
         <f>C103/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G103" s="113" t="s">
         <v>84</v>
@@ -12836,7 +12836,7 @@
       <c r="Q103" s="108"/>
       <c r="R103" s="108"/>
     </row>
-    <row r="104" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="123" t="s">
         <v>100</v>
       </c>
@@ -12853,9 +12853,9 @@
       <c r="E104" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="F104" s="127" t="e">
+      <c r="F104" s="127">
         <f>SQRT((F105*F105)+(F106*F106)+(F107*F107))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G104" s="126" t="e">
         <f>100*B100/B104/B104</f>
@@ -12877,7 +12877,7 @@
       <c r="Q104" s="108"/>
       <c r="R104" s="108"/>
     </row>
-    <row r="105" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="109" t="s">
         <v>85</v>
       </c>
@@ -12911,7 +12911,7 @@
       <c r="Q105" s="108"/>
       <c r="R105" s="108"/>
     </row>
-    <row r="106" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="109" t="s">
         <v>87</v>
       </c>
@@ -12944,7 +12944,7 @@
       <c r="Q106" s="108"/>
       <c r="R106" s="108"/>
     </row>
-    <row r="107" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="109" t="s">
         <v>91</v>
       </c>
@@ -12959,9 +12959,9 @@
       <c r="E107" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F107" s="112" t="e">
+      <c r="F107" s="112">
         <f>C107/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G107" s="113" t="s">
         <v>84</v>
@@ -12977,7 +12977,7 @@
       <c r="Q107" s="108"/>
       <c r="R107" s="108"/>
     </row>
-    <row r="108" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="151" t="s">
         <v>110</v>
       </c>
@@ -13008,7 +13008,7 @@
       <c r="Q108" s="108"/>
       <c r="R108" s="108"/>
     </row>
-    <row r="109" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="242"/>
       <c r="B109" s="243"/>
       <c r="C109" s="244" t="s">
@@ -13029,7 +13029,7 @@
       <c r="Q109" s="108"/>
       <c r="R109" s="108"/>
     </row>
-    <row r="110" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="245"/>
       <c r="B110" s="246"/>
       <c r="C110" s="247" t="s">
@@ -13050,7 +13050,7 @@
       <c r="Q110" s="108"/>
       <c r="R110" s="108"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.2">
       <c r="K111" s="108"/>
       <c r="N111" s="108"/>
       <c r="O111" s="108"/>
@@ -13058,7 +13058,7 @@
       <c r="Q111" s="108"/>
       <c r="R111" s="108"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="K112" s="108"/>
       <c r="N112" s="108"/>
       <c r="O112" s="108"/>
@@ -13066,23 +13066,23 @@
       <c r="Q112" s="108"/>
       <c r="R112" s="108"/>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A113" s="377" t="s">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A113" s="374" t="s">
+        <v>212</v>
+      </c>
+      <c r="B113" s="443" t="s">
         <v>213</v>
       </c>
-      <c r="B113" s="446" t="s">
+      <c r="C113" s="444"/>
+      <c r="D113" s="375"/>
+      <c r="E113" s="445" t="s">
         <v>214</v>
       </c>
-      <c r="C113" s="447"/>
-      <c r="D113" s="378"/>
-      <c r="E113" s="448" t="s">
+      <c r="F113" s="445"/>
+      <c r="G113" s="446" t="s">
         <v>215</v>
       </c>
-      <c r="F113" s="448"/>
-      <c r="G113" s="449" t="s">
-        <v>216</v>
-      </c>
-      <c r="H113" s="450"/>
+      <c r="H113" s="447"/>
       <c r="K113" s="108"/>
       <c r="N113" s="108"/>
       <c r="O113" s="108"/>
@@ -13090,7 +13090,7 @@
       <c r="Q113" s="108"/>
       <c r="R113" s="108"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.2">
       <c r="K114" s="108"/>
       <c r="L114" s="108"/>
       <c r="M114" s="108"/>
@@ -13100,22 +13100,22 @@
       <c r="Q114" s="108"/>
       <c r="R114" s="108"/>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A115" s="379" t="s">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A115" s="376" t="s">
+        <v>216</v>
+      </c>
+      <c r="B115" s="448">
+        <v>44869</v>
+      </c>
+      <c r="C115" s="449"/>
+      <c r="E115" s="450" t="s">
         <v>217</v>
       </c>
-      <c r="B115" s="451">
-        <v>44869</v>
-      </c>
-      <c r="C115" s="452"/>
-      <c r="E115" s="453" t="s">
-        <v>218</v>
-      </c>
-      <c r="F115" s="453"/>
-      <c r="G115" s="451">
+      <c r="F115" s="450"/>
+      <c r="G115" s="448">
         <v>44870</v>
       </c>
-      <c r="H115" s="452"/>
+      <c r="H115" s="449"/>
       <c r="K115" s="108"/>
       <c r="L115" s="108"/>
       <c r="M115" s="108"/>
@@ -13165,217 +13165,217 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B6:I30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="168" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="168"/>
-    <col min="3" max="3" width="11.44140625" style="168" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="168" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="168"/>
+    <col min="3" max="3" width="11.42578125" style="168" customWidth="1"/>
     <col min="4" max="4" width="12" style="168" customWidth="1"/>
-    <col min="5" max="7" width="11.44140625" style="168"/>
-    <col min="8" max="8" width="14.44140625" style="168" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="168"/>
-    <col min="10" max="10" width="11.88671875" style="168" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="168"/>
+    <col min="5" max="7" width="11.42578125" style="168"/>
+    <col min="8" max="8" width="14.42578125" style="168" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="168"/>
+    <col min="10" max="10" width="11.85546875" style="168" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="168"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6" s="261" t="s">
         <v>112</v>
       </c>
       <c r="C6" s="252"/>
       <c r="D6" s="252"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="263">
-        <v>-2.4000000000000001E-5</v>
-      </c>
-      <c r="D7" s="264"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="463">
+        <v>-2.4600000000000002E-5</v>
+      </c>
+      <c r="D7" s="263"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="264">
+      <c r="C8" s="263">
         <v>1.81E-3</v>
       </c>
-      <c r="D8" s="264">
-        <v>8.1800000000000004E-11</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D8" s="263">
+        <v>2.1500000000000001E-10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="103" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="265" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="264"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="464" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="263"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="266" t="s">
+      <c r="C10" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="264"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D10" s="263"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="264" t="s">
+      <c r="C11" s="263" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="264"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="263"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="103" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="303">
-        <v>45799</v>
-      </c>
-      <c r="D12" s="264"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="C12" s="465">
+        <v>46160</v>
+      </c>
+      <c r="D12" s="263"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="103"/>
       <c r="C13" s="262"/>
     </row>
-    <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="269" t="s">
+    <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="267" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="268" t="s">
+      <c r="C14" s="266" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="269">
+      <c r="D14" s="267">
         <v>20</v>
       </c>
-      <c r="E14" s="269">
+      <c r="E14" s="267">
         <v>200</v>
       </c>
-      <c r="F14" s="269">
+      <c r="F14" s="267">
         <v>500</v>
       </c>
-      <c r="G14" s="269">
+      <c r="G14" s="267">
         <v>1000</v>
       </c>
-      <c r="H14" s="269">
+      <c r="H14" s="267">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="268"/>
-      <c r="C15" s="270"/>
-      <c r="D15" s="271"/>
-      <c r="E15" s="271"/>
-      <c r="F15" s="271"/>
-      <c r="G15" s="271"/>
-      <c r="H15" s="271"/>
-    </row>
-    <row r="16" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="268"/>
-      <c r="C16" s="270"/>
-      <c r="D16" s="271"/>
-      <c r="E16" s="271"/>
-      <c r="F16" s="271"/>
-      <c r="G16" s="271"/>
-      <c r="H16" s="271"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="264"/>
-      <c r="C17" s="264"/>
-      <c r="D17" s="264"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="292"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="272"/>
-      <c r="C18" s="267" t="s">
+    <row r="15" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="266"/>
+      <c r="C15" s="268"/>
+      <c r="D15" s="269"/>
+      <c r="E15" s="269"/>
+      <c r="F15" s="269"/>
+      <c r="G15" s="269"/>
+      <c r="H15" s="269"/>
+    </row>
+    <row r="16" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="266"/>
+      <c r="C16" s="268"/>
+      <c r="D16" s="269"/>
+      <c r="E16" s="269"/>
+      <c r="F16" s="269"/>
+      <c r="G16" s="269"/>
+      <c r="H16" s="269"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="263"/>
+      <c r="C17" s="263"/>
+      <c r="D17" s="263"/>
+      <c r="E17" s="263"/>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="290"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="270"/>
+      <c r="C18" s="265" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="273">
+      <c r="D18" s="271">
         <v>0</v>
       </c>
-      <c r="E18" s="273">
+      <c r="E18" s="271">
         <v>0</v>
       </c>
-      <c r="F18" s="273">
+      <c r="F18" s="271">
         <v>0</v>
       </c>
-      <c r="G18" s="273">
+      <c r="G18" s="271">
         <v>0</v>
       </c>
-      <c r="H18" s="273">
+      <c r="H18" s="271">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="D20" s="237" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="269">
+    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D22" s="267">
         <v>20</v>
       </c>
-      <c r="E22" s="269">
+      <c r="E22" s="267">
         <v>200</v>
       </c>
-      <c r="F22" s="269">
+      <c r="F22" s="267">
         <v>500</v>
       </c>
-      <c r="G22" s="269">
+      <c r="G22" s="267">
         <v>1000</v>
       </c>
-      <c r="H22" s="269">
+      <c r="H22" s="267">
         <v>5000</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D23" s="273">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="D23" s="271">
         <f>D18</f>
         <v>0</v>
       </c>
-      <c r="E23" s="273">
+      <c r="E23" s="271">
         <f>E18</f>
         <v>0</v>
       </c>
-      <c r="F23" s="273">
+      <c r="F23" s="271">
         <f>F18</f>
         <v>0</v>
       </c>
-      <c r="G23" s="273">
+      <c r="G23" s="271">
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="H23" s="273">
+      <c r="H23" s="271">
         <f>H18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G24" s="103"/>
       <c r="H24" s="103"/>
       <c r="I24" s="103"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C25" s="274"/>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C25" s="272"/>
       <c r="D25" s="161"/>
-      <c r="E25" s="275" t="s">
+      <c r="E25" s="273" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="276">
+      <c r="F25" s="274">
         <f>+'DATOS ENSAYO'!K19</f>
         <v>0</v>
       </c>
-      <c r="G25" s="273">
+      <c r="G25" s="271">
         <f>IF(F25&lt;=$D$22,$D$23,IF(AND(F25&gt;$D$22,F25&lt;=$E$22),$E$23,IF(AND(F25&gt;$E$22,F25&lt;=$F$22),$F$23,IF(AND(F25&gt;$F$22,F25&lt;=$G$22),$G$23,IF(AND(F25&gt;$G$22,F25&lt;=$H$22),$H$23,$H$23)))))</f>
         <v>0</v>
       </c>
@@ -13383,17 +13383,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C26" s="277"/>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C26" s="275"/>
       <c r="D26" s="162"/>
-      <c r="E26" s="278" t="s">
+      <c r="E26" s="276" t="s">
         <v>101</v>
       </c>
-      <c r="F26" s="279">
+      <c r="F26" s="277">
         <f>+'DATOS ENSAYO'!K14</f>
         <v>0</v>
       </c>
-      <c r="G26" s="273">
+      <c r="G26" s="271">
         <f t="shared" ref="G26:G28" si="0">IF(F26&lt;=$D$22,$D$23,IF(AND(F26&gt;$D$22,F26&lt;=$E$22),$E$23,IF(AND(F26&gt;$E$22,F26&lt;=$F$22),$F$23,IF(AND(F26&gt;$F$22,F26&lt;=$G$22),$G$23,IF(AND(F26&gt;$G$22,F26&lt;=$H$22),$H$23,$H$23)))))</f>
         <v>0</v>
       </c>
@@ -13401,17 +13401,17 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C27" s="274"/>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C27" s="272"/>
       <c r="D27" s="164"/>
-      <c r="E27" s="275" t="s">
+      <c r="E27" s="273" t="s">
         <v>102</v>
       </c>
-      <c r="F27" s="276">
+      <c r="F27" s="274">
         <f>+'DATOS ENSAYO'!K13</f>
         <v>0</v>
       </c>
-      <c r="G27" s="273">
+      <c r="G27" s="271">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -13419,17 +13419,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C28" s="280"/>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C28" s="278"/>
       <c r="D28" s="163"/>
-      <c r="E28" s="281" t="s">
+      <c r="E28" s="279" t="s">
         <v>99</v>
       </c>
-      <c r="F28" s="282">
+      <c r="F28" s="280">
         <f>+'DATOS ENSAYO'!K12</f>
         <v>0</v>
       </c>
-      <c r="G28" s="273">
+      <c r="G28" s="271">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -13437,17 +13437,16 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E29" s="283"/>
-      <c r="F29" s="283"/>
-      <c r="G29" s="283"/>
-      <c r="H29" s="283"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D30" s="284"/>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E29" s="281"/>
+      <c r="F29" s="281"/>
+      <c r="G29" s="281"/>
+      <c r="H29" s="281"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="D30" s="282"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="f0ciYwvxe7UHHRXKEjtrp/LoYgPmrOM+rv7ht5t8sHmUm46brISaapGOOvEXfrFksoTcv1V5WbbSrtJUibYYww==" saltValue="i06vstC4ZGS1dxneJcaTdg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -13457,1165 +13456,1165 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Y37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="214" customWidth="1"/>
-    <col min="2" max="4" width="11.88671875" style="214" customWidth="1"/>
-    <col min="5" max="5" width="1.88671875" style="214" customWidth="1"/>
-    <col min="6" max="6" width="30.5546875" style="214" customWidth="1"/>
-    <col min="7" max="9" width="11.88671875" style="214" customWidth="1"/>
-    <col min="10" max="10" width="1.33203125" style="214" customWidth="1"/>
-    <col min="11" max="11" width="29.88671875" style="214" customWidth="1"/>
-    <col min="12" max="14" width="11.88671875" style="214" customWidth="1"/>
-    <col min="15" max="15" width="2.109375" style="214" customWidth="1"/>
-    <col min="16" max="16" width="29.88671875" style="214" customWidth="1"/>
-    <col min="17" max="19" width="11.88671875" style="214" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="214" customWidth="1"/>
+    <col min="2" max="4" width="11.85546875" style="214" customWidth="1"/>
+    <col min="5" max="5" width="1.85546875" style="214" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" style="214" customWidth="1"/>
+    <col min="7" max="9" width="11.85546875" style="214" customWidth="1"/>
+    <col min="10" max="10" width="1.28515625" style="214" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" style="214" customWidth="1"/>
+    <col min="12" max="14" width="11.85546875" style="214" customWidth="1"/>
+    <col min="15" max="15" width="2.140625" style="214" customWidth="1"/>
+    <col min="16" max="16" width="29.85546875" style="214" customWidth="1"/>
+    <col min="17" max="19" width="11.85546875" style="214" customWidth="1"/>
     <col min="20" max="20" width="5" style="214" customWidth="1"/>
-    <col min="21" max="21" width="16.5546875" style="214" customWidth="1"/>
-    <col min="22" max="250" width="11.44140625" style="214"/>
+    <col min="21" max="21" width="16.5703125" style="214" customWidth="1"/>
+    <col min="22" max="250" width="11.42578125" style="214"/>
     <col min="251" max="252" width="20" style="214" customWidth="1"/>
-    <col min="253" max="253" width="11.44140625" style="214"/>
-    <col min="254" max="255" width="6.109375" style="214" customWidth="1"/>
+    <col min="253" max="253" width="11.42578125" style="214"/>
+    <col min="254" max="255" width="6.140625" style="214" customWidth="1"/>
     <col min="256" max="256" width="14" style="214" customWidth="1"/>
-    <col min="257" max="257" width="4.44140625" style="214" customWidth="1"/>
-    <col min="258" max="258" width="20.88671875" style="214" customWidth="1"/>
-    <col min="259" max="260" width="11.44140625" style="214"/>
-    <col min="261" max="262" width="4.109375" style="214" customWidth="1"/>
-    <col min="263" max="263" width="11.44140625" style="214"/>
-    <col min="264" max="264" width="19.109375" style="214" customWidth="1"/>
-    <col min="265" max="266" width="11.44140625" style="214"/>
-    <col min="267" max="268" width="4.88671875" style="214" customWidth="1"/>
-    <col min="269" max="269" width="10.88671875" style="214" customWidth="1"/>
-    <col min="270" max="270" width="11.44140625" style="214"/>
+    <col min="257" max="257" width="4.42578125" style="214" customWidth="1"/>
+    <col min="258" max="258" width="20.85546875" style="214" customWidth="1"/>
+    <col min="259" max="260" width="11.42578125" style="214"/>
+    <col min="261" max="262" width="4.140625" style="214" customWidth="1"/>
+    <col min="263" max="263" width="11.42578125" style="214"/>
+    <col min="264" max="264" width="19.140625" style="214" customWidth="1"/>
+    <col min="265" max="266" width="11.42578125" style="214"/>
+    <col min="267" max="268" width="4.85546875" style="214" customWidth="1"/>
+    <col min="269" max="269" width="10.85546875" style="214" customWidth="1"/>
+    <col min="270" max="270" width="11.42578125" style="214"/>
     <col min="271" max="271" width="22" style="214" customWidth="1"/>
-    <col min="272" max="273" width="11.44140625" style="214"/>
+    <col min="272" max="273" width="11.42578125" style="214"/>
     <col min="274" max="275" width="6" style="214" customWidth="1"/>
-    <col min="276" max="506" width="11.44140625" style="214"/>
+    <col min="276" max="506" width="11.42578125" style="214"/>
     <col min="507" max="508" width="20" style="214" customWidth="1"/>
-    <col min="509" max="509" width="11.44140625" style="214"/>
-    <col min="510" max="511" width="6.109375" style="214" customWidth="1"/>
+    <col min="509" max="509" width="11.42578125" style="214"/>
+    <col min="510" max="511" width="6.140625" style="214" customWidth="1"/>
     <col min="512" max="512" width="14" style="214" customWidth="1"/>
-    <col min="513" max="513" width="4.44140625" style="214" customWidth="1"/>
-    <col min="514" max="514" width="20.88671875" style="214" customWidth="1"/>
-    <col min="515" max="516" width="11.44140625" style="214"/>
-    <col min="517" max="518" width="4.109375" style="214" customWidth="1"/>
-    <col min="519" max="519" width="11.44140625" style="214"/>
-    <col min="520" max="520" width="19.109375" style="214" customWidth="1"/>
-    <col min="521" max="522" width="11.44140625" style="214"/>
-    <col min="523" max="524" width="4.88671875" style="214" customWidth="1"/>
-    <col min="525" max="525" width="10.88671875" style="214" customWidth="1"/>
-    <col min="526" max="526" width="11.44140625" style="214"/>
+    <col min="513" max="513" width="4.42578125" style="214" customWidth="1"/>
+    <col min="514" max="514" width="20.85546875" style="214" customWidth="1"/>
+    <col min="515" max="516" width="11.42578125" style="214"/>
+    <col min="517" max="518" width="4.140625" style="214" customWidth="1"/>
+    <col min="519" max="519" width="11.42578125" style="214"/>
+    <col min="520" max="520" width="19.140625" style="214" customWidth="1"/>
+    <col min="521" max="522" width="11.42578125" style="214"/>
+    <col min="523" max="524" width="4.85546875" style="214" customWidth="1"/>
+    <col min="525" max="525" width="10.85546875" style="214" customWidth="1"/>
+    <col min="526" max="526" width="11.42578125" style="214"/>
     <col min="527" max="527" width="22" style="214" customWidth="1"/>
-    <col min="528" max="529" width="11.44140625" style="214"/>
+    <col min="528" max="529" width="11.42578125" style="214"/>
     <col min="530" max="531" width="6" style="214" customWidth="1"/>
-    <col min="532" max="762" width="11.44140625" style="214"/>
+    <col min="532" max="762" width="11.42578125" style="214"/>
     <col min="763" max="764" width="20" style="214" customWidth="1"/>
-    <col min="765" max="765" width="11.44140625" style="214"/>
-    <col min="766" max="767" width="6.109375" style="214" customWidth="1"/>
+    <col min="765" max="765" width="11.42578125" style="214"/>
+    <col min="766" max="767" width="6.140625" style="214" customWidth="1"/>
     <col min="768" max="768" width="14" style="214" customWidth="1"/>
-    <col min="769" max="769" width="4.44140625" style="214" customWidth="1"/>
-    <col min="770" max="770" width="20.88671875" style="214" customWidth="1"/>
-    <col min="771" max="772" width="11.44140625" style="214"/>
-    <col min="773" max="774" width="4.109375" style="214" customWidth="1"/>
-    <col min="775" max="775" width="11.44140625" style="214"/>
-    <col min="776" max="776" width="19.109375" style="214" customWidth="1"/>
-    <col min="777" max="778" width="11.44140625" style="214"/>
-    <col min="779" max="780" width="4.88671875" style="214" customWidth="1"/>
-    <col min="781" max="781" width="10.88671875" style="214" customWidth="1"/>
-    <col min="782" max="782" width="11.44140625" style="214"/>
+    <col min="769" max="769" width="4.42578125" style="214" customWidth="1"/>
+    <col min="770" max="770" width="20.85546875" style="214" customWidth="1"/>
+    <col min="771" max="772" width="11.42578125" style="214"/>
+    <col min="773" max="774" width="4.140625" style="214" customWidth="1"/>
+    <col min="775" max="775" width="11.42578125" style="214"/>
+    <col min="776" max="776" width="19.140625" style="214" customWidth="1"/>
+    <col min="777" max="778" width="11.42578125" style="214"/>
+    <col min="779" max="780" width="4.85546875" style="214" customWidth="1"/>
+    <col min="781" max="781" width="10.85546875" style="214" customWidth="1"/>
+    <col min="782" max="782" width="11.42578125" style="214"/>
     <col min="783" max="783" width="22" style="214" customWidth="1"/>
-    <col min="784" max="785" width="11.44140625" style="214"/>
+    <col min="784" max="785" width="11.42578125" style="214"/>
     <col min="786" max="787" width="6" style="214" customWidth="1"/>
-    <col min="788" max="1018" width="11.44140625" style="214"/>
+    <col min="788" max="1018" width="11.42578125" style="214"/>
     <col min="1019" max="1020" width="20" style="214" customWidth="1"/>
-    <col min="1021" max="1021" width="11.44140625" style="214"/>
-    <col min="1022" max="1023" width="6.109375" style="214" customWidth="1"/>
+    <col min="1021" max="1021" width="11.42578125" style="214"/>
+    <col min="1022" max="1023" width="6.140625" style="214" customWidth="1"/>
     <col min="1024" max="1024" width="14" style="214" customWidth="1"/>
-    <col min="1025" max="1025" width="4.44140625" style="214" customWidth="1"/>
-    <col min="1026" max="1026" width="20.88671875" style="214" customWidth="1"/>
-    <col min="1027" max="1028" width="11.44140625" style="214"/>
-    <col min="1029" max="1030" width="4.109375" style="214" customWidth="1"/>
-    <col min="1031" max="1031" width="11.44140625" style="214"/>
-    <col min="1032" max="1032" width="19.109375" style="214" customWidth="1"/>
-    <col min="1033" max="1034" width="11.44140625" style="214"/>
-    <col min="1035" max="1036" width="4.88671875" style="214" customWidth="1"/>
-    <col min="1037" max="1037" width="10.88671875" style="214" customWidth="1"/>
-    <col min="1038" max="1038" width="11.44140625" style="214"/>
+    <col min="1025" max="1025" width="4.42578125" style="214" customWidth="1"/>
+    <col min="1026" max="1026" width="20.85546875" style="214" customWidth="1"/>
+    <col min="1027" max="1028" width="11.42578125" style="214"/>
+    <col min="1029" max="1030" width="4.140625" style="214" customWidth="1"/>
+    <col min="1031" max="1031" width="11.42578125" style="214"/>
+    <col min="1032" max="1032" width="19.140625" style="214" customWidth="1"/>
+    <col min="1033" max="1034" width="11.42578125" style="214"/>
+    <col min="1035" max="1036" width="4.85546875" style="214" customWidth="1"/>
+    <col min="1037" max="1037" width="10.85546875" style="214" customWidth="1"/>
+    <col min="1038" max="1038" width="11.42578125" style="214"/>
     <col min="1039" max="1039" width="22" style="214" customWidth="1"/>
-    <col min="1040" max="1041" width="11.44140625" style="214"/>
+    <col min="1040" max="1041" width="11.42578125" style="214"/>
     <col min="1042" max="1043" width="6" style="214" customWidth="1"/>
-    <col min="1044" max="1274" width="11.44140625" style="214"/>
+    <col min="1044" max="1274" width="11.42578125" style="214"/>
     <col min="1275" max="1276" width="20" style="214" customWidth="1"/>
-    <col min="1277" max="1277" width="11.44140625" style="214"/>
-    <col min="1278" max="1279" width="6.109375" style="214" customWidth="1"/>
+    <col min="1277" max="1277" width="11.42578125" style="214"/>
+    <col min="1278" max="1279" width="6.140625" style="214" customWidth="1"/>
     <col min="1280" max="1280" width="14" style="214" customWidth="1"/>
-    <col min="1281" max="1281" width="4.44140625" style="214" customWidth="1"/>
-    <col min="1282" max="1282" width="20.88671875" style="214" customWidth="1"/>
-    <col min="1283" max="1284" width="11.44140625" style="214"/>
-    <col min="1285" max="1286" width="4.109375" style="214" customWidth="1"/>
-    <col min="1287" max="1287" width="11.44140625" style="214"/>
-    <col min="1288" max="1288" width="19.109375" style="214" customWidth="1"/>
-    <col min="1289" max="1290" width="11.44140625" style="214"/>
-    <col min="1291" max="1292" width="4.88671875" style="214" customWidth="1"/>
-    <col min="1293" max="1293" width="10.88671875" style="214" customWidth="1"/>
-    <col min="1294" max="1294" width="11.44140625" style="214"/>
+    <col min="1281" max="1281" width="4.42578125" style="214" customWidth="1"/>
+    <col min="1282" max="1282" width="20.85546875" style="214" customWidth="1"/>
+    <col min="1283" max="1284" width="11.42578125" style="214"/>
+    <col min="1285" max="1286" width="4.140625" style="214" customWidth="1"/>
+    <col min="1287" max="1287" width="11.42578125" style="214"/>
+    <col min="1288" max="1288" width="19.140625" style="214" customWidth="1"/>
+    <col min="1289" max="1290" width="11.42578125" style="214"/>
+    <col min="1291" max="1292" width="4.85546875" style="214" customWidth="1"/>
+    <col min="1293" max="1293" width="10.85546875" style="214" customWidth="1"/>
+    <col min="1294" max="1294" width="11.42578125" style="214"/>
     <col min="1295" max="1295" width="22" style="214" customWidth="1"/>
-    <col min="1296" max="1297" width="11.44140625" style="214"/>
+    <col min="1296" max="1297" width="11.42578125" style="214"/>
     <col min="1298" max="1299" width="6" style="214" customWidth="1"/>
-    <col min="1300" max="1530" width="11.44140625" style="214"/>
+    <col min="1300" max="1530" width="11.42578125" style="214"/>
     <col min="1531" max="1532" width="20" style="214" customWidth="1"/>
-    <col min="1533" max="1533" width="11.44140625" style="214"/>
-    <col min="1534" max="1535" width="6.109375" style="214" customWidth="1"/>
+    <col min="1533" max="1533" width="11.42578125" style="214"/>
+    <col min="1534" max="1535" width="6.140625" style="214" customWidth="1"/>
     <col min="1536" max="1536" width="14" style="214" customWidth="1"/>
-    <col min="1537" max="1537" width="4.44140625" style="214" customWidth="1"/>
-    <col min="1538" max="1538" width="20.88671875" style="214" customWidth="1"/>
-    <col min="1539" max="1540" width="11.44140625" style="214"/>
-    <col min="1541" max="1542" width="4.109375" style="214" customWidth="1"/>
-    <col min="1543" max="1543" width="11.44140625" style="214"/>
-    <col min="1544" max="1544" width="19.109375" style="214" customWidth="1"/>
-    <col min="1545" max="1546" width="11.44140625" style="214"/>
-    <col min="1547" max="1548" width="4.88671875" style="214" customWidth="1"/>
-    <col min="1549" max="1549" width="10.88671875" style="214" customWidth="1"/>
-    <col min="1550" max="1550" width="11.44140625" style="214"/>
+    <col min="1537" max="1537" width="4.42578125" style="214" customWidth="1"/>
+    <col min="1538" max="1538" width="20.85546875" style="214" customWidth="1"/>
+    <col min="1539" max="1540" width="11.42578125" style="214"/>
+    <col min="1541" max="1542" width="4.140625" style="214" customWidth="1"/>
+    <col min="1543" max="1543" width="11.42578125" style="214"/>
+    <col min="1544" max="1544" width="19.140625" style="214" customWidth="1"/>
+    <col min="1545" max="1546" width="11.42578125" style="214"/>
+    <col min="1547" max="1548" width="4.85546875" style="214" customWidth="1"/>
+    <col min="1549" max="1549" width="10.85546875" style="214" customWidth="1"/>
+    <col min="1550" max="1550" width="11.42578125" style="214"/>
     <col min="1551" max="1551" width="22" style="214" customWidth="1"/>
-    <col min="1552" max="1553" width="11.44140625" style="214"/>
+    <col min="1552" max="1553" width="11.42578125" style="214"/>
     <col min="1554" max="1555" width="6" style="214" customWidth="1"/>
-    <col min="1556" max="1786" width="11.44140625" style="214"/>
+    <col min="1556" max="1786" width="11.42578125" style="214"/>
     <col min="1787" max="1788" width="20" style="214" customWidth="1"/>
-    <col min="1789" max="1789" width="11.44140625" style="214"/>
-    <col min="1790" max="1791" width="6.109375" style="214" customWidth="1"/>
+    <col min="1789" max="1789" width="11.42578125" style="214"/>
+    <col min="1790" max="1791" width="6.140625" style="214" customWidth="1"/>
     <col min="1792" max="1792" width="14" style="214" customWidth="1"/>
-    <col min="1793" max="1793" width="4.44140625" style="214" customWidth="1"/>
-    <col min="1794" max="1794" width="20.88671875" style="214" customWidth="1"/>
-    <col min="1795" max="1796" width="11.44140625" style="214"/>
-    <col min="1797" max="1798" width="4.109375" style="214" customWidth="1"/>
-    <col min="1799" max="1799" width="11.44140625" style="214"/>
-    <col min="1800" max="1800" width="19.109375" style="214" customWidth="1"/>
-    <col min="1801" max="1802" width="11.44140625" style="214"/>
-    <col min="1803" max="1804" width="4.88671875" style="214" customWidth="1"/>
-    <col min="1805" max="1805" width="10.88671875" style="214" customWidth="1"/>
-    <col min="1806" max="1806" width="11.44140625" style="214"/>
+    <col min="1793" max="1793" width="4.42578125" style="214" customWidth="1"/>
+    <col min="1794" max="1794" width="20.85546875" style="214" customWidth="1"/>
+    <col min="1795" max="1796" width="11.42578125" style="214"/>
+    <col min="1797" max="1798" width="4.140625" style="214" customWidth="1"/>
+    <col min="1799" max="1799" width="11.42578125" style="214"/>
+    <col min="1800" max="1800" width="19.140625" style="214" customWidth="1"/>
+    <col min="1801" max="1802" width="11.42578125" style="214"/>
+    <col min="1803" max="1804" width="4.85546875" style="214" customWidth="1"/>
+    <col min="1805" max="1805" width="10.85546875" style="214" customWidth="1"/>
+    <col min="1806" max="1806" width="11.42578125" style="214"/>
     <col min="1807" max="1807" width="22" style="214" customWidth="1"/>
-    <col min="1808" max="1809" width="11.44140625" style="214"/>
+    <col min="1808" max="1809" width="11.42578125" style="214"/>
     <col min="1810" max="1811" width="6" style="214" customWidth="1"/>
-    <col min="1812" max="2042" width="11.44140625" style="214"/>
+    <col min="1812" max="2042" width="11.42578125" style="214"/>
     <col min="2043" max="2044" width="20" style="214" customWidth="1"/>
-    <col min="2045" max="2045" width="11.44140625" style="214"/>
-    <col min="2046" max="2047" width="6.109375" style="214" customWidth="1"/>
+    <col min="2045" max="2045" width="11.42578125" style="214"/>
+    <col min="2046" max="2047" width="6.140625" style="214" customWidth="1"/>
     <col min="2048" max="2048" width="14" style="214" customWidth="1"/>
-    <col min="2049" max="2049" width="4.44140625" style="214" customWidth="1"/>
-    <col min="2050" max="2050" width="20.88671875" style="214" customWidth="1"/>
-    <col min="2051" max="2052" width="11.44140625" style="214"/>
-    <col min="2053" max="2054" width="4.109375" style="214" customWidth="1"/>
-    <col min="2055" max="2055" width="11.44140625" style="214"/>
-    <col min="2056" max="2056" width="19.109375" style="214" customWidth="1"/>
-    <col min="2057" max="2058" width="11.44140625" style="214"/>
-    <col min="2059" max="2060" width="4.88671875" style="214" customWidth="1"/>
-    <col min="2061" max="2061" width="10.88671875" style="214" customWidth="1"/>
-    <col min="2062" max="2062" width="11.44140625" style="214"/>
+    <col min="2049" max="2049" width="4.42578125" style="214" customWidth="1"/>
+    <col min="2050" max="2050" width="20.85546875" style="214" customWidth="1"/>
+    <col min="2051" max="2052" width="11.42578125" style="214"/>
+    <col min="2053" max="2054" width="4.140625" style="214" customWidth="1"/>
+    <col min="2055" max="2055" width="11.42578125" style="214"/>
+    <col min="2056" max="2056" width="19.140625" style="214" customWidth="1"/>
+    <col min="2057" max="2058" width="11.42578125" style="214"/>
+    <col min="2059" max="2060" width="4.85546875" style="214" customWidth="1"/>
+    <col min="2061" max="2061" width="10.85546875" style="214" customWidth="1"/>
+    <col min="2062" max="2062" width="11.42578125" style="214"/>
     <col min="2063" max="2063" width="22" style="214" customWidth="1"/>
-    <col min="2064" max="2065" width="11.44140625" style="214"/>
+    <col min="2064" max="2065" width="11.42578125" style="214"/>
     <col min="2066" max="2067" width="6" style="214" customWidth="1"/>
-    <col min="2068" max="2298" width="11.44140625" style="214"/>
+    <col min="2068" max="2298" width="11.42578125" style="214"/>
     <col min="2299" max="2300" width="20" style="214" customWidth="1"/>
-    <col min="2301" max="2301" width="11.44140625" style="214"/>
-    <col min="2302" max="2303" width="6.109375" style="214" customWidth="1"/>
+    <col min="2301" max="2301" width="11.42578125" style="214"/>
+    <col min="2302" max="2303" width="6.140625" style="214" customWidth="1"/>
     <col min="2304" max="2304" width="14" style="214" customWidth="1"/>
-    <col min="2305" max="2305" width="4.44140625" style="214" customWidth="1"/>
-    <col min="2306" max="2306" width="20.88671875" style="214" customWidth="1"/>
-    <col min="2307" max="2308" width="11.44140625" style="214"/>
-    <col min="2309" max="2310" width="4.109375" style="214" customWidth="1"/>
-    <col min="2311" max="2311" width="11.44140625" style="214"/>
-    <col min="2312" max="2312" width="19.109375" style="214" customWidth="1"/>
-    <col min="2313" max="2314" width="11.44140625" style="214"/>
-    <col min="2315" max="2316" width="4.88671875" style="214" customWidth="1"/>
-    <col min="2317" max="2317" width="10.88671875" style="214" customWidth="1"/>
-    <col min="2318" max="2318" width="11.44140625" style="214"/>
+    <col min="2305" max="2305" width="4.42578125" style="214" customWidth="1"/>
+    <col min="2306" max="2306" width="20.85546875" style="214" customWidth="1"/>
+    <col min="2307" max="2308" width="11.42578125" style="214"/>
+    <col min="2309" max="2310" width="4.140625" style="214" customWidth="1"/>
+    <col min="2311" max="2311" width="11.42578125" style="214"/>
+    <col min="2312" max="2312" width="19.140625" style="214" customWidth="1"/>
+    <col min="2313" max="2314" width="11.42578125" style="214"/>
+    <col min="2315" max="2316" width="4.85546875" style="214" customWidth="1"/>
+    <col min="2317" max="2317" width="10.85546875" style="214" customWidth="1"/>
+    <col min="2318" max="2318" width="11.42578125" style="214"/>
     <col min="2319" max="2319" width="22" style="214" customWidth="1"/>
-    <col min="2320" max="2321" width="11.44140625" style="214"/>
+    <col min="2320" max="2321" width="11.42578125" style="214"/>
     <col min="2322" max="2323" width="6" style="214" customWidth="1"/>
-    <col min="2324" max="2554" width="11.44140625" style="214"/>
+    <col min="2324" max="2554" width="11.42578125" style="214"/>
     <col min="2555" max="2556" width="20" style="214" customWidth="1"/>
-    <col min="2557" max="2557" width="11.44140625" style="214"/>
-    <col min="2558" max="2559" width="6.109375" style="214" customWidth="1"/>
+    <col min="2557" max="2557" width="11.42578125" style="214"/>
+    <col min="2558" max="2559" width="6.140625" style="214" customWidth="1"/>
     <col min="2560" max="2560" width="14" style="214" customWidth="1"/>
-    <col min="2561" max="2561" width="4.44140625" style="214" customWidth="1"/>
-    <col min="2562" max="2562" width="20.88671875" style="214" customWidth="1"/>
-    <col min="2563" max="2564" width="11.44140625" style="214"/>
-    <col min="2565" max="2566" width="4.109375" style="214" customWidth="1"/>
-    <col min="2567" max="2567" width="11.44140625" style="214"/>
-    <col min="2568" max="2568" width="19.109375" style="214" customWidth="1"/>
-    <col min="2569" max="2570" width="11.44140625" style="214"/>
-    <col min="2571" max="2572" width="4.88671875" style="214" customWidth="1"/>
-    <col min="2573" max="2573" width="10.88671875" style="214" customWidth="1"/>
-    <col min="2574" max="2574" width="11.44140625" style="214"/>
+    <col min="2561" max="2561" width="4.42578125" style="214" customWidth="1"/>
+    <col min="2562" max="2562" width="20.85546875" style="214" customWidth="1"/>
+    <col min="2563" max="2564" width="11.42578125" style="214"/>
+    <col min="2565" max="2566" width="4.140625" style="214" customWidth="1"/>
+    <col min="2567" max="2567" width="11.42578125" style="214"/>
+    <col min="2568" max="2568" width="19.140625" style="214" customWidth="1"/>
+    <col min="2569" max="2570" width="11.42578125" style="214"/>
+    <col min="2571" max="2572" width="4.85546875" style="214" customWidth="1"/>
+    <col min="2573" max="2573" width="10.85546875" style="214" customWidth="1"/>
+    <col min="2574" max="2574" width="11.42578125" style="214"/>
     <col min="2575" max="2575" width="22" style="214" customWidth="1"/>
-    <col min="2576" max="2577" width="11.44140625" style="214"/>
+    <col min="2576" max="2577" width="11.42578125" style="214"/>
     <col min="2578" max="2579" width="6" style="214" customWidth="1"/>
-    <col min="2580" max="2810" width="11.44140625" style="214"/>
+    <col min="2580" max="2810" width="11.42578125" style="214"/>
     <col min="2811" max="2812" width="20" style="214" customWidth="1"/>
-    <col min="2813" max="2813" width="11.44140625" style="214"/>
-    <col min="2814" max="2815" width="6.109375" style="214" customWidth="1"/>
+    <col min="2813" max="2813" width="11.42578125" style="214"/>
+    <col min="2814" max="2815" width="6.140625" style="214" customWidth="1"/>
     <col min="2816" max="2816" width="14" style="214" customWidth="1"/>
-    <col min="2817" max="2817" width="4.44140625" style="214" customWidth="1"/>
-    <col min="2818" max="2818" width="20.88671875" style="214" customWidth="1"/>
-    <col min="2819" max="2820" width="11.44140625" style="214"/>
-    <col min="2821" max="2822" width="4.109375" style="214" customWidth="1"/>
-    <col min="2823" max="2823" width="11.44140625" style="214"/>
-    <col min="2824" max="2824" width="19.109375" style="214" customWidth="1"/>
-    <col min="2825" max="2826" width="11.44140625" style="214"/>
-    <col min="2827" max="2828" width="4.88671875" style="214" customWidth="1"/>
-    <col min="2829" max="2829" width="10.88671875" style="214" customWidth="1"/>
-    <col min="2830" max="2830" width="11.44140625" style="214"/>
+    <col min="2817" max="2817" width="4.42578125" style="214" customWidth="1"/>
+    <col min="2818" max="2818" width="20.85546875" style="214" customWidth="1"/>
+    <col min="2819" max="2820" width="11.42578125" style="214"/>
+    <col min="2821" max="2822" width="4.140625" style="214" customWidth="1"/>
+    <col min="2823" max="2823" width="11.42578125" style="214"/>
+    <col min="2824" max="2824" width="19.140625" style="214" customWidth="1"/>
+    <col min="2825" max="2826" width="11.42578125" style="214"/>
+    <col min="2827" max="2828" width="4.85546875" style="214" customWidth="1"/>
+    <col min="2829" max="2829" width="10.85546875" style="214" customWidth="1"/>
+    <col min="2830" max="2830" width="11.42578125" style="214"/>
     <col min="2831" max="2831" width="22" style="214" customWidth="1"/>
-    <col min="2832" max="2833" width="11.44140625" style="214"/>
+    <col min="2832" max="2833" width="11.42578125" style="214"/>
     <col min="2834" max="2835" width="6" style="214" customWidth="1"/>
-    <col min="2836" max="3066" width="11.44140625" style="214"/>
+    <col min="2836" max="3066" width="11.42578125" style="214"/>
     <col min="3067" max="3068" width="20" style="214" customWidth="1"/>
-    <col min="3069" max="3069" width="11.44140625" style="214"/>
-    <col min="3070" max="3071" width="6.109375" style="214" customWidth="1"/>
+    <col min="3069" max="3069" width="11.42578125" style="214"/>
+    <col min="3070" max="3071" width="6.140625" style="214" customWidth="1"/>
     <col min="3072" max="3072" width="14" style="214" customWidth="1"/>
-    <col min="3073" max="3073" width="4.44140625" style="214" customWidth="1"/>
-    <col min="3074" max="3074" width="20.88671875" style="214" customWidth="1"/>
-    <col min="3075" max="3076" width="11.44140625" style="214"/>
-    <col min="3077" max="3078" width="4.109375" style="214" customWidth="1"/>
-    <col min="3079" max="3079" width="11.44140625" style="214"/>
-    <col min="3080" max="3080" width="19.109375" style="214" customWidth="1"/>
-    <col min="3081" max="3082" width="11.44140625" style="214"/>
-    <col min="3083" max="3084" width="4.88671875" style="214" customWidth="1"/>
-    <col min="3085" max="3085" width="10.88671875" style="214" customWidth="1"/>
-    <col min="3086" max="3086" width="11.44140625" style="214"/>
+    <col min="3073" max="3073" width="4.42578125" style="214" customWidth="1"/>
+    <col min="3074" max="3074" width="20.85546875" style="214" customWidth="1"/>
+    <col min="3075" max="3076" width="11.42578125" style="214"/>
+    <col min="3077" max="3078" width="4.140625" style="214" customWidth="1"/>
+    <col min="3079" max="3079" width="11.42578125" style="214"/>
+    <col min="3080" max="3080" width="19.140625" style="214" customWidth="1"/>
+    <col min="3081" max="3082" width="11.42578125" style="214"/>
+    <col min="3083" max="3084" width="4.85546875" style="214" customWidth="1"/>
+    <col min="3085" max="3085" width="10.85546875" style="214" customWidth="1"/>
+    <col min="3086" max="3086" width="11.42578125" style="214"/>
     <col min="3087" max="3087" width="22" style="214" customWidth="1"/>
-    <col min="3088" max="3089" width="11.44140625" style="214"/>
+    <col min="3088" max="3089" width="11.42578125" style="214"/>
     <col min="3090" max="3091" width="6" style="214" customWidth="1"/>
-    <col min="3092" max="3322" width="11.44140625" style="214"/>
+    <col min="3092" max="3322" width="11.42578125" style="214"/>
     <col min="3323" max="3324" width="20" style="214" customWidth="1"/>
-    <col min="3325" max="3325" width="11.44140625" style="214"/>
-    <col min="3326" max="3327" width="6.109375" style="214" customWidth="1"/>
+    <col min="3325" max="3325" width="11.42578125" style="214"/>
+    <col min="3326" max="3327" width="6.140625" style="214" customWidth="1"/>
     <col min="3328" max="3328" width="14" style="214" customWidth="1"/>
-    <col min="3329" max="3329" width="4.44140625" style="214" customWidth="1"/>
-    <col min="3330" max="3330" width="20.88671875" style="214" customWidth="1"/>
-    <col min="3331" max="3332" width="11.44140625" style="214"/>
-    <col min="3333" max="3334" width="4.109375" style="214" customWidth="1"/>
-    <col min="3335" max="3335" width="11.44140625" style="214"/>
-    <col min="3336" max="3336" width="19.109375" style="214" customWidth="1"/>
-    <col min="3337" max="3338" width="11.44140625" style="214"/>
-    <col min="3339" max="3340" width="4.88671875" style="214" customWidth="1"/>
-    <col min="3341" max="3341" width="10.88671875" style="214" customWidth="1"/>
-    <col min="3342" max="3342" width="11.44140625" style="214"/>
+    <col min="3329" max="3329" width="4.42578125" style="214" customWidth="1"/>
+    <col min="3330" max="3330" width="20.85546875" style="214" customWidth="1"/>
+    <col min="3331" max="3332" width="11.42578125" style="214"/>
+    <col min="3333" max="3334" width="4.140625" style="214" customWidth="1"/>
+    <col min="3335" max="3335" width="11.42578125" style="214"/>
+    <col min="3336" max="3336" width="19.140625" style="214" customWidth="1"/>
+    <col min="3337" max="3338" width="11.42578125" style="214"/>
+    <col min="3339" max="3340" width="4.85546875" style="214" customWidth="1"/>
+    <col min="3341" max="3341" width="10.85546875" style="214" customWidth="1"/>
+    <col min="3342" max="3342" width="11.42578125" style="214"/>
     <col min="3343" max="3343" width="22" style="214" customWidth="1"/>
-    <col min="3344" max="3345" width="11.44140625" style="214"/>
+    <col min="3344" max="3345" width="11.42578125" style="214"/>
     <col min="3346" max="3347" width="6" style="214" customWidth="1"/>
-    <col min="3348" max="3578" width="11.44140625" style="214"/>
+    <col min="3348" max="3578" width="11.42578125" style="214"/>
     <col min="3579" max="3580" width="20" style="214" customWidth="1"/>
-    <col min="3581" max="3581" width="11.44140625" style="214"/>
-    <col min="3582" max="3583" width="6.109375" style="214" customWidth="1"/>
+    <col min="3581" max="3581" width="11.42578125" style="214"/>
+    <col min="3582" max="3583" width="6.140625" style="214" customWidth="1"/>
     <col min="3584" max="3584" width="14" style="214" customWidth="1"/>
-    <col min="3585" max="3585" width="4.44140625" style="214" customWidth="1"/>
-    <col min="3586" max="3586" width="20.88671875" style="214" customWidth="1"/>
-    <col min="3587" max="3588" width="11.44140625" style="214"/>
-    <col min="3589" max="3590" width="4.109375" style="214" customWidth="1"/>
-    <col min="3591" max="3591" width="11.44140625" style="214"/>
-    <col min="3592" max="3592" width="19.109375" style="214" customWidth="1"/>
-    <col min="3593" max="3594" width="11.44140625" style="214"/>
-    <col min="3595" max="3596" width="4.88671875" style="214" customWidth="1"/>
-    <col min="3597" max="3597" width="10.88671875" style="214" customWidth="1"/>
-    <col min="3598" max="3598" width="11.44140625" style="214"/>
+    <col min="3585" max="3585" width="4.42578125" style="214" customWidth="1"/>
+    <col min="3586" max="3586" width="20.85546875" style="214" customWidth="1"/>
+    <col min="3587" max="3588" width="11.42578125" style="214"/>
+    <col min="3589" max="3590" width="4.140625" style="214" customWidth="1"/>
+    <col min="3591" max="3591" width="11.42578125" style="214"/>
+    <col min="3592" max="3592" width="19.140625" style="214" customWidth="1"/>
+    <col min="3593" max="3594" width="11.42578125" style="214"/>
+    <col min="3595" max="3596" width="4.85546875" style="214" customWidth="1"/>
+    <col min="3597" max="3597" width="10.85546875" style="214" customWidth="1"/>
+    <col min="3598" max="3598" width="11.42578125" style="214"/>
     <col min="3599" max="3599" width="22" style="214" customWidth="1"/>
-    <col min="3600" max="3601" width="11.44140625" style="214"/>
+    <col min="3600" max="3601" width="11.42578125" style="214"/>
     <col min="3602" max="3603" width="6" style="214" customWidth="1"/>
-    <col min="3604" max="3834" width="11.44140625" style="214"/>
+    <col min="3604" max="3834" width="11.42578125" style="214"/>
     <col min="3835" max="3836" width="20" style="214" customWidth="1"/>
-    <col min="3837" max="3837" width="11.44140625" style="214"/>
-    <col min="3838" max="3839" width="6.109375" style="214" customWidth="1"/>
+    <col min="3837" max="3837" width="11.42578125" style="214"/>
+    <col min="3838" max="3839" width="6.140625" style="214" customWidth="1"/>
     <col min="3840" max="3840" width="14" style="214" customWidth="1"/>
-    <col min="3841" max="3841" width="4.44140625" style="214" customWidth="1"/>
-    <col min="3842" max="3842" width="20.88671875" style="214" customWidth="1"/>
-    <col min="3843" max="3844" width="11.44140625" style="214"/>
-    <col min="3845" max="3846" width="4.109375" style="214" customWidth="1"/>
-    <col min="3847" max="3847" width="11.44140625" style="214"/>
-    <col min="3848" max="3848" width="19.109375" style="214" customWidth="1"/>
-    <col min="3849" max="3850" width="11.44140625" style="214"/>
-    <col min="3851" max="3852" width="4.88671875" style="214" customWidth="1"/>
-    <col min="3853" max="3853" width="10.88671875" style="214" customWidth="1"/>
-    <col min="3854" max="3854" width="11.44140625" style="214"/>
+    <col min="3841" max="3841" width="4.42578125" style="214" customWidth="1"/>
+    <col min="3842" max="3842" width="20.85546875" style="214" customWidth="1"/>
+    <col min="3843" max="3844" width="11.42578125" style="214"/>
+    <col min="3845" max="3846" width="4.140625" style="214" customWidth="1"/>
+    <col min="3847" max="3847" width="11.42578125" style="214"/>
+    <col min="3848" max="3848" width="19.140625" style="214" customWidth="1"/>
+    <col min="3849" max="3850" width="11.42578125" style="214"/>
+    <col min="3851" max="3852" width="4.85546875" style="214" customWidth="1"/>
+    <col min="3853" max="3853" width="10.85546875" style="214" customWidth="1"/>
+    <col min="3854" max="3854" width="11.42578125" style="214"/>
     <col min="3855" max="3855" width="22" style="214" customWidth="1"/>
-    <col min="3856" max="3857" width="11.44140625" style="214"/>
+    <col min="3856" max="3857" width="11.42578125" style="214"/>
     <col min="3858" max="3859" width="6" style="214" customWidth="1"/>
-    <col min="3860" max="4090" width="11.44140625" style="214"/>
+    <col min="3860" max="4090" width="11.42578125" style="214"/>
     <col min="4091" max="4092" width="20" style="214" customWidth="1"/>
-    <col min="4093" max="4093" width="11.44140625" style="214"/>
-    <col min="4094" max="4095" width="6.109375" style="214" customWidth="1"/>
+    <col min="4093" max="4093" width="11.42578125" style="214"/>
+    <col min="4094" max="4095" width="6.140625" style="214" customWidth="1"/>
     <col min="4096" max="4096" width="14" style="214" customWidth="1"/>
-    <col min="4097" max="4097" width="4.44140625" style="214" customWidth="1"/>
-    <col min="4098" max="4098" width="20.88671875" style="214" customWidth="1"/>
-    <col min="4099" max="4100" width="11.44140625" style="214"/>
-    <col min="4101" max="4102" width="4.109375" style="214" customWidth="1"/>
-    <col min="4103" max="4103" width="11.44140625" style="214"/>
-    <col min="4104" max="4104" width="19.109375" style="214" customWidth="1"/>
-    <col min="4105" max="4106" width="11.44140625" style="214"/>
-    <col min="4107" max="4108" width="4.88671875" style="214" customWidth="1"/>
-    <col min="4109" max="4109" width="10.88671875" style="214" customWidth="1"/>
-    <col min="4110" max="4110" width="11.44140625" style="214"/>
+    <col min="4097" max="4097" width="4.42578125" style="214" customWidth="1"/>
+    <col min="4098" max="4098" width="20.85546875" style="214" customWidth="1"/>
+    <col min="4099" max="4100" width="11.42578125" style="214"/>
+    <col min="4101" max="4102" width="4.140625" style="214" customWidth="1"/>
+    <col min="4103" max="4103" width="11.42578125" style="214"/>
+    <col min="4104" max="4104" width="19.140625" style="214" customWidth="1"/>
+    <col min="4105" max="4106" width="11.42578125" style="214"/>
+    <col min="4107" max="4108" width="4.85546875" style="214" customWidth="1"/>
+    <col min="4109" max="4109" width="10.85546875" style="214" customWidth="1"/>
+    <col min="4110" max="4110" width="11.42578125" style="214"/>
     <col min="4111" max="4111" width="22" style="214" customWidth="1"/>
-    <col min="4112" max="4113" width="11.44140625" style="214"/>
+    <col min="4112" max="4113" width="11.42578125" style="214"/>
     <col min="4114" max="4115" width="6" style="214" customWidth="1"/>
-    <col min="4116" max="4346" width="11.44140625" style="214"/>
+    <col min="4116" max="4346" width="11.42578125" style="214"/>
     <col min="4347" max="4348" width="20" style="214" customWidth="1"/>
-    <col min="4349" max="4349" width="11.44140625" style="214"/>
-    <col min="4350" max="4351" width="6.109375" style="214" customWidth="1"/>
+    <col min="4349" max="4349" width="11.42578125" style="214"/>
+    <col min="4350" max="4351" width="6.140625" style="214" customWidth="1"/>
     <col min="4352" max="4352" width="14" style="214" customWidth="1"/>
-    <col min="4353" max="4353" width="4.44140625" style="214" customWidth="1"/>
-    <col min="4354" max="4354" width="20.88671875" style="214" customWidth="1"/>
-    <col min="4355" max="4356" width="11.44140625" style="214"/>
-    <col min="4357" max="4358" width="4.109375" style="214" customWidth="1"/>
-    <col min="4359" max="4359" width="11.44140625" style="214"/>
-    <col min="4360" max="4360" width="19.109375" style="214" customWidth="1"/>
-    <col min="4361" max="4362" width="11.44140625" style="214"/>
-    <col min="4363" max="4364" width="4.88671875" style="214" customWidth="1"/>
-    <col min="4365" max="4365" width="10.88671875" style="214" customWidth="1"/>
-    <col min="4366" max="4366" width="11.44140625" style="214"/>
+    <col min="4353" max="4353" width="4.42578125" style="214" customWidth="1"/>
+    <col min="4354" max="4354" width="20.85546875" style="214" customWidth="1"/>
+    <col min="4355" max="4356" width="11.42578125" style="214"/>
+    <col min="4357" max="4358" width="4.140625" style="214" customWidth="1"/>
+    <col min="4359" max="4359" width="11.42578125" style="214"/>
+    <col min="4360" max="4360" width="19.140625" style="214" customWidth="1"/>
+    <col min="4361" max="4362" width="11.42578125" style="214"/>
+    <col min="4363" max="4364" width="4.85546875" style="214" customWidth="1"/>
+    <col min="4365" max="4365" width="10.85546875" style="214" customWidth="1"/>
+    <col min="4366" max="4366" width="11.42578125" style="214"/>
     <col min="4367" max="4367" width="22" style="214" customWidth="1"/>
-    <col min="4368" max="4369" width="11.44140625" style="214"/>
+    <col min="4368" max="4369" width="11.42578125" style="214"/>
     <col min="4370" max="4371" width="6" style="214" customWidth="1"/>
-    <col min="4372" max="4602" width="11.44140625" style="214"/>
+    <col min="4372" max="4602" width="11.42578125" style="214"/>
     <col min="4603" max="4604" width="20" style="214" customWidth="1"/>
-    <col min="4605" max="4605" width="11.44140625" style="214"/>
-    <col min="4606" max="4607" width="6.109375" style="214" customWidth="1"/>
+    <col min="4605" max="4605" width="11.42578125" style="214"/>
+    <col min="4606" max="4607" width="6.140625" style="214" customWidth="1"/>
     <col min="4608" max="4608" width="14" style="214" customWidth="1"/>
-    <col min="4609" max="4609" width="4.44140625" style="214" customWidth="1"/>
-    <col min="4610" max="4610" width="20.88671875" style="214" customWidth="1"/>
-    <col min="4611" max="4612" width="11.44140625" style="214"/>
-    <col min="4613" max="4614" width="4.109375" style="214" customWidth="1"/>
-    <col min="4615" max="4615" width="11.44140625" style="214"/>
-    <col min="4616" max="4616" width="19.109375" style="214" customWidth="1"/>
-    <col min="4617" max="4618" width="11.44140625" style="214"/>
-    <col min="4619" max="4620" width="4.88671875" style="214" customWidth="1"/>
-    <col min="4621" max="4621" width="10.88671875" style="214" customWidth="1"/>
-    <col min="4622" max="4622" width="11.44140625" style="214"/>
+    <col min="4609" max="4609" width="4.42578125" style="214" customWidth="1"/>
+    <col min="4610" max="4610" width="20.85546875" style="214" customWidth="1"/>
+    <col min="4611" max="4612" width="11.42578125" style="214"/>
+    <col min="4613" max="4614" width="4.140625" style="214" customWidth="1"/>
+    <col min="4615" max="4615" width="11.42578125" style="214"/>
+    <col min="4616" max="4616" width="19.140625" style="214" customWidth="1"/>
+    <col min="4617" max="4618" width="11.42578125" style="214"/>
+    <col min="4619" max="4620" width="4.85546875" style="214" customWidth="1"/>
+    <col min="4621" max="4621" width="10.85546875" style="214" customWidth="1"/>
+    <col min="4622" max="4622" width="11.42578125" style="214"/>
     <col min="4623" max="4623" width="22" style="214" customWidth="1"/>
-    <col min="4624" max="4625" width="11.44140625" style="214"/>
+    <col min="4624" max="4625" width="11.42578125" style="214"/>
     <col min="4626" max="4627" width="6" style="214" customWidth="1"/>
-    <col min="4628" max="4858" width="11.44140625" style="214"/>
+    <col min="4628" max="4858" width="11.42578125" style="214"/>
     <col min="4859" max="4860" width="20" style="214" customWidth="1"/>
-    <col min="4861" max="4861" width="11.44140625" style="214"/>
-    <col min="4862" max="4863" width="6.109375" style="214" customWidth="1"/>
+    <col min="4861" max="4861" width="11.42578125" style="214"/>
+    <col min="4862" max="4863" width="6.140625" style="214" customWidth="1"/>
     <col min="4864" max="4864" width="14" style="214" customWidth="1"/>
-    <col min="4865" max="4865" width="4.44140625" style="214" customWidth="1"/>
-    <col min="4866" max="4866" width="20.88671875" style="214" customWidth="1"/>
-    <col min="4867" max="4868" width="11.44140625" style="214"/>
-    <col min="4869" max="4870" width="4.109375" style="214" customWidth="1"/>
-    <col min="4871" max="4871" width="11.44140625" style="214"/>
-    <col min="4872" max="4872" width="19.109375" style="214" customWidth="1"/>
-    <col min="4873" max="4874" width="11.44140625" style="214"/>
-    <col min="4875" max="4876" width="4.88671875" style="214" customWidth="1"/>
-    <col min="4877" max="4877" width="10.88671875" style="214" customWidth="1"/>
-    <col min="4878" max="4878" width="11.44140625" style="214"/>
+    <col min="4865" max="4865" width="4.42578125" style="214" customWidth="1"/>
+    <col min="4866" max="4866" width="20.85546875" style="214" customWidth="1"/>
+    <col min="4867" max="4868" width="11.42578125" style="214"/>
+    <col min="4869" max="4870" width="4.140625" style="214" customWidth="1"/>
+    <col min="4871" max="4871" width="11.42578125" style="214"/>
+    <col min="4872" max="4872" width="19.140625" style="214" customWidth="1"/>
+    <col min="4873" max="4874" width="11.42578125" style="214"/>
+    <col min="4875" max="4876" width="4.85546875" style="214" customWidth="1"/>
+    <col min="4877" max="4877" width="10.85546875" style="214" customWidth="1"/>
+    <col min="4878" max="4878" width="11.42578125" style="214"/>
     <col min="4879" max="4879" width="22" style="214" customWidth="1"/>
-    <col min="4880" max="4881" width="11.44140625" style="214"/>
+    <col min="4880" max="4881" width="11.42578125" style="214"/>
     <col min="4882" max="4883" width="6" style="214" customWidth="1"/>
-    <col min="4884" max="5114" width="11.44140625" style="214"/>
+    <col min="4884" max="5114" width="11.42578125" style="214"/>
     <col min="5115" max="5116" width="20" style="214" customWidth="1"/>
-    <col min="5117" max="5117" width="11.44140625" style="214"/>
-    <col min="5118" max="5119" width="6.109375" style="214" customWidth="1"/>
+    <col min="5117" max="5117" width="11.42578125" style="214"/>
+    <col min="5118" max="5119" width="6.140625" style="214" customWidth="1"/>
     <col min="5120" max="5120" width="14" style="214" customWidth="1"/>
-    <col min="5121" max="5121" width="4.44140625" style="214" customWidth="1"/>
-    <col min="5122" max="5122" width="20.88671875" style="214" customWidth="1"/>
-    <col min="5123" max="5124" width="11.44140625" style="214"/>
-    <col min="5125" max="5126" width="4.109375" style="214" customWidth="1"/>
-    <col min="5127" max="5127" width="11.44140625" style="214"/>
-    <col min="5128" max="5128" width="19.109375" style="214" customWidth="1"/>
-    <col min="5129" max="5130" width="11.44140625" style="214"/>
-    <col min="5131" max="5132" width="4.88671875" style="214" customWidth="1"/>
-    <col min="5133" max="5133" width="10.88671875" style="214" customWidth="1"/>
-    <col min="5134" max="5134" width="11.44140625" style="214"/>
+    <col min="5121" max="5121" width="4.42578125" style="214" customWidth="1"/>
+    <col min="5122" max="5122" width="20.85546875" style="214" customWidth="1"/>
+    <col min="5123" max="5124" width="11.42578125" style="214"/>
+    <col min="5125" max="5126" width="4.140625" style="214" customWidth="1"/>
+    <col min="5127" max="5127" width="11.42578125" style="214"/>
+    <col min="5128" max="5128" width="19.140625" style="214" customWidth="1"/>
+    <col min="5129" max="5130" width="11.42578125" style="214"/>
+    <col min="5131" max="5132" width="4.85546875" style="214" customWidth="1"/>
+    <col min="5133" max="5133" width="10.85546875" style="214" customWidth="1"/>
+    <col min="5134" max="5134" width="11.42578125" style="214"/>
     <col min="5135" max="5135" width="22" style="214" customWidth="1"/>
-    <col min="5136" max="5137" width="11.44140625" style="214"/>
+    <col min="5136" max="5137" width="11.42578125" style="214"/>
     <col min="5138" max="5139" width="6" style="214" customWidth="1"/>
-    <col min="5140" max="5370" width="11.44140625" style="214"/>
+    <col min="5140" max="5370" width="11.42578125" style="214"/>
     <col min="5371" max="5372" width="20" style="214" customWidth="1"/>
-    <col min="5373" max="5373" width="11.44140625" style="214"/>
-    <col min="5374" max="5375" width="6.109375" style="214" customWidth="1"/>
+    <col min="5373" max="5373" width="11.42578125" style="214"/>
+    <col min="5374" max="5375" width="6.140625" style="214" customWidth="1"/>
     <col min="5376" max="5376" width="14" style="214" customWidth="1"/>
-    <col min="5377" max="5377" width="4.44140625" style="214" customWidth="1"/>
-    <col min="5378" max="5378" width="20.88671875" style="214" customWidth="1"/>
-    <col min="5379" max="5380" width="11.44140625" style="214"/>
-    <col min="5381" max="5382" width="4.109375" style="214" customWidth="1"/>
-    <col min="5383" max="5383" width="11.44140625" style="214"/>
-    <col min="5384" max="5384" width="19.109375" style="214" customWidth="1"/>
-    <col min="5385" max="5386" width="11.44140625" style="214"/>
-    <col min="5387" max="5388" width="4.88671875" style="214" customWidth="1"/>
-    <col min="5389" max="5389" width="10.88671875" style="214" customWidth="1"/>
-    <col min="5390" max="5390" width="11.44140625" style="214"/>
+    <col min="5377" max="5377" width="4.42578125" style="214" customWidth="1"/>
+    <col min="5378" max="5378" width="20.85546875" style="214" customWidth="1"/>
+    <col min="5379" max="5380" width="11.42578125" style="214"/>
+    <col min="5381" max="5382" width="4.140625" style="214" customWidth="1"/>
+    <col min="5383" max="5383" width="11.42578125" style="214"/>
+    <col min="5384" max="5384" width="19.140625" style="214" customWidth="1"/>
+    <col min="5385" max="5386" width="11.42578125" style="214"/>
+    <col min="5387" max="5388" width="4.85546875" style="214" customWidth="1"/>
+    <col min="5389" max="5389" width="10.85546875" style="214" customWidth="1"/>
+    <col min="5390" max="5390" width="11.42578125" style="214"/>
     <col min="5391" max="5391" width="22" style="214" customWidth="1"/>
-    <col min="5392" max="5393" width="11.44140625" style="214"/>
+    <col min="5392" max="5393" width="11.42578125" style="214"/>
     <col min="5394" max="5395" width="6" style="214" customWidth="1"/>
-    <col min="5396" max="5626" width="11.44140625" style="214"/>
+    <col min="5396" max="5626" width="11.42578125" style="214"/>
     <col min="5627" max="5628" width="20" style="214" customWidth="1"/>
-    <col min="5629" max="5629" width="11.44140625" style="214"/>
-    <col min="5630" max="5631" width="6.109375" style="214" customWidth="1"/>
+    <col min="5629" max="5629" width="11.42578125" style="214"/>
+    <col min="5630" max="5631" width="6.140625" style="214" customWidth="1"/>
     <col min="5632" max="5632" width="14" style="214" customWidth="1"/>
-    <col min="5633" max="5633" width="4.44140625" style="214" customWidth="1"/>
-    <col min="5634" max="5634" width="20.88671875" style="214" customWidth="1"/>
-    <col min="5635" max="5636" width="11.44140625" style="214"/>
-    <col min="5637" max="5638" width="4.109375" style="214" customWidth="1"/>
-    <col min="5639" max="5639" width="11.44140625" style="214"/>
-    <col min="5640" max="5640" width="19.109375" style="214" customWidth="1"/>
-    <col min="5641" max="5642" width="11.44140625" style="214"/>
-    <col min="5643" max="5644" width="4.88671875" style="214" customWidth="1"/>
-    <col min="5645" max="5645" width="10.88671875" style="214" customWidth="1"/>
-    <col min="5646" max="5646" width="11.44140625" style="214"/>
+    <col min="5633" max="5633" width="4.42578125" style="214" customWidth="1"/>
+    <col min="5634" max="5634" width="20.85546875" style="214" customWidth="1"/>
+    <col min="5635" max="5636" width="11.42578125" style="214"/>
+    <col min="5637" max="5638" width="4.140625" style="214" customWidth="1"/>
+    <col min="5639" max="5639" width="11.42578125" style="214"/>
+    <col min="5640" max="5640" width="19.140625" style="214" customWidth="1"/>
+    <col min="5641" max="5642" width="11.42578125" style="214"/>
+    <col min="5643" max="5644" width="4.85546875" style="214" customWidth="1"/>
+    <col min="5645" max="5645" width="10.85546875" style="214" customWidth="1"/>
+    <col min="5646" max="5646" width="11.42578125" style="214"/>
     <col min="5647" max="5647" width="22" style="214" customWidth="1"/>
-    <col min="5648" max="5649" width="11.44140625" style="214"/>
+    <col min="5648" max="5649" width="11.42578125" style="214"/>
     <col min="5650" max="5651" width="6" style="214" customWidth="1"/>
-    <col min="5652" max="5882" width="11.44140625" style="214"/>
+    <col min="5652" max="5882" width="11.42578125" style="214"/>
     <col min="5883" max="5884" width="20" style="214" customWidth="1"/>
-    <col min="5885" max="5885" width="11.44140625" style="214"/>
-    <col min="5886" max="5887" width="6.109375" style="214" customWidth="1"/>
+    <col min="5885" max="5885" width="11.42578125" style="214"/>
+    <col min="5886" max="5887" width="6.140625" style="214" customWidth="1"/>
     <col min="5888" max="5888" width="14" style="214" customWidth="1"/>
-    <col min="5889" max="5889" width="4.44140625" style="214" customWidth="1"/>
-    <col min="5890" max="5890" width="20.88671875" style="214" customWidth="1"/>
-    <col min="5891" max="5892" width="11.44140625" style="214"/>
-    <col min="5893" max="5894" width="4.109375" style="214" customWidth="1"/>
-    <col min="5895" max="5895" width="11.44140625" style="214"/>
-    <col min="5896" max="5896" width="19.109375" style="214" customWidth="1"/>
-    <col min="5897" max="5898" width="11.44140625" style="214"/>
-    <col min="5899" max="5900" width="4.88671875" style="214" customWidth="1"/>
-    <col min="5901" max="5901" width="10.88671875" style="214" customWidth="1"/>
-    <col min="5902" max="5902" width="11.44140625" style="214"/>
+    <col min="5889" max="5889" width="4.42578125" style="214" customWidth="1"/>
+    <col min="5890" max="5890" width="20.85546875" style="214" customWidth="1"/>
+    <col min="5891" max="5892" width="11.42578125" style="214"/>
+    <col min="5893" max="5894" width="4.140625" style="214" customWidth="1"/>
+    <col min="5895" max="5895" width="11.42578125" style="214"/>
+    <col min="5896" max="5896" width="19.140625" style="214" customWidth="1"/>
+    <col min="5897" max="5898" width="11.42578125" style="214"/>
+    <col min="5899" max="5900" width="4.85546875" style="214" customWidth="1"/>
+    <col min="5901" max="5901" width="10.85546875" style="214" customWidth="1"/>
+    <col min="5902" max="5902" width="11.42578125" style="214"/>
     <col min="5903" max="5903" width="22" style="214" customWidth="1"/>
-    <col min="5904" max="5905" width="11.44140625" style="214"/>
+    <col min="5904" max="5905" width="11.42578125" style="214"/>
     <col min="5906" max="5907" width="6" style="214" customWidth="1"/>
-    <col min="5908" max="6138" width="11.44140625" style="214"/>
+    <col min="5908" max="6138" width="11.42578125" style="214"/>
     <col min="6139" max="6140" width="20" style="214" customWidth="1"/>
-    <col min="6141" max="6141" width="11.44140625" style="214"/>
-    <col min="6142" max="6143" width="6.109375" style="214" customWidth="1"/>
+    <col min="6141" max="6141" width="11.42578125" style="214"/>
+    <col min="6142" max="6143" width="6.140625" style="214" customWidth="1"/>
     <col min="6144" max="6144" width="14" style="214" customWidth="1"/>
-    <col min="6145" max="6145" width="4.44140625" style="214" customWidth="1"/>
-    <col min="6146" max="6146" width="20.88671875" style="214" customWidth="1"/>
-    <col min="6147" max="6148" width="11.44140625" style="214"/>
-    <col min="6149" max="6150" width="4.109375" style="214" customWidth="1"/>
-    <col min="6151" max="6151" width="11.44140625" style="214"/>
-    <col min="6152" max="6152" width="19.109375" style="214" customWidth="1"/>
-    <col min="6153" max="6154" width="11.44140625" style="214"/>
-    <col min="6155" max="6156" width="4.88671875" style="214" customWidth="1"/>
-    <col min="6157" max="6157" width="10.88671875" style="214" customWidth="1"/>
-    <col min="6158" max="6158" width="11.44140625" style="214"/>
+    <col min="6145" max="6145" width="4.42578125" style="214" customWidth="1"/>
+    <col min="6146" max="6146" width="20.85546875" style="214" customWidth="1"/>
+    <col min="6147" max="6148" width="11.42578125" style="214"/>
+    <col min="6149" max="6150" width="4.140625" style="214" customWidth="1"/>
+    <col min="6151" max="6151" width="11.42578125" style="214"/>
+    <col min="6152" max="6152" width="19.140625" style="214" customWidth="1"/>
+    <col min="6153" max="6154" width="11.42578125" style="214"/>
+    <col min="6155" max="6156" width="4.85546875" style="214" customWidth="1"/>
+    <col min="6157" max="6157" width="10.85546875" style="214" customWidth="1"/>
+    <col min="6158" max="6158" width="11.42578125" style="214"/>
     <col min="6159" max="6159" width="22" style="214" customWidth="1"/>
-    <col min="6160" max="6161" width="11.44140625" style="214"/>
+    <col min="6160" max="6161" width="11.42578125" style="214"/>
     <col min="6162" max="6163" width="6" style="214" customWidth="1"/>
-    <col min="6164" max="6394" width="11.44140625" style="214"/>
+    <col min="6164" max="6394" width="11.42578125" style="214"/>
     <col min="6395" max="6396" width="20" style="214" customWidth="1"/>
-    <col min="6397" max="6397" width="11.44140625" style="214"/>
-    <col min="6398" max="6399" width="6.109375" style="214" customWidth="1"/>
+    <col min="6397" max="6397" width="11.42578125" style="214"/>
+    <col min="6398" max="6399" width="6.140625" style="214" customWidth="1"/>
     <col min="6400" max="6400" width="14" style="214" customWidth="1"/>
-    <col min="6401" max="6401" width="4.44140625" style="214" customWidth="1"/>
-    <col min="6402" max="6402" width="20.88671875" style="214" customWidth="1"/>
-    <col min="6403" max="6404" width="11.44140625" style="214"/>
-    <col min="6405" max="6406" width="4.109375" style="214" customWidth="1"/>
-    <col min="6407" max="6407" width="11.44140625" style="214"/>
-    <col min="6408" max="6408" width="19.109375" style="214" customWidth="1"/>
-    <col min="6409" max="6410" width="11.44140625" style="214"/>
-    <col min="6411" max="6412" width="4.88671875" style="214" customWidth="1"/>
-    <col min="6413" max="6413" width="10.88671875" style="214" customWidth="1"/>
-    <col min="6414" max="6414" width="11.44140625" style="214"/>
+    <col min="6401" max="6401" width="4.42578125" style="214" customWidth="1"/>
+    <col min="6402" max="6402" width="20.85546875" style="214" customWidth="1"/>
+    <col min="6403" max="6404" width="11.42578125" style="214"/>
+    <col min="6405" max="6406" width="4.140625" style="214" customWidth="1"/>
+    <col min="6407" max="6407" width="11.42578125" style="214"/>
+    <col min="6408" max="6408" width="19.140625" style="214" customWidth="1"/>
+    <col min="6409" max="6410" width="11.42578125" style="214"/>
+    <col min="6411" max="6412" width="4.85546875" style="214" customWidth="1"/>
+    <col min="6413" max="6413" width="10.85546875" style="214" customWidth="1"/>
+    <col min="6414" max="6414" width="11.42578125" style="214"/>
     <col min="6415" max="6415" width="22" style="214" customWidth="1"/>
-    <col min="6416" max="6417" width="11.44140625" style="214"/>
+    <col min="6416" max="6417" width="11.42578125" style="214"/>
     <col min="6418" max="6419" width="6" style="214" customWidth="1"/>
-    <col min="6420" max="6650" width="11.44140625" style="214"/>
+    <col min="6420" max="6650" width="11.42578125" style="214"/>
     <col min="6651" max="6652" width="20" style="214" customWidth="1"/>
-    <col min="6653" max="6653" width="11.44140625" style="214"/>
-    <col min="6654" max="6655" width="6.109375" style="214" customWidth="1"/>
+    <col min="6653" max="6653" width="11.42578125" style="214"/>
+    <col min="6654" max="6655" width="6.140625" style="214" customWidth="1"/>
     <col min="6656" max="6656" width="14" style="214" customWidth="1"/>
-    <col min="6657" max="6657" width="4.44140625" style="214" customWidth="1"/>
-    <col min="6658" max="6658" width="20.88671875" style="214" customWidth="1"/>
-    <col min="6659" max="6660" width="11.44140625" style="214"/>
-    <col min="6661" max="6662" width="4.109375" style="214" customWidth="1"/>
-    <col min="6663" max="6663" width="11.44140625" style="214"/>
-    <col min="6664" max="6664" width="19.109375" style="214" customWidth="1"/>
-    <col min="6665" max="6666" width="11.44140625" style="214"/>
-    <col min="6667" max="6668" width="4.88671875" style="214" customWidth="1"/>
-    <col min="6669" max="6669" width="10.88671875" style="214" customWidth="1"/>
-    <col min="6670" max="6670" width="11.44140625" style="214"/>
+    <col min="6657" max="6657" width="4.42578125" style="214" customWidth="1"/>
+    <col min="6658" max="6658" width="20.85546875" style="214" customWidth="1"/>
+    <col min="6659" max="6660" width="11.42578125" style="214"/>
+    <col min="6661" max="6662" width="4.140625" style="214" customWidth="1"/>
+    <col min="6663" max="6663" width="11.42578125" style="214"/>
+    <col min="6664" max="6664" width="19.140625" style="214" customWidth="1"/>
+    <col min="6665" max="6666" width="11.42578125" style="214"/>
+    <col min="6667" max="6668" width="4.85546875" style="214" customWidth="1"/>
+    <col min="6669" max="6669" width="10.85546875" style="214" customWidth="1"/>
+    <col min="6670" max="6670" width="11.42578125" style="214"/>
     <col min="6671" max="6671" width="22" style="214" customWidth="1"/>
-    <col min="6672" max="6673" width="11.44140625" style="214"/>
+    <col min="6672" max="6673" width="11.42578125" style="214"/>
     <col min="6674" max="6675" width="6" style="214" customWidth="1"/>
-    <col min="6676" max="6906" width="11.44140625" style="214"/>
+    <col min="6676" max="6906" width="11.42578125" style="214"/>
     <col min="6907" max="6908" width="20" style="214" customWidth="1"/>
-    <col min="6909" max="6909" width="11.44140625" style="214"/>
-    <col min="6910" max="6911" width="6.109375" style="214" customWidth="1"/>
+    <col min="6909" max="6909" width="11.42578125" style="214"/>
+    <col min="6910" max="6911" width="6.140625" style="214" customWidth="1"/>
     <col min="6912" max="6912" width="14" style="214" customWidth="1"/>
-    <col min="6913" max="6913" width="4.44140625" style="214" customWidth="1"/>
-    <col min="6914" max="6914" width="20.88671875" style="214" customWidth="1"/>
-    <col min="6915" max="6916" width="11.44140625" style="214"/>
-    <col min="6917" max="6918" width="4.109375" style="214" customWidth="1"/>
-    <col min="6919" max="6919" width="11.44140625" style="214"/>
-    <col min="6920" max="6920" width="19.109375" style="214" customWidth="1"/>
-    <col min="6921" max="6922" width="11.44140625" style="214"/>
-    <col min="6923" max="6924" width="4.88671875" style="214" customWidth="1"/>
-    <col min="6925" max="6925" width="10.88671875" style="214" customWidth="1"/>
-    <col min="6926" max="6926" width="11.44140625" style="214"/>
+    <col min="6913" max="6913" width="4.42578125" style="214" customWidth="1"/>
+    <col min="6914" max="6914" width="20.85546875" style="214" customWidth="1"/>
+    <col min="6915" max="6916" width="11.42578125" style="214"/>
+    <col min="6917" max="6918" width="4.140625" style="214" customWidth="1"/>
+    <col min="6919" max="6919" width="11.42578125" style="214"/>
+    <col min="6920" max="6920" width="19.140625" style="214" customWidth="1"/>
+    <col min="6921" max="6922" width="11.42578125" style="214"/>
+    <col min="6923" max="6924" width="4.85546875" style="214" customWidth="1"/>
+    <col min="6925" max="6925" width="10.85546875" style="214" customWidth="1"/>
+    <col min="6926" max="6926" width="11.42578125" style="214"/>
     <col min="6927" max="6927" width="22" style="214" customWidth="1"/>
-    <col min="6928" max="6929" width="11.44140625" style="214"/>
+    <col min="6928" max="6929" width="11.42578125" style="214"/>
     <col min="6930" max="6931" width="6" style="214" customWidth="1"/>
-    <col min="6932" max="7162" width="11.44140625" style="214"/>
+    <col min="6932" max="7162" width="11.42578125" style="214"/>
     <col min="7163" max="7164" width="20" style="214" customWidth="1"/>
-    <col min="7165" max="7165" width="11.44140625" style="214"/>
-    <col min="7166" max="7167" width="6.109375" style="214" customWidth="1"/>
+    <col min="7165" max="7165" width="11.42578125" style="214"/>
+    <col min="7166" max="7167" width="6.140625" style="214" customWidth="1"/>
     <col min="7168" max="7168" width="14" style="214" customWidth="1"/>
-    <col min="7169" max="7169" width="4.44140625" style="214" customWidth="1"/>
-    <col min="7170" max="7170" width="20.88671875" style="214" customWidth="1"/>
-    <col min="7171" max="7172" width="11.44140625" style="214"/>
-    <col min="7173" max="7174" width="4.109375" style="214" customWidth="1"/>
-    <col min="7175" max="7175" width="11.44140625" style="214"/>
-    <col min="7176" max="7176" width="19.109375" style="214" customWidth="1"/>
-    <col min="7177" max="7178" width="11.44140625" style="214"/>
-    <col min="7179" max="7180" width="4.88671875" style="214" customWidth="1"/>
-    <col min="7181" max="7181" width="10.88671875" style="214" customWidth="1"/>
-    <col min="7182" max="7182" width="11.44140625" style="214"/>
+    <col min="7169" max="7169" width="4.42578125" style="214" customWidth="1"/>
+    <col min="7170" max="7170" width="20.85546875" style="214" customWidth="1"/>
+    <col min="7171" max="7172" width="11.42578125" style="214"/>
+    <col min="7173" max="7174" width="4.140625" style="214" customWidth="1"/>
+    <col min="7175" max="7175" width="11.42578125" style="214"/>
+    <col min="7176" max="7176" width="19.140625" style="214" customWidth="1"/>
+    <col min="7177" max="7178" width="11.42578125" style="214"/>
+    <col min="7179" max="7180" width="4.85546875" style="214" customWidth="1"/>
+    <col min="7181" max="7181" width="10.85546875" style="214" customWidth="1"/>
+    <col min="7182" max="7182" width="11.42578125" style="214"/>
     <col min="7183" max="7183" width="22" style="214" customWidth="1"/>
-    <col min="7184" max="7185" width="11.44140625" style="214"/>
+    <col min="7184" max="7185" width="11.42578125" style="214"/>
     <col min="7186" max="7187" width="6" style="214" customWidth="1"/>
-    <col min="7188" max="7418" width="11.44140625" style="214"/>
+    <col min="7188" max="7418" width="11.42578125" style="214"/>
     <col min="7419" max="7420" width="20" style="214" customWidth="1"/>
-    <col min="7421" max="7421" width="11.44140625" style="214"/>
-    <col min="7422" max="7423" width="6.109375" style="214" customWidth="1"/>
+    <col min="7421" max="7421" width="11.42578125" style="214"/>
+    <col min="7422" max="7423" width="6.140625" style="214" customWidth="1"/>
     <col min="7424" max="7424" width="14" style="214" customWidth="1"/>
-    <col min="7425" max="7425" width="4.44140625" style="214" customWidth="1"/>
-    <col min="7426" max="7426" width="20.88671875" style="214" customWidth="1"/>
-    <col min="7427" max="7428" width="11.44140625" style="214"/>
-    <col min="7429" max="7430" width="4.109375" style="214" customWidth="1"/>
-    <col min="7431" max="7431" width="11.44140625" style="214"/>
-    <col min="7432" max="7432" width="19.109375" style="214" customWidth="1"/>
-    <col min="7433" max="7434" width="11.44140625" style="214"/>
-    <col min="7435" max="7436" width="4.88671875" style="214" customWidth="1"/>
-    <col min="7437" max="7437" width="10.88671875" style="214" customWidth="1"/>
-    <col min="7438" max="7438" width="11.44140625" style="214"/>
+    <col min="7425" max="7425" width="4.42578125" style="214" customWidth="1"/>
+    <col min="7426" max="7426" width="20.85546875" style="214" customWidth="1"/>
+    <col min="7427" max="7428" width="11.42578125" style="214"/>
+    <col min="7429" max="7430" width="4.140625" style="214" customWidth="1"/>
+    <col min="7431" max="7431" width="11.42578125" style="214"/>
+    <col min="7432" max="7432" width="19.140625" style="214" customWidth="1"/>
+    <col min="7433" max="7434" width="11.42578125" style="214"/>
+    <col min="7435" max="7436" width="4.85546875" style="214" customWidth="1"/>
+    <col min="7437" max="7437" width="10.85546875" style="214" customWidth="1"/>
+    <col min="7438" max="7438" width="11.42578125" style="214"/>
     <col min="7439" max="7439" width="22" style="214" customWidth="1"/>
-    <col min="7440" max="7441" width="11.44140625" style="214"/>
+    <col min="7440" max="7441" width="11.42578125" style="214"/>
     <col min="7442" max="7443" width="6" style="214" customWidth="1"/>
-    <col min="7444" max="7674" width="11.44140625" style="214"/>
+    <col min="7444" max="7674" width="11.42578125" style="214"/>
     <col min="7675" max="7676" width="20" style="214" customWidth="1"/>
-    <col min="7677" max="7677" width="11.44140625" style="214"/>
-    <col min="7678" max="7679" width="6.109375" style="214" customWidth="1"/>
+    <col min="7677" max="7677" width="11.42578125" style="214"/>
+    <col min="7678" max="7679" width="6.140625" style="214" customWidth="1"/>
     <col min="7680" max="7680" width="14" style="214" customWidth="1"/>
-    <col min="7681" max="7681" width="4.44140625" style="214" customWidth="1"/>
-    <col min="7682" max="7682" width="20.88671875" style="214" customWidth="1"/>
-    <col min="7683" max="7684" width="11.44140625" style="214"/>
-    <col min="7685" max="7686" width="4.109375" style="214" customWidth="1"/>
-    <col min="7687" max="7687" width="11.44140625" style="214"/>
-    <col min="7688" max="7688" width="19.109375" style="214" customWidth="1"/>
-    <col min="7689" max="7690" width="11.44140625" style="214"/>
-    <col min="7691" max="7692" width="4.88671875" style="214" customWidth="1"/>
-    <col min="7693" max="7693" width="10.88671875" style="214" customWidth="1"/>
-    <col min="7694" max="7694" width="11.44140625" style="214"/>
+    <col min="7681" max="7681" width="4.42578125" style="214" customWidth="1"/>
+    <col min="7682" max="7682" width="20.85546875" style="214" customWidth="1"/>
+    <col min="7683" max="7684" width="11.42578125" style="214"/>
+    <col min="7685" max="7686" width="4.140625" style="214" customWidth="1"/>
+    <col min="7687" max="7687" width="11.42578125" style="214"/>
+    <col min="7688" max="7688" width="19.140625" style="214" customWidth="1"/>
+    <col min="7689" max="7690" width="11.42578125" style="214"/>
+    <col min="7691" max="7692" width="4.85546875" style="214" customWidth="1"/>
+    <col min="7693" max="7693" width="10.85546875" style="214" customWidth="1"/>
+    <col min="7694" max="7694" width="11.42578125" style="214"/>
     <col min="7695" max="7695" width="22" style="214" customWidth="1"/>
-    <col min="7696" max="7697" width="11.44140625" style="214"/>
+    <col min="7696" max="7697" width="11.42578125" style="214"/>
     <col min="7698" max="7699" width="6" style="214" customWidth="1"/>
-    <col min="7700" max="7930" width="11.44140625" style="214"/>
+    <col min="7700" max="7930" width="11.42578125" style="214"/>
     <col min="7931" max="7932" width="20" style="214" customWidth="1"/>
-    <col min="7933" max="7933" width="11.44140625" style="214"/>
-    <col min="7934" max="7935" width="6.109375" style="214" customWidth="1"/>
+    <col min="7933" max="7933" width="11.42578125" style="214"/>
+    <col min="7934" max="7935" width="6.140625" style="214" customWidth="1"/>
     <col min="7936" max="7936" width="14" style="214" customWidth="1"/>
-    <col min="7937" max="7937" width="4.44140625" style="214" customWidth="1"/>
-    <col min="7938" max="7938" width="20.88671875" style="214" customWidth="1"/>
-    <col min="7939" max="7940" width="11.44140625" style="214"/>
-    <col min="7941" max="7942" width="4.109375" style="214" customWidth="1"/>
-    <col min="7943" max="7943" width="11.44140625" style="214"/>
-    <col min="7944" max="7944" width="19.109375" style="214" customWidth="1"/>
-    <col min="7945" max="7946" width="11.44140625" style="214"/>
-    <col min="7947" max="7948" width="4.88671875" style="214" customWidth="1"/>
-    <col min="7949" max="7949" width="10.88671875" style="214" customWidth="1"/>
-    <col min="7950" max="7950" width="11.44140625" style="214"/>
+    <col min="7937" max="7937" width="4.42578125" style="214" customWidth="1"/>
+    <col min="7938" max="7938" width="20.85546875" style="214" customWidth="1"/>
+    <col min="7939" max="7940" width="11.42578125" style="214"/>
+    <col min="7941" max="7942" width="4.140625" style="214" customWidth="1"/>
+    <col min="7943" max="7943" width="11.42578125" style="214"/>
+    <col min="7944" max="7944" width="19.140625" style="214" customWidth="1"/>
+    <col min="7945" max="7946" width="11.42578125" style="214"/>
+    <col min="7947" max="7948" width="4.85546875" style="214" customWidth="1"/>
+    <col min="7949" max="7949" width="10.85546875" style="214" customWidth="1"/>
+    <col min="7950" max="7950" width="11.42578125" style="214"/>
     <col min="7951" max="7951" width="22" style="214" customWidth="1"/>
-    <col min="7952" max="7953" width="11.44140625" style="214"/>
+    <col min="7952" max="7953" width="11.42578125" style="214"/>
     <col min="7954" max="7955" width="6" style="214" customWidth="1"/>
-    <col min="7956" max="8186" width="11.44140625" style="214"/>
+    <col min="7956" max="8186" width="11.42578125" style="214"/>
     <col min="8187" max="8188" width="20" style="214" customWidth="1"/>
-    <col min="8189" max="8189" width="11.44140625" style="214"/>
-    <col min="8190" max="8191" width="6.109375" style="214" customWidth="1"/>
+    <col min="8189" max="8189" width="11.42578125" style="214"/>
+    <col min="8190" max="8191" width="6.140625" style="214" customWidth="1"/>
     <col min="8192" max="8192" width="14" style="214" customWidth="1"/>
-    <col min="8193" max="8193" width="4.44140625" style="214" customWidth="1"/>
-    <col min="8194" max="8194" width="20.88671875" style="214" customWidth="1"/>
-    <col min="8195" max="8196" width="11.44140625" style="214"/>
-    <col min="8197" max="8198" width="4.109375" style="214" customWidth="1"/>
-    <col min="8199" max="8199" width="11.44140625" style="214"/>
-    <col min="8200" max="8200" width="19.109375" style="214" customWidth="1"/>
-    <col min="8201" max="8202" width="11.44140625" style="214"/>
-    <col min="8203" max="8204" width="4.88671875" style="214" customWidth="1"/>
-    <col min="8205" max="8205" width="10.88671875" style="214" customWidth="1"/>
-    <col min="8206" max="8206" width="11.44140625" style="214"/>
+    <col min="8193" max="8193" width="4.42578125" style="214" customWidth="1"/>
+    <col min="8194" max="8194" width="20.85546875" style="214" customWidth="1"/>
+    <col min="8195" max="8196" width="11.42578125" style="214"/>
+    <col min="8197" max="8198" width="4.140625" style="214" customWidth="1"/>
+    <col min="8199" max="8199" width="11.42578125" style="214"/>
+    <col min="8200" max="8200" width="19.140625" style="214" customWidth="1"/>
+    <col min="8201" max="8202" width="11.42578125" style="214"/>
+    <col min="8203" max="8204" width="4.85546875" style="214" customWidth="1"/>
+    <col min="8205" max="8205" width="10.85546875" style="214" customWidth="1"/>
+    <col min="8206" max="8206" width="11.42578125" style="214"/>
     <col min="8207" max="8207" width="22" style="214" customWidth="1"/>
-    <col min="8208" max="8209" width="11.44140625" style="214"/>
+    <col min="8208" max="8209" width="11.42578125" style="214"/>
     <col min="8210" max="8211" width="6" style="214" customWidth="1"/>
-    <col min="8212" max="8442" width="11.44140625" style="214"/>
+    <col min="8212" max="8442" width="11.42578125" style="214"/>
     <col min="8443" max="8444" width="20" style="214" customWidth="1"/>
-    <col min="8445" max="8445" width="11.44140625" style="214"/>
-    <col min="8446" max="8447" width="6.109375" style="214" customWidth="1"/>
+    <col min="8445" max="8445" width="11.42578125" style="214"/>
+    <col min="8446" max="8447" width="6.140625" style="214" customWidth="1"/>
     <col min="8448" max="8448" width="14" style="214" customWidth="1"/>
-    <col min="8449" max="8449" width="4.44140625" style="214" customWidth="1"/>
-    <col min="8450" max="8450" width="20.88671875" style="214" customWidth="1"/>
-    <col min="8451" max="8452" width="11.44140625" style="214"/>
-    <col min="8453" max="8454" width="4.109375" style="214" customWidth="1"/>
-    <col min="8455" max="8455" width="11.44140625" style="214"/>
-    <col min="8456" max="8456" width="19.109375" style="214" customWidth="1"/>
-    <col min="8457" max="8458" width="11.44140625" style="214"/>
-    <col min="8459" max="8460" width="4.88671875" style="214" customWidth="1"/>
-    <col min="8461" max="8461" width="10.88671875" style="214" customWidth="1"/>
-    <col min="8462" max="8462" width="11.44140625" style="214"/>
+    <col min="8449" max="8449" width="4.42578125" style="214" customWidth="1"/>
+    <col min="8450" max="8450" width="20.85546875" style="214" customWidth="1"/>
+    <col min="8451" max="8452" width="11.42578125" style="214"/>
+    <col min="8453" max="8454" width="4.140625" style="214" customWidth="1"/>
+    <col min="8455" max="8455" width="11.42578125" style="214"/>
+    <col min="8456" max="8456" width="19.140625" style="214" customWidth="1"/>
+    <col min="8457" max="8458" width="11.42578125" style="214"/>
+    <col min="8459" max="8460" width="4.85546875" style="214" customWidth="1"/>
+    <col min="8461" max="8461" width="10.85546875" style="214" customWidth="1"/>
+    <col min="8462" max="8462" width="11.42578125" style="214"/>
     <col min="8463" max="8463" width="22" style="214" customWidth="1"/>
-    <col min="8464" max="8465" width="11.44140625" style="214"/>
+    <col min="8464" max="8465" width="11.42578125" style="214"/>
     <col min="8466" max="8467" width="6" style="214" customWidth="1"/>
-    <col min="8468" max="8698" width="11.44140625" style="214"/>
+    <col min="8468" max="8698" width="11.42578125" style="214"/>
     <col min="8699" max="8700" width="20" style="214" customWidth="1"/>
-    <col min="8701" max="8701" width="11.44140625" style="214"/>
-    <col min="8702" max="8703" width="6.109375" style="214" customWidth="1"/>
+    <col min="8701" max="8701" width="11.42578125" style="214"/>
+    <col min="8702" max="8703" width="6.140625" style="214" customWidth="1"/>
     <col min="8704" max="8704" width="14" style="214" customWidth="1"/>
-    <col min="8705" max="8705" width="4.44140625" style="214" customWidth="1"/>
-    <col min="8706" max="8706" width="20.88671875" style="214" customWidth="1"/>
-    <col min="8707" max="8708" width="11.44140625" style="214"/>
-    <col min="8709" max="8710" width="4.109375" style="214" customWidth="1"/>
-    <col min="8711" max="8711" width="11.44140625" style="214"/>
-    <col min="8712" max="8712" width="19.109375" style="214" customWidth="1"/>
-    <col min="8713" max="8714" width="11.44140625" style="214"/>
-    <col min="8715" max="8716" width="4.88671875" style="214" customWidth="1"/>
-    <col min="8717" max="8717" width="10.88671875" style="214" customWidth="1"/>
-    <col min="8718" max="8718" width="11.44140625" style="214"/>
+    <col min="8705" max="8705" width="4.42578125" style="214" customWidth="1"/>
+    <col min="8706" max="8706" width="20.85546875" style="214" customWidth="1"/>
+    <col min="8707" max="8708" width="11.42578125" style="214"/>
+    <col min="8709" max="8710" width="4.140625" style="214" customWidth="1"/>
+    <col min="8711" max="8711" width="11.42578125" style="214"/>
+    <col min="8712" max="8712" width="19.140625" style="214" customWidth="1"/>
+    <col min="8713" max="8714" width="11.42578125" style="214"/>
+    <col min="8715" max="8716" width="4.85546875" style="214" customWidth="1"/>
+    <col min="8717" max="8717" width="10.85546875" style="214" customWidth="1"/>
+    <col min="8718" max="8718" width="11.42578125" style="214"/>
     <col min="8719" max="8719" width="22" style="214" customWidth="1"/>
-    <col min="8720" max="8721" width="11.44140625" style="214"/>
+    <col min="8720" max="8721" width="11.42578125" style="214"/>
     <col min="8722" max="8723" width="6" style="214" customWidth="1"/>
-    <col min="8724" max="8954" width="11.44140625" style="214"/>
+    <col min="8724" max="8954" width="11.42578125" style="214"/>
     <col min="8955" max="8956" width="20" style="214" customWidth="1"/>
-    <col min="8957" max="8957" width="11.44140625" style="214"/>
-    <col min="8958" max="8959" width="6.109375" style="214" customWidth="1"/>
+    <col min="8957" max="8957" width="11.42578125" style="214"/>
+    <col min="8958" max="8959" width="6.140625" style="214" customWidth="1"/>
     <col min="8960" max="8960" width="14" style="214" customWidth="1"/>
-    <col min="8961" max="8961" width="4.44140625" style="214" customWidth="1"/>
-    <col min="8962" max="8962" width="20.88671875" style="214" customWidth="1"/>
-    <col min="8963" max="8964" width="11.44140625" style="214"/>
-    <col min="8965" max="8966" width="4.109375" style="214" customWidth="1"/>
-    <col min="8967" max="8967" width="11.44140625" style="214"/>
-    <col min="8968" max="8968" width="19.109375" style="214" customWidth="1"/>
-    <col min="8969" max="8970" width="11.44140625" style="214"/>
-    <col min="8971" max="8972" width="4.88671875" style="214" customWidth="1"/>
-    <col min="8973" max="8973" width="10.88671875" style="214" customWidth="1"/>
-    <col min="8974" max="8974" width="11.44140625" style="214"/>
+    <col min="8961" max="8961" width="4.42578125" style="214" customWidth="1"/>
+    <col min="8962" max="8962" width="20.85546875" style="214" customWidth="1"/>
+    <col min="8963" max="8964" width="11.42578125" style="214"/>
+    <col min="8965" max="8966" width="4.140625" style="214" customWidth="1"/>
+    <col min="8967" max="8967" width="11.42578125" style="214"/>
+    <col min="8968" max="8968" width="19.140625" style="214" customWidth="1"/>
+    <col min="8969" max="8970" width="11.42578125" style="214"/>
+    <col min="8971" max="8972" width="4.85546875" style="214" customWidth="1"/>
+    <col min="8973" max="8973" width="10.85546875" style="214" customWidth="1"/>
+    <col min="8974" max="8974" width="11.42578125" style="214"/>
     <col min="8975" max="8975" width="22" style="214" customWidth="1"/>
-    <col min="8976" max="8977" width="11.44140625" style="214"/>
+    <col min="8976" max="8977" width="11.42578125" style="214"/>
     <col min="8978" max="8979" width="6" style="214" customWidth="1"/>
-    <col min="8980" max="9210" width="11.44140625" style="214"/>
+    <col min="8980" max="9210" width="11.42578125" style="214"/>
     <col min="9211" max="9212" width="20" style="214" customWidth="1"/>
-    <col min="9213" max="9213" width="11.44140625" style="214"/>
-    <col min="9214" max="9215" width="6.109375" style="214" customWidth="1"/>
+    <col min="9213" max="9213" width="11.42578125" style="214"/>
+    <col min="9214" max="9215" width="6.140625" style="214" customWidth="1"/>
     <col min="9216" max="9216" width="14" style="214" customWidth="1"/>
-    <col min="9217" max="9217" width="4.44140625" style="214" customWidth="1"/>
-    <col min="9218" max="9218" width="20.88671875" style="214" customWidth="1"/>
-    <col min="9219" max="9220" width="11.44140625" style="214"/>
-    <col min="9221" max="9222" width="4.109375" style="214" customWidth="1"/>
-    <col min="9223" max="9223" width="11.44140625" style="214"/>
-    <col min="9224" max="9224" width="19.109375" style="214" customWidth="1"/>
-    <col min="9225" max="9226" width="11.44140625" style="214"/>
-    <col min="9227" max="9228" width="4.88671875" style="214" customWidth="1"/>
-    <col min="9229" max="9229" width="10.88671875" style="214" customWidth="1"/>
-    <col min="9230" max="9230" width="11.44140625" style="214"/>
+    <col min="9217" max="9217" width="4.42578125" style="214" customWidth="1"/>
+    <col min="9218" max="9218" width="20.85546875" style="214" customWidth="1"/>
+    <col min="9219" max="9220" width="11.42578125" style="214"/>
+    <col min="9221" max="9222" width="4.140625" style="214" customWidth="1"/>
+    <col min="9223" max="9223" width="11.42578125" style="214"/>
+    <col min="9224" max="9224" width="19.140625" style="214" customWidth="1"/>
+    <col min="9225" max="9226" width="11.42578125" style="214"/>
+    <col min="9227" max="9228" width="4.85546875" style="214" customWidth="1"/>
+    <col min="9229" max="9229" width="10.85546875" style="214" customWidth="1"/>
+    <col min="9230" max="9230" width="11.42578125" style="214"/>
     <col min="9231" max="9231" width="22" style="214" customWidth="1"/>
-    <col min="9232" max="9233" width="11.44140625" style="214"/>
+    <col min="9232" max="9233" width="11.42578125" style="214"/>
     <col min="9234" max="9235" width="6" style="214" customWidth="1"/>
-    <col min="9236" max="9466" width="11.44140625" style="214"/>
+    <col min="9236" max="9466" width="11.42578125" style="214"/>
     <col min="9467" max="9468" width="20" style="214" customWidth="1"/>
-    <col min="9469" max="9469" width="11.44140625" style="214"/>
-    <col min="9470" max="9471" width="6.109375" style="214" customWidth="1"/>
+    <col min="9469" max="9469" width="11.42578125" style="214"/>
+    <col min="9470" max="9471" width="6.140625" style="214" customWidth="1"/>
     <col min="9472" max="9472" width="14" style="214" customWidth="1"/>
-    <col min="9473" max="9473" width="4.44140625" style="214" customWidth="1"/>
-    <col min="9474" max="9474" width="20.88671875" style="214" customWidth="1"/>
-    <col min="9475" max="9476" width="11.44140625" style="214"/>
-    <col min="9477" max="9478" width="4.109375" style="214" customWidth="1"/>
-    <col min="9479" max="9479" width="11.44140625" style="214"/>
-    <col min="9480" max="9480" width="19.109375" style="214" customWidth="1"/>
-    <col min="9481" max="9482" width="11.44140625" style="214"/>
-    <col min="9483" max="9484" width="4.88671875" style="214" customWidth="1"/>
-    <col min="9485" max="9485" width="10.88671875" style="214" customWidth="1"/>
-    <col min="9486" max="9486" width="11.44140625" style="214"/>
+    <col min="9473" max="9473" width="4.42578125" style="214" customWidth="1"/>
+    <col min="9474" max="9474" width="20.85546875" style="214" customWidth="1"/>
+    <col min="9475" max="9476" width="11.42578125" style="214"/>
+    <col min="9477" max="9478" width="4.140625" style="214" customWidth="1"/>
+    <col min="9479" max="9479" width="11.42578125" style="214"/>
+    <col min="9480" max="9480" width="19.140625" style="214" customWidth="1"/>
+    <col min="9481" max="9482" width="11.42578125" style="214"/>
+    <col min="9483" max="9484" width="4.85546875" style="214" customWidth="1"/>
+    <col min="9485" max="9485" width="10.85546875" style="214" customWidth="1"/>
+    <col min="9486" max="9486" width="11.42578125" style="214"/>
     <col min="9487" max="9487" width="22" style="214" customWidth="1"/>
-    <col min="9488" max="9489" width="11.44140625" style="214"/>
+    <col min="9488" max="9489" width="11.42578125" style="214"/>
     <col min="9490" max="9491" width="6" style="214" customWidth="1"/>
-    <col min="9492" max="9722" width="11.44140625" style="214"/>
+    <col min="9492" max="9722" width="11.42578125" style="214"/>
     <col min="9723" max="9724" width="20" style="214" customWidth="1"/>
-    <col min="9725" max="9725" width="11.44140625" style="214"/>
-    <col min="9726" max="9727" width="6.109375" style="214" customWidth="1"/>
+    <col min="9725" max="9725" width="11.42578125" style="214"/>
+    <col min="9726" max="9727" width="6.140625" style="214" customWidth="1"/>
     <col min="9728" max="9728" width="14" style="214" customWidth="1"/>
-    <col min="9729" max="9729" width="4.44140625" style="214" customWidth="1"/>
-    <col min="9730" max="9730" width="20.88671875" style="214" customWidth="1"/>
-    <col min="9731" max="9732" width="11.44140625" style="214"/>
-    <col min="9733" max="9734" width="4.109375" style="214" customWidth="1"/>
-    <col min="9735" max="9735" width="11.44140625" style="214"/>
-    <col min="9736" max="9736" width="19.109375" style="214" customWidth="1"/>
-    <col min="9737" max="9738" width="11.44140625" style="214"/>
-    <col min="9739" max="9740" width="4.88671875" style="214" customWidth="1"/>
-    <col min="9741" max="9741" width="10.88671875" style="214" customWidth="1"/>
-    <col min="9742" max="9742" width="11.44140625" style="214"/>
+    <col min="9729" max="9729" width="4.42578125" style="214" customWidth="1"/>
+    <col min="9730" max="9730" width="20.85546875" style="214" customWidth="1"/>
+    <col min="9731" max="9732" width="11.42578125" style="214"/>
+    <col min="9733" max="9734" width="4.140625" style="214" customWidth="1"/>
+    <col min="9735" max="9735" width="11.42578125" style="214"/>
+    <col min="9736" max="9736" width="19.140625" style="214" customWidth="1"/>
+    <col min="9737" max="9738" width="11.42578125" style="214"/>
+    <col min="9739" max="9740" width="4.85546875" style="214" customWidth="1"/>
+    <col min="9741" max="9741" width="10.85546875" style="214" customWidth="1"/>
+    <col min="9742" max="9742" width="11.42578125" style="214"/>
     <col min="9743" max="9743" width="22" style="214" customWidth="1"/>
-    <col min="9744" max="9745" width="11.44140625" style="214"/>
+    <col min="9744" max="9745" width="11.42578125" style="214"/>
     <col min="9746" max="9747" width="6" style="214" customWidth="1"/>
-    <col min="9748" max="9978" width="11.44140625" style="214"/>
+    <col min="9748" max="9978" width="11.42578125" style="214"/>
     <col min="9979" max="9980" width="20" style="214" customWidth="1"/>
-    <col min="9981" max="9981" width="11.44140625" style="214"/>
-    <col min="9982" max="9983" width="6.109375" style="214" customWidth="1"/>
+    <col min="9981" max="9981" width="11.42578125" style="214"/>
+    <col min="9982" max="9983" width="6.140625" style="214" customWidth="1"/>
     <col min="9984" max="9984" width="14" style="214" customWidth="1"/>
-    <col min="9985" max="9985" width="4.44140625" style="214" customWidth="1"/>
-    <col min="9986" max="9986" width="20.88671875" style="214" customWidth="1"/>
-    <col min="9987" max="9988" width="11.44140625" style="214"/>
-    <col min="9989" max="9990" width="4.109375" style="214" customWidth="1"/>
-    <col min="9991" max="9991" width="11.44140625" style="214"/>
-    <col min="9992" max="9992" width="19.109375" style="214" customWidth="1"/>
-    <col min="9993" max="9994" width="11.44140625" style="214"/>
-    <col min="9995" max="9996" width="4.88671875" style="214" customWidth="1"/>
-    <col min="9997" max="9997" width="10.88671875" style="214" customWidth="1"/>
-    <col min="9998" max="9998" width="11.44140625" style="214"/>
+    <col min="9985" max="9985" width="4.42578125" style="214" customWidth="1"/>
+    <col min="9986" max="9986" width="20.85546875" style="214" customWidth="1"/>
+    <col min="9987" max="9988" width="11.42578125" style="214"/>
+    <col min="9989" max="9990" width="4.140625" style="214" customWidth="1"/>
+    <col min="9991" max="9991" width="11.42578125" style="214"/>
+    <col min="9992" max="9992" width="19.140625" style="214" customWidth="1"/>
+    <col min="9993" max="9994" width="11.42578125" style="214"/>
+    <col min="9995" max="9996" width="4.85546875" style="214" customWidth="1"/>
+    <col min="9997" max="9997" width="10.85546875" style="214" customWidth="1"/>
+    <col min="9998" max="9998" width="11.42578125" style="214"/>
     <col min="9999" max="9999" width="22" style="214" customWidth="1"/>
-    <col min="10000" max="10001" width="11.44140625" style="214"/>
+    <col min="10000" max="10001" width="11.42578125" style="214"/>
     <col min="10002" max="10003" width="6" style="214" customWidth="1"/>
-    <col min="10004" max="10234" width="11.44140625" style="214"/>
+    <col min="10004" max="10234" width="11.42578125" style="214"/>
     <col min="10235" max="10236" width="20" style="214" customWidth="1"/>
-    <col min="10237" max="10237" width="11.44140625" style="214"/>
-    <col min="10238" max="10239" width="6.109375" style="214" customWidth="1"/>
+    <col min="10237" max="10237" width="11.42578125" style="214"/>
+    <col min="10238" max="10239" width="6.140625" style="214" customWidth="1"/>
     <col min="10240" max="10240" width="14" style="214" customWidth="1"/>
-    <col min="10241" max="10241" width="4.44140625" style="214" customWidth="1"/>
-    <col min="10242" max="10242" width="20.88671875" style="214" customWidth="1"/>
-    <col min="10243" max="10244" width="11.44140625" style="214"/>
-    <col min="10245" max="10246" width="4.109375" style="214" customWidth="1"/>
-    <col min="10247" max="10247" width="11.44140625" style="214"/>
-    <col min="10248" max="10248" width="19.109375" style="214" customWidth="1"/>
-    <col min="10249" max="10250" width="11.44140625" style="214"/>
-    <col min="10251" max="10252" width="4.88671875" style="214" customWidth="1"/>
-    <col min="10253" max="10253" width="10.88671875" style="214" customWidth="1"/>
-    <col min="10254" max="10254" width="11.44140625" style="214"/>
+    <col min="10241" max="10241" width="4.42578125" style="214" customWidth="1"/>
+    <col min="10242" max="10242" width="20.85546875" style="214" customWidth="1"/>
+    <col min="10243" max="10244" width="11.42578125" style="214"/>
+    <col min="10245" max="10246" width="4.140625" style="214" customWidth="1"/>
+    <col min="10247" max="10247" width="11.42578125" style="214"/>
+    <col min="10248" max="10248" width="19.140625" style="214" customWidth="1"/>
+    <col min="10249" max="10250" width="11.42578125" style="214"/>
+    <col min="10251" max="10252" width="4.85546875" style="214" customWidth="1"/>
+    <col min="10253" max="10253" width="10.85546875" style="214" customWidth="1"/>
+    <col min="10254" max="10254" width="11.42578125" style="214"/>
     <col min="10255" max="10255" width="22" style="214" customWidth="1"/>
-    <col min="10256" max="10257" width="11.44140625" style="214"/>
+    <col min="10256" max="10257" width="11.42578125" style="214"/>
     <col min="10258" max="10259" width="6" style="214" customWidth="1"/>
-    <col min="10260" max="10490" width="11.44140625" style="214"/>
+    <col min="10260" max="10490" width="11.42578125" style="214"/>
     <col min="10491" max="10492" width="20" style="214" customWidth="1"/>
-    <col min="10493" max="10493" width="11.44140625" style="214"/>
-    <col min="10494" max="10495" width="6.109375" style="214" customWidth="1"/>
+    <col min="10493" max="10493" width="11.42578125" style="214"/>
+    <col min="10494" max="10495" width="6.140625" style="214" customWidth="1"/>
     <col min="10496" max="10496" width="14" style="214" customWidth="1"/>
-    <col min="10497" max="10497" width="4.44140625" style="214" customWidth="1"/>
-    <col min="10498" max="10498" width="20.88671875" style="214" customWidth="1"/>
-    <col min="10499" max="10500" width="11.44140625" style="214"/>
-    <col min="10501" max="10502" width="4.109375" style="214" customWidth="1"/>
-    <col min="10503" max="10503" width="11.44140625" style="214"/>
-    <col min="10504" max="10504" width="19.109375" style="214" customWidth="1"/>
-    <col min="10505" max="10506" width="11.44140625" style="214"/>
-    <col min="10507" max="10508" width="4.88671875" style="214" customWidth="1"/>
-    <col min="10509" max="10509" width="10.88671875" style="214" customWidth="1"/>
-    <col min="10510" max="10510" width="11.44140625" style="214"/>
+    <col min="10497" max="10497" width="4.42578125" style="214" customWidth="1"/>
+    <col min="10498" max="10498" width="20.85546875" style="214" customWidth="1"/>
+    <col min="10499" max="10500" width="11.42578125" style="214"/>
+    <col min="10501" max="10502" width="4.140625" style="214" customWidth="1"/>
+    <col min="10503" max="10503" width="11.42578125" style="214"/>
+    <col min="10504" max="10504" width="19.140625" style="214" customWidth="1"/>
+    <col min="10505" max="10506" width="11.42578125" style="214"/>
+    <col min="10507" max="10508" width="4.85546875" style="214" customWidth="1"/>
+    <col min="10509" max="10509" width="10.85546875" style="214" customWidth="1"/>
+    <col min="10510" max="10510" width="11.42578125" style="214"/>
     <col min="10511" max="10511" width="22" style="214" customWidth="1"/>
-    <col min="10512" max="10513" width="11.44140625" style="214"/>
+    <col min="10512" max="10513" width="11.42578125" style="214"/>
     <col min="10514" max="10515" width="6" style="214" customWidth="1"/>
-    <col min="10516" max="10746" width="11.44140625" style="214"/>
+    <col min="10516" max="10746" width="11.42578125" style="214"/>
     <col min="10747" max="10748" width="20" style="214" customWidth="1"/>
-    <col min="10749" max="10749" width="11.44140625" style="214"/>
-    <col min="10750" max="10751" width="6.109375" style="214" customWidth="1"/>
+    <col min="10749" max="10749" width="11.42578125" style="214"/>
+    <col min="10750" max="10751" width="6.140625" style="214" customWidth="1"/>
     <col min="10752" max="10752" width="14" style="214" customWidth="1"/>
-    <col min="10753" max="10753" width="4.44140625" style="214" customWidth="1"/>
-    <col min="10754" max="10754" width="20.88671875" style="214" customWidth="1"/>
-    <col min="10755" max="10756" width="11.44140625" style="214"/>
-    <col min="10757" max="10758" width="4.109375" style="214" customWidth="1"/>
-    <col min="10759" max="10759" width="11.44140625" style="214"/>
-    <col min="10760" max="10760" width="19.109375" style="214" customWidth="1"/>
-    <col min="10761" max="10762" width="11.44140625" style="214"/>
-    <col min="10763" max="10764" width="4.88671875" style="214" customWidth="1"/>
-    <col min="10765" max="10765" width="10.88671875" style="214" customWidth="1"/>
-    <col min="10766" max="10766" width="11.44140625" style="214"/>
+    <col min="10753" max="10753" width="4.42578125" style="214" customWidth="1"/>
+    <col min="10754" max="10754" width="20.85546875" style="214" customWidth="1"/>
+    <col min="10755" max="10756" width="11.42578125" style="214"/>
+    <col min="10757" max="10758" width="4.140625" style="214" customWidth="1"/>
+    <col min="10759" max="10759" width="11.42578125" style="214"/>
+    <col min="10760" max="10760" width="19.140625" style="214" customWidth="1"/>
+    <col min="10761" max="10762" width="11.42578125" style="214"/>
+    <col min="10763" max="10764" width="4.85546875" style="214" customWidth="1"/>
+    <col min="10765" max="10765" width="10.85546875" style="214" customWidth="1"/>
+    <col min="10766" max="10766" width="11.42578125" style="214"/>
     <col min="10767" max="10767" width="22" style="214" customWidth="1"/>
-    <col min="10768" max="10769" width="11.44140625" style="214"/>
+    <col min="10768" max="10769" width="11.42578125" style="214"/>
     <col min="10770" max="10771" width="6" style="214" customWidth="1"/>
-    <col min="10772" max="11002" width="11.44140625" style="214"/>
+    <col min="10772" max="11002" width="11.42578125" style="214"/>
     <col min="11003" max="11004" width="20" style="214" customWidth="1"/>
-    <col min="11005" max="11005" width="11.44140625" style="214"/>
-    <col min="11006" max="11007" width="6.109375" style="214" customWidth="1"/>
+    <col min="11005" max="11005" width="11.42578125" style="214"/>
+    <col min="11006" max="11007" width="6.140625" style="214" customWidth="1"/>
     <col min="11008" max="11008" width="14" style="214" customWidth="1"/>
-    <col min="11009" max="11009" width="4.44140625" style="214" customWidth="1"/>
-    <col min="11010" max="11010" width="20.88671875" style="214" customWidth="1"/>
-    <col min="11011" max="11012" width="11.44140625" style="214"/>
-    <col min="11013" max="11014" width="4.109375" style="214" customWidth="1"/>
-    <col min="11015" max="11015" width="11.44140625" style="214"/>
-    <col min="11016" max="11016" width="19.109375" style="214" customWidth="1"/>
-    <col min="11017" max="11018" width="11.44140625" style="214"/>
-    <col min="11019" max="11020" width="4.88671875" style="214" customWidth="1"/>
-    <col min="11021" max="11021" width="10.88671875" style="214" customWidth="1"/>
-    <col min="11022" max="11022" width="11.44140625" style="214"/>
+    <col min="11009" max="11009" width="4.42578125" style="214" customWidth="1"/>
+    <col min="11010" max="11010" width="20.85546875" style="214" customWidth="1"/>
+    <col min="11011" max="11012" width="11.42578125" style="214"/>
+    <col min="11013" max="11014" width="4.140625" style="214" customWidth="1"/>
+    <col min="11015" max="11015" width="11.42578125" style="214"/>
+    <col min="11016" max="11016" width="19.140625" style="214" customWidth="1"/>
+    <col min="11017" max="11018" width="11.42578125" style="214"/>
+    <col min="11019" max="11020" width="4.85546875" style="214" customWidth="1"/>
+    <col min="11021" max="11021" width="10.85546875" style="214" customWidth="1"/>
+    <col min="11022" max="11022" width="11.42578125" style="214"/>
     <col min="11023" max="11023" width="22" style="214" customWidth="1"/>
-    <col min="11024" max="11025" width="11.44140625" style="214"/>
+    <col min="11024" max="11025" width="11.42578125" style="214"/>
     <col min="11026" max="11027" width="6" style="214" customWidth="1"/>
-    <col min="11028" max="11258" width="11.44140625" style="214"/>
+    <col min="11028" max="11258" width="11.42578125" style="214"/>
     <col min="11259" max="11260" width="20" style="214" customWidth="1"/>
-    <col min="11261" max="11261" width="11.44140625" style="214"/>
-    <col min="11262" max="11263" width="6.109375" style="214" customWidth="1"/>
+    <col min="11261" max="11261" width="11.42578125" style="214"/>
+    <col min="11262" max="11263" width="6.140625" style="214" customWidth="1"/>
     <col min="11264" max="11264" width="14" style="214" customWidth="1"/>
-    <col min="11265" max="11265" width="4.44140625" style="214" customWidth="1"/>
-    <col min="11266" max="11266" width="20.88671875" style="214" customWidth="1"/>
-    <col min="11267" max="11268" width="11.44140625" style="214"/>
-    <col min="11269" max="11270" width="4.109375" style="214" customWidth="1"/>
-    <col min="11271" max="11271" width="11.44140625" style="214"/>
-    <col min="11272" max="11272" width="19.109375" style="214" customWidth="1"/>
-    <col min="11273" max="11274" width="11.44140625" style="214"/>
-    <col min="11275" max="11276" width="4.88671875" style="214" customWidth="1"/>
-    <col min="11277" max="11277" width="10.88671875" style="214" customWidth="1"/>
-    <col min="11278" max="11278" width="11.44140625" style="214"/>
+    <col min="11265" max="11265" width="4.42578125" style="214" customWidth="1"/>
+    <col min="11266" max="11266" width="20.85546875" style="214" customWidth="1"/>
+    <col min="11267" max="11268" width="11.42578125" style="214"/>
+    <col min="11269" max="11270" width="4.140625" style="214" customWidth="1"/>
+    <col min="11271" max="11271" width="11.42578125" style="214"/>
+    <col min="11272" max="11272" width="19.140625" style="214" customWidth="1"/>
+    <col min="11273" max="11274" width="11.42578125" style="214"/>
+    <col min="11275" max="11276" width="4.85546875" style="214" customWidth="1"/>
+    <col min="11277" max="11277" width="10.85546875" style="214" customWidth="1"/>
+    <col min="11278" max="11278" width="11.42578125" style="214"/>
     <col min="11279" max="11279" width="22" style="214" customWidth="1"/>
-    <col min="11280" max="11281" width="11.44140625" style="214"/>
+    <col min="11280" max="11281" width="11.42578125" style="214"/>
     <col min="11282" max="11283" width="6" style="214" customWidth="1"/>
-    <col min="11284" max="11514" width="11.44140625" style="214"/>
+    <col min="11284" max="11514" width="11.42578125" style="214"/>
     <col min="11515" max="11516" width="20" style="214" customWidth="1"/>
-    <col min="11517" max="11517" width="11.44140625" style="214"/>
-    <col min="11518" max="11519" width="6.109375" style="214" customWidth="1"/>
+    <col min="11517" max="11517" width="11.42578125" style="214"/>
+    <col min="11518" max="11519" width="6.140625" style="214" customWidth="1"/>
     <col min="11520" max="11520" width="14" style="214" customWidth="1"/>
-    <col min="11521" max="11521" width="4.44140625" style="214" customWidth="1"/>
-    <col min="11522" max="11522" width="20.88671875" style="214" customWidth="1"/>
-    <col min="11523" max="11524" width="11.44140625" style="214"/>
-    <col min="11525" max="11526" width="4.109375" style="214" customWidth="1"/>
-    <col min="11527" max="11527" width="11.44140625" style="214"/>
-    <col min="11528" max="11528" width="19.109375" style="214" customWidth="1"/>
-    <col min="11529" max="11530" width="11.44140625" style="214"/>
-    <col min="11531" max="11532" width="4.88671875" style="214" customWidth="1"/>
-    <col min="11533" max="11533" width="10.88671875" style="214" customWidth="1"/>
-    <col min="11534" max="11534" width="11.44140625" style="214"/>
+    <col min="11521" max="11521" width="4.42578125" style="214" customWidth="1"/>
+    <col min="11522" max="11522" width="20.85546875" style="214" customWidth="1"/>
+    <col min="11523" max="11524" width="11.42578125" style="214"/>
+    <col min="11525" max="11526" width="4.140625" style="214" customWidth="1"/>
+    <col min="11527" max="11527" width="11.42578125" style="214"/>
+    <col min="11528" max="11528" width="19.140625" style="214" customWidth="1"/>
+    <col min="11529" max="11530" width="11.42578125" style="214"/>
+    <col min="11531" max="11532" width="4.85546875" style="214" customWidth="1"/>
+    <col min="11533" max="11533" width="10.85546875" style="214" customWidth="1"/>
+    <col min="11534" max="11534" width="11.42578125" style="214"/>
     <col min="11535" max="11535" width="22" style="214" customWidth="1"/>
-    <col min="11536" max="11537" width="11.44140625" style="214"/>
+    <col min="11536" max="11537" width="11.42578125" style="214"/>
     <col min="11538" max="11539" width="6" style="214" customWidth="1"/>
-    <col min="11540" max="11770" width="11.44140625" style="214"/>
+    <col min="11540" max="11770" width="11.42578125" style="214"/>
     <col min="11771" max="11772" width="20" style="214" customWidth="1"/>
-    <col min="11773" max="11773" width="11.44140625" style="214"/>
-    <col min="11774" max="11775" width="6.109375" style="214" customWidth="1"/>
+    <col min="11773" max="11773" width="11.42578125" style="214"/>
+    <col min="11774" max="11775" width="6.140625" style="214" customWidth="1"/>
     <col min="11776" max="11776" width="14" style="214" customWidth="1"/>
-    <col min="11777" max="11777" width="4.44140625" style="214" customWidth="1"/>
-    <col min="11778" max="11778" width="20.88671875" style="214" customWidth="1"/>
-    <col min="11779" max="11780" width="11.44140625" style="214"/>
-    <col min="11781" max="11782" width="4.109375" style="214" customWidth="1"/>
-    <col min="11783" max="11783" width="11.44140625" style="214"/>
-    <col min="11784" max="11784" width="19.109375" style="214" customWidth="1"/>
-    <col min="11785" max="11786" width="11.44140625" style="214"/>
-    <col min="11787" max="11788" width="4.88671875" style="214" customWidth="1"/>
-    <col min="11789" max="11789" width="10.88671875" style="214" customWidth="1"/>
-    <col min="11790" max="11790" width="11.44140625" style="214"/>
+    <col min="11777" max="11777" width="4.42578125" style="214" customWidth="1"/>
+    <col min="11778" max="11778" width="20.85546875" style="214" customWidth="1"/>
+    <col min="11779" max="11780" width="11.42578125" style="214"/>
+    <col min="11781" max="11782" width="4.140625" style="214" customWidth="1"/>
+    <col min="11783" max="11783" width="11.42578125" style="214"/>
+    <col min="11784" max="11784" width="19.140625" style="214" customWidth="1"/>
+    <col min="11785" max="11786" width="11.42578125" style="214"/>
+    <col min="11787" max="11788" width="4.85546875" style="214" customWidth="1"/>
+    <col min="11789" max="11789" width="10.85546875" style="214" customWidth="1"/>
+    <col min="11790" max="11790" width="11.42578125" style="214"/>
     <col min="11791" max="11791" width="22" style="214" customWidth="1"/>
-    <col min="11792" max="11793" width="11.44140625" style="214"/>
+    <col min="11792" max="11793" width="11.42578125" style="214"/>
     <col min="11794" max="11795" width="6" style="214" customWidth="1"/>
-    <col min="11796" max="12026" width="11.44140625" style="214"/>
+    <col min="11796" max="12026" width="11.42578125" style="214"/>
     <col min="12027" max="12028" width="20" style="214" customWidth="1"/>
-    <col min="12029" max="12029" width="11.44140625" style="214"/>
-    <col min="12030" max="12031" width="6.109375" style="214" customWidth="1"/>
+    <col min="12029" max="12029" width="11.42578125" style="214"/>
+    <col min="12030" max="12031" width="6.140625" style="214" customWidth="1"/>
     <col min="12032" max="12032" width="14" style="214" customWidth="1"/>
-    <col min="12033" max="12033" width="4.44140625" style="214" customWidth="1"/>
-    <col min="12034" max="12034" width="20.88671875" style="214" customWidth="1"/>
-    <col min="12035" max="12036" width="11.44140625" style="214"/>
-    <col min="12037" max="12038" width="4.109375" style="214" customWidth="1"/>
-    <col min="12039" max="12039" width="11.44140625" style="214"/>
-    <col min="12040" max="12040" width="19.109375" style="214" customWidth="1"/>
-    <col min="12041" max="12042" width="11.44140625" style="214"/>
-    <col min="12043" max="12044" width="4.88671875" style="214" customWidth="1"/>
-    <col min="12045" max="12045" width="10.88671875" style="214" customWidth="1"/>
-    <col min="12046" max="12046" width="11.44140625" style="214"/>
+    <col min="12033" max="12033" width="4.42578125" style="214" customWidth="1"/>
+    <col min="12034" max="12034" width="20.85546875" style="214" customWidth="1"/>
+    <col min="12035" max="12036" width="11.42578125" style="214"/>
+    <col min="12037" max="12038" width="4.140625" style="214" customWidth="1"/>
+    <col min="12039" max="12039" width="11.42578125" style="214"/>
+    <col min="12040" max="12040" width="19.140625" style="214" customWidth="1"/>
+    <col min="12041" max="12042" width="11.42578125" style="214"/>
+    <col min="12043" max="12044" width="4.85546875" style="214" customWidth="1"/>
+    <col min="12045" max="12045" width="10.85546875" style="214" customWidth="1"/>
+    <col min="12046" max="12046" width="11.42578125" style="214"/>
     <col min="12047" max="12047" width="22" style="214" customWidth="1"/>
-    <col min="12048" max="12049" width="11.44140625" style="214"/>
+    <col min="12048" max="12049" width="11.42578125" style="214"/>
     <col min="12050" max="12051" width="6" style="214" customWidth="1"/>
-    <col min="12052" max="12282" width="11.44140625" style="214"/>
+    <col min="12052" max="12282" width="11.42578125" style="214"/>
     <col min="12283" max="12284" width="20" style="214" customWidth="1"/>
-    <col min="12285" max="12285" width="11.44140625" style="214"/>
-    <col min="12286" max="12287" width="6.109375" style="214" customWidth="1"/>
+    <col min="12285" max="12285" width="11.42578125" style="214"/>
+    <col min="12286" max="12287" width="6.140625" style="214" customWidth="1"/>
     <col min="12288" max="12288" width="14" style="214" customWidth="1"/>
-    <col min="12289" max="12289" width="4.44140625" style="214" customWidth="1"/>
-    <col min="12290" max="12290" width="20.88671875" style="214" customWidth="1"/>
-    <col min="12291" max="12292" width="11.44140625" style="214"/>
-    <col min="12293" max="12294" width="4.109375" style="214" customWidth="1"/>
-    <col min="12295" max="12295" width="11.44140625" style="214"/>
-    <col min="12296" max="12296" width="19.109375" style="214" customWidth="1"/>
-    <col min="12297" max="12298" width="11.44140625" style="214"/>
-    <col min="12299" max="12300" width="4.88671875" style="214" customWidth="1"/>
-    <col min="12301" max="12301" width="10.88671875" style="214" customWidth="1"/>
-    <col min="12302" max="12302" width="11.44140625" style="214"/>
+    <col min="12289" max="12289" width="4.42578125" style="214" customWidth="1"/>
+    <col min="12290" max="12290" width="20.85546875" style="214" customWidth="1"/>
+    <col min="12291" max="12292" width="11.42578125" style="214"/>
+    <col min="12293" max="12294" width="4.140625" style="214" customWidth="1"/>
+    <col min="12295" max="12295" width="11.42578125" style="214"/>
+    <col min="12296" max="12296" width="19.140625" style="214" customWidth="1"/>
+    <col min="12297" max="12298" width="11.42578125" style="214"/>
+    <col min="12299" max="12300" width="4.85546875" style="214" customWidth="1"/>
+    <col min="12301" max="12301" width="10.85546875" style="214" customWidth="1"/>
+    <col min="12302" max="12302" width="11.42578125" style="214"/>
     <col min="12303" max="12303" width="22" style="214" customWidth="1"/>
-    <col min="12304" max="12305" width="11.44140625" style="214"/>
+    <col min="12304" max="12305" width="11.42578125" style="214"/>
     <col min="12306" max="12307" width="6" style="214" customWidth="1"/>
-    <col min="12308" max="12538" width="11.44140625" style="214"/>
+    <col min="12308" max="12538" width="11.42578125" style="214"/>
     <col min="12539" max="12540" width="20" style="214" customWidth="1"/>
-    <col min="12541" max="12541" width="11.44140625" style="214"/>
-    <col min="12542" max="12543" width="6.109375" style="214" customWidth="1"/>
+    <col min="12541" max="12541" width="11.42578125" style="214"/>
+    <col min="12542" max="12543" width="6.140625" style="214" customWidth="1"/>
     <col min="12544" max="12544" width="14" style="214" customWidth="1"/>
-    <col min="12545" max="12545" width="4.44140625" style="214" customWidth="1"/>
-    <col min="12546" max="12546" width="20.88671875" style="214" customWidth="1"/>
-    <col min="12547" max="12548" width="11.44140625" style="214"/>
-    <col min="12549" max="12550" width="4.109375" style="214" customWidth="1"/>
-    <col min="12551" max="12551" width="11.44140625" style="214"/>
-    <col min="12552" max="12552" width="19.109375" style="214" customWidth="1"/>
-    <col min="12553" max="12554" width="11.44140625" style="214"/>
-    <col min="12555" max="12556" width="4.88671875" style="214" customWidth="1"/>
-    <col min="12557" max="12557" width="10.88671875" style="214" customWidth="1"/>
-    <col min="12558" max="12558" width="11.44140625" style="214"/>
+    <col min="12545" max="12545" width="4.42578125" style="214" customWidth="1"/>
+    <col min="12546" max="12546" width="20.85546875" style="214" customWidth="1"/>
+    <col min="12547" max="12548" width="11.42578125" style="214"/>
+    <col min="12549" max="12550" width="4.140625" style="214" customWidth="1"/>
+    <col min="12551" max="12551" width="11.42578125" style="214"/>
+    <col min="12552" max="12552" width="19.140625" style="214" customWidth="1"/>
+    <col min="12553" max="12554" width="11.42578125" style="214"/>
+    <col min="12555" max="12556" width="4.85546875" style="214" customWidth="1"/>
+    <col min="12557" max="12557" width="10.85546875" style="214" customWidth="1"/>
+    <col min="12558" max="12558" width="11.42578125" style="214"/>
     <col min="12559" max="12559" width="22" style="214" customWidth="1"/>
-    <col min="12560" max="12561" width="11.44140625" style="214"/>
+    <col min="12560" max="12561" width="11.42578125" style="214"/>
     <col min="12562" max="12563" width="6" style="214" customWidth="1"/>
-    <col min="12564" max="12794" width="11.44140625" style="214"/>
+    <col min="12564" max="12794" width="11.42578125" style="214"/>
     <col min="12795" max="12796" width="20" style="214" customWidth="1"/>
-    <col min="12797" max="12797" width="11.44140625" style="214"/>
-    <col min="12798" max="12799" width="6.109375" style="214" customWidth="1"/>
+    <col min="12797" max="12797" width="11.42578125" style="214"/>
+    <col min="12798" max="12799" width="6.140625" style="214" customWidth="1"/>
     <col min="12800" max="12800" width="14" style="214" customWidth="1"/>
-    <col min="12801" max="12801" width="4.44140625" style="214" customWidth="1"/>
-    <col min="12802" max="12802" width="20.88671875" style="214" customWidth="1"/>
-    <col min="12803" max="12804" width="11.44140625" style="214"/>
-    <col min="12805" max="12806" width="4.109375" style="214" customWidth="1"/>
-    <col min="12807" max="12807" width="11.44140625" style="214"/>
-    <col min="12808" max="12808" width="19.109375" style="214" customWidth="1"/>
-    <col min="12809" max="12810" width="11.44140625" style="214"/>
-    <col min="12811" max="12812" width="4.88671875" style="214" customWidth="1"/>
-    <col min="12813" max="12813" width="10.88671875" style="214" customWidth="1"/>
-    <col min="12814" max="12814" width="11.44140625" style="214"/>
+    <col min="12801" max="12801" width="4.42578125" style="214" customWidth="1"/>
+    <col min="12802" max="12802" width="20.85546875" style="214" customWidth="1"/>
+    <col min="12803" max="12804" width="11.42578125" style="214"/>
+    <col min="12805" max="12806" width="4.140625" style="214" customWidth="1"/>
+    <col min="12807" max="12807" width="11.42578125" style="214"/>
+    <col min="12808" max="12808" width="19.140625" style="214" customWidth="1"/>
+    <col min="12809" max="12810" width="11.42578125" style="214"/>
+    <col min="12811" max="12812" width="4.85546875" style="214" customWidth="1"/>
+    <col min="12813" max="12813" width="10.85546875" style="214" customWidth="1"/>
+    <col min="12814" max="12814" width="11.42578125" style="214"/>
     <col min="12815" max="12815" width="22" style="214" customWidth="1"/>
-    <col min="12816" max="12817" width="11.44140625" style="214"/>
+    <col min="12816" max="12817" width="11.42578125" style="214"/>
     <col min="12818" max="12819" width="6" style="214" customWidth="1"/>
-    <col min="12820" max="13050" width="11.44140625" style="214"/>
+    <col min="12820" max="13050" width="11.42578125" style="214"/>
     <col min="13051" max="13052" width="20" style="214" customWidth="1"/>
-    <col min="13053" max="13053" width="11.44140625" style="214"/>
-    <col min="13054" max="13055" width="6.109375" style="214" customWidth="1"/>
+    <col min="13053" max="13053" width="11.42578125" style="214"/>
+    <col min="13054" max="13055" width="6.140625" style="214" customWidth="1"/>
     <col min="13056" max="13056" width="14" style="214" customWidth="1"/>
-    <col min="13057" max="13057" width="4.44140625" style="214" customWidth="1"/>
-    <col min="13058" max="13058" width="20.88671875" style="214" customWidth="1"/>
-    <col min="13059" max="13060" width="11.44140625" style="214"/>
-    <col min="13061" max="13062" width="4.109375" style="214" customWidth="1"/>
-    <col min="13063" max="13063" width="11.44140625" style="214"/>
-    <col min="13064" max="13064" width="19.109375" style="214" customWidth="1"/>
-    <col min="13065" max="13066" width="11.44140625" style="214"/>
-    <col min="13067" max="13068" width="4.88671875" style="214" customWidth="1"/>
-    <col min="13069" max="13069" width="10.88671875" style="214" customWidth="1"/>
-    <col min="13070" max="13070" width="11.44140625" style="214"/>
+    <col min="13057" max="13057" width="4.42578125" style="214" customWidth="1"/>
+    <col min="13058" max="13058" width="20.85546875" style="214" customWidth="1"/>
+    <col min="13059" max="13060" width="11.42578125" style="214"/>
+    <col min="13061" max="13062" width="4.140625" style="214" customWidth="1"/>
+    <col min="13063" max="13063" width="11.42578125" style="214"/>
+    <col min="13064" max="13064" width="19.140625" style="214" customWidth="1"/>
+    <col min="13065" max="13066" width="11.42578125" style="214"/>
+    <col min="13067" max="13068" width="4.85546875" style="214" customWidth="1"/>
+    <col min="13069" max="13069" width="10.85546875" style="214" customWidth="1"/>
+    <col min="13070" max="13070" width="11.42578125" style="214"/>
     <col min="13071" max="13071" width="22" style="214" customWidth="1"/>
-    <col min="13072" max="13073" width="11.44140625" style="214"/>
+    <col min="13072" max="13073" width="11.42578125" style="214"/>
     <col min="13074" max="13075" width="6" style="214" customWidth="1"/>
-    <col min="13076" max="13306" width="11.44140625" style="214"/>
+    <col min="13076" max="13306" width="11.42578125" style="214"/>
     <col min="13307" max="13308" width="20" style="214" customWidth="1"/>
-    <col min="13309" max="13309" width="11.44140625" style="214"/>
-    <col min="13310" max="13311" width="6.109375" style="214" customWidth="1"/>
+    <col min="13309" max="13309" width="11.42578125" style="214"/>
+    <col min="13310" max="13311" width="6.140625" style="214" customWidth="1"/>
     <col min="13312" max="13312" width="14" style="214" customWidth="1"/>
-    <col min="13313" max="13313" width="4.44140625" style="214" customWidth="1"/>
-    <col min="13314" max="13314" width="20.88671875" style="214" customWidth="1"/>
-    <col min="13315" max="13316" width="11.44140625" style="214"/>
-    <col min="13317" max="13318" width="4.109375" style="214" customWidth="1"/>
-    <col min="13319" max="13319" width="11.44140625" style="214"/>
-    <col min="13320" max="13320" width="19.109375" style="214" customWidth="1"/>
-    <col min="13321" max="13322" width="11.44140625" style="214"/>
-    <col min="13323" max="13324" width="4.88671875" style="214" customWidth="1"/>
-    <col min="13325" max="13325" width="10.88671875" style="214" customWidth="1"/>
-    <col min="13326" max="13326" width="11.44140625" style="214"/>
+    <col min="13313" max="13313" width="4.42578125" style="214" customWidth="1"/>
+    <col min="13314" max="13314" width="20.85546875" style="214" customWidth="1"/>
+    <col min="13315" max="13316" width="11.42578125" style="214"/>
+    <col min="13317" max="13318" width="4.140625" style="214" customWidth="1"/>
+    <col min="13319" max="13319" width="11.42578125" style="214"/>
+    <col min="13320" max="13320" width="19.140625" style="214" customWidth="1"/>
+    <col min="13321" max="13322" width="11.42578125" style="214"/>
+    <col min="13323" max="13324" width="4.85546875" style="214" customWidth="1"/>
+    <col min="13325" max="13325" width="10.85546875" style="214" customWidth="1"/>
+    <col min="13326" max="13326" width="11.42578125" style="214"/>
     <col min="13327" max="13327" width="22" style="214" customWidth="1"/>
-    <col min="13328" max="13329" width="11.44140625" style="214"/>
+    <col min="13328" max="13329" width="11.42578125" style="214"/>
     <col min="13330" max="13331" width="6" style="214" customWidth="1"/>
-    <col min="13332" max="13562" width="11.44140625" style="214"/>
+    <col min="13332" max="13562" width="11.42578125" style="214"/>
     <col min="13563" max="13564" width="20" style="214" customWidth="1"/>
-    <col min="13565" max="13565" width="11.44140625" style="214"/>
-    <col min="13566" max="13567" width="6.109375" style="214" customWidth="1"/>
+    <col min="13565" max="13565" width="11.42578125" style="214"/>
+    <col min="13566" max="13567" width="6.140625" style="214" customWidth="1"/>
     <col min="13568" max="13568" width="14" style="214" customWidth="1"/>
-    <col min="13569" max="13569" width="4.44140625" style="214" customWidth="1"/>
-    <col min="13570" max="13570" width="20.88671875" style="214" customWidth="1"/>
-    <col min="13571" max="13572" width="11.44140625" style="214"/>
-    <col min="13573" max="13574" width="4.109375" style="214" customWidth="1"/>
-    <col min="13575" max="13575" width="11.44140625" style="214"/>
-    <col min="13576" max="13576" width="19.109375" style="214" customWidth="1"/>
-    <col min="13577" max="13578" width="11.44140625" style="214"/>
-    <col min="13579" max="13580" width="4.88671875" style="214" customWidth="1"/>
-    <col min="13581" max="13581" width="10.88671875" style="214" customWidth="1"/>
-    <col min="13582" max="13582" width="11.44140625" style="214"/>
+    <col min="13569" max="13569" width="4.42578125" style="214" customWidth="1"/>
+    <col min="13570" max="13570" width="20.85546875" style="214" customWidth="1"/>
+    <col min="13571" max="13572" width="11.42578125" style="214"/>
+    <col min="13573" max="13574" width="4.140625" style="214" customWidth="1"/>
+    <col min="13575" max="13575" width="11.42578125" style="214"/>
+    <col min="13576" max="13576" width="19.140625" style="214" customWidth="1"/>
+    <col min="13577" max="13578" width="11.42578125" style="214"/>
+    <col min="13579" max="13580" width="4.85546875" style="214" customWidth="1"/>
+    <col min="13581" max="13581" width="10.85546875" style="214" customWidth="1"/>
+    <col min="13582" max="13582" width="11.42578125" style="214"/>
     <col min="13583" max="13583" width="22" style="214" customWidth="1"/>
-    <col min="13584" max="13585" width="11.44140625" style="214"/>
+    <col min="13584" max="13585" width="11.42578125" style="214"/>
     <col min="13586" max="13587" width="6" style="214" customWidth="1"/>
-    <col min="13588" max="13818" width="11.44140625" style="214"/>
+    <col min="13588" max="13818" width="11.42578125" style="214"/>
     <col min="13819" max="13820" width="20" style="214" customWidth="1"/>
-    <col min="13821" max="13821" width="11.44140625" style="214"/>
-    <col min="13822" max="13823" width="6.109375" style="214" customWidth="1"/>
+    <col min="13821" max="13821" width="11.42578125" style="214"/>
+    <col min="13822" max="13823" width="6.140625" style="214" customWidth="1"/>
     <col min="13824" max="13824" width="14" style="214" customWidth="1"/>
-    <col min="13825" max="13825" width="4.44140625" style="214" customWidth="1"/>
-    <col min="13826" max="13826" width="20.88671875" style="214" customWidth="1"/>
-    <col min="13827" max="13828" width="11.44140625" style="214"/>
-    <col min="13829" max="13830" width="4.109375" style="214" customWidth="1"/>
-    <col min="13831" max="13831" width="11.44140625" style="214"/>
-    <col min="13832" max="13832" width="19.109375" style="214" customWidth="1"/>
-    <col min="13833" max="13834" width="11.44140625" style="214"/>
-    <col min="13835" max="13836" width="4.88671875" style="214" customWidth="1"/>
-    <col min="13837" max="13837" width="10.88671875" style="214" customWidth="1"/>
-    <col min="13838" max="13838" width="11.44140625" style="214"/>
+    <col min="13825" max="13825" width="4.42578125" style="214" customWidth="1"/>
+    <col min="13826" max="13826" width="20.85546875" style="214" customWidth="1"/>
+    <col min="13827" max="13828" width="11.42578125" style="214"/>
+    <col min="13829" max="13830" width="4.140625" style="214" customWidth="1"/>
+    <col min="13831" max="13831" width="11.42578125" style="214"/>
+    <col min="13832" max="13832" width="19.140625" style="214" customWidth="1"/>
+    <col min="13833" max="13834" width="11.42578125" style="214"/>
+    <col min="13835" max="13836" width="4.85546875" style="214" customWidth="1"/>
+    <col min="13837" max="13837" width="10.85546875" style="214" customWidth="1"/>
+    <col min="13838" max="13838" width="11.42578125" style="214"/>
     <col min="13839" max="13839" width="22" style="214" customWidth="1"/>
-    <col min="13840" max="13841" width="11.44140625" style="214"/>
+    <col min="13840" max="13841" width="11.42578125" style="214"/>
     <col min="13842" max="13843" width="6" style="214" customWidth="1"/>
-    <col min="13844" max="14074" width="11.44140625" style="214"/>
+    <col min="13844" max="14074" width="11.42578125" style="214"/>
     <col min="14075" max="14076" width="20" style="214" customWidth="1"/>
-    <col min="14077" max="14077" width="11.44140625" style="214"/>
-    <col min="14078" max="14079" width="6.109375" style="214" customWidth="1"/>
+    <col min="14077" max="14077" width="11.42578125" style="214"/>
+    <col min="14078" max="14079" width="6.140625" style="214" customWidth="1"/>
     <col min="14080" max="14080" width="14" style="214" customWidth="1"/>
-    <col min="14081" max="14081" width="4.44140625" style="214" customWidth="1"/>
-    <col min="14082" max="14082" width="20.88671875" style="214" customWidth="1"/>
-    <col min="14083" max="14084" width="11.44140625" style="214"/>
-    <col min="14085" max="14086" width="4.109375" style="214" customWidth="1"/>
-    <col min="14087" max="14087" width="11.44140625" style="214"/>
-    <col min="14088" max="14088" width="19.109375" style="214" customWidth="1"/>
-    <col min="14089" max="14090" width="11.44140625" style="214"/>
-    <col min="14091" max="14092" width="4.88671875" style="214" customWidth="1"/>
-    <col min="14093" max="14093" width="10.88671875" style="214" customWidth="1"/>
-    <col min="14094" max="14094" width="11.44140625" style="214"/>
+    <col min="14081" max="14081" width="4.42578125" style="214" customWidth="1"/>
+    <col min="14082" max="14082" width="20.85546875" style="214" customWidth="1"/>
+    <col min="14083" max="14084" width="11.42578125" style="214"/>
+    <col min="14085" max="14086" width="4.140625" style="214" customWidth="1"/>
+    <col min="14087" max="14087" width="11.42578125" style="214"/>
+    <col min="14088" max="14088" width="19.140625" style="214" customWidth="1"/>
+    <col min="14089" max="14090" width="11.42578125" style="214"/>
+    <col min="14091" max="14092" width="4.85546875" style="214" customWidth="1"/>
+    <col min="14093" max="14093" width="10.85546875" style="214" customWidth="1"/>
+    <col min="14094" max="14094" width="11.42578125" style="214"/>
     <col min="14095" max="14095" width="22" style="214" customWidth="1"/>
-    <col min="14096" max="14097" width="11.44140625" style="214"/>
+    <col min="14096" max="14097" width="11.42578125" style="214"/>
     <col min="14098" max="14099" width="6" style="214" customWidth="1"/>
-    <col min="14100" max="14330" width="11.44140625" style="214"/>
+    <col min="14100" max="14330" width="11.42578125" style="214"/>
     <col min="14331" max="14332" width="20" style="214" customWidth="1"/>
-    <col min="14333" max="14333" width="11.44140625" style="214"/>
-    <col min="14334" max="14335" width="6.109375" style="214" customWidth="1"/>
+    <col min="14333" max="14333" width="11.42578125" style="214"/>
+    <col min="14334" max="14335" width="6.140625" style="214" customWidth="1"/>
     <col min="14336" max="14336" width="14" style="214" customWidth="1"/>
-    <col min="14337" max="14337" width="4.44140625" style="214" customWidth="1"/>
-    <col min="14338" max="14338" width="20.88671875" style="214" customWidth="1"/>
-    <col min="14339" max="14340" width="11.44140625" style="214"/>
-    <col min="14341" max="14342" width="4.109375" style="214" customWidth="1"/>
-    <col min="14343" max="14343" width="11.44140625" style="214"/>
-    <col min="14344" max="14344" width="19.109375" style="214" customWidth="1"/>
-    <col min="14345" max="14346" width="11.44140625" style="214"/>
-    <col min="14347" max="14348" width="4.88671875" style="214" customWidth="1"/>
-    <col min="14349" max="14349" width="10.88671875" style="214" customWidth="1"/>
-    <col min="14350" max="14350" width="11.44140625" style="214"/>
+    <col min="14337" max="14337" width="4.42578125" style="214" customWidth="1"/>
+    <col min="14338" max="14338" width="20.85546875" style="214" customWidth="1"/>
+    <col min="14339" max="14340" width="11.42578125" style="214"/>
+    <col min="14341" max="14342" width="4.140625" style="214" customWidth="1"/>
+    <col min="14343" max="14343" width="11.42578125" style="214"/>
+    <col min="14344" max="14344" width="19.140625" style="214" customWidth="1"/>
+    <col min="14345" max="14346" width="11.42578125" style="214"/>
+    <col min="14347" max="14348" width="4.85546875" style="214" customWidth="1"/>
+    <col min="14349" max="14349" width="10.85546875" style="214" customWidth="1"/>
+    <col min="14350" max="14350" width="11.42578125" style="214"/>
     <col min="14351" max="14351" width="22" style="214" customWidth="1"/>
-    <col min="14352" max="14353" width="11.44140625" style="214"/>
+    <col min="14352" max="14353" width="11.42578125" style="214"/>
     <col min="14354" max="14355" width="6" style="214" customWidth="1"/>
-    <col min="14356" max="14586" width="11.44140625" style="214"/>
+    <col min="14356" max="14586" width="11.42578125" style="214"/>
     <col min="14587" max="14588" width="20" style="214" customWidth="1"/>
-    <col min="14589" max="14589" width="11.44140625" style="214"/>
-    <col min="14590" max="14591" width="6.109375" style="214" customWidth="1"/>
+    <col min="14589" max="14589" width="11.42578125" style="214"/>
+    <col min="14590" max="14591" width="6.140625" style="214" customWidth="1"/>
     <col min="14592" max="14592" width="14" style="214" customWidth="1"/>
-    <col min="14593" max="14593" width="4.44140625" style="214" customWidth="1"/>
-    <col min="14594" max="14594" width="20.88671875" style="214" customWidth="1"/>
-    <col min="14595" max="14596" width="11.44140625" style="214"/>
-    <col min="14597" max="14598" width="4.109375" style="214" customWidth="1"/>
-    <col min="14599" max="14599" width="11.44140625" style="214"/>
-    <col min="14600" max="14600" width="19.109375" style="214" customWidth="1"/>
-    <col min="14601" max="14602" width="11.44140625" style="214"/>
-    <col min="14603" max="14604" width="4.88671875" style="214" customWidth="1"/>
-    <col min="14605" max="14605" width="10.88671875" style="214" customWidth="1"/>
-    <col min="14606" max="14606" width="11.44140625" style="214"/>
+    <col min="14593" max="14593" width="4.42578125" style="214" customWidth="1"/>
+    <col min="14594" max="14594" width="20.85546875" style="214" customWidth="1"/>
+    <col min="14595" max="14596" width="11.42578125" style="214"/>
+    <col min="14597" max="14598" width="4.140625" style="214" customWidth="1"/>
+    <col min="14599" max="14599" width="11.42578125" style="214"/>
+    <col min="14600" max="14600" width="19.140625" style="214" customWidth="1"/>
+    <col min="14601" max="14602" width="11.42578125" style="214"/>
+    <col min="14603" max="14604" width="4.85546875" style="214" customWidth="1"/>
+    <col min="14605" max="14605" width="10.85546875" style="214" customWidth="1"/>
+    <col min="14606" max="14606" width="11.42578125" style="214"/>
     <col min="14607" max="14607" width="22" style="214" customWidth="1"/>
-    <col min="14608" max="14609" width="11.44140625" style="214"/>
+    <col min="14608" max="14609" width="11.42578125" style="214"/>
     <col min="14610" max="14611" width="6" style="214" customWidth="1"/>
-    <col min="14612" max="14842" width="11.44140625" style="214"/>
+    <col min="14612" max="14842" width="11.42578125" style="214"/>
     <col min="14843" max="14844" width="20" style="214" customWidth="1"/>
-    <col min="14845" max="14845" width="11.44140625" style="214"/>
-    <col min="14846" max="14847" width="6.109375" style="214" customWidth="1"/>
+    <col min="14845" max="14845" width="11.42578125" style="214"/>
+    <col min="14846" max="14847" width="6.140625" style="214" customWidth="1"/>
     <col min="14848" max="14848" width="14" style="214" customWidth="1"/>
-    <col min="14849" max="14849" width="4.44140625" style="214" customWidth="1"/>
-    <col min="14850" max="14850" width="20.88671875" style="214" customWidth="1"/>
-    <col min="14851" max="14852" width="11.44140625" style="214"/>
-    <col min="14853" max="14854" width="4.109375" style="214" customWidth="1"/>
-    <col min="14855" max="14855" width="11.44140625" style="214"/>
-    <col min="14856" max="14856" width="19.109375" style="214" customWidth="1"/>
-    <col min="14857" max="14858" width="11.44140625" style="214"/>
-    <col min="14859" max="14860" width="4.88671875" style="214" customWidth="1"/>
-    <col min="14861" max="14861" width="10.88671875" style="214" customWidth="1"/>
-    <col min="14862" max="14862" width="11.44140625" style="214"/>
+    <col min="14849" max="14849" width="4.42578125" style="214" customWidth="1"/>
+    <col min="14850" max="14850" width="20.85546875" style="214" customWidth="1"/>
+    <col min="14851" max="14852" width="11.42578125" style="214"/>
+    <col min="14853" max="14854" width="4.140625" style="214" customWidth="1"/>
+    <col min="14855" max="14855" width="11.42578125" style="214"/>
+    <col min="14856" max="14856" width="19.140625" style="214" customWidth="1"/>
+    <col min="14857" max="14858" width="11.42578125" style="214"/>
+    <col min="14859" max="14860" width="4.85546875" style="214" customWidth="1"/>
+    <col min="14861" max="14861" width="10.85546875" style="214" customWidth="1"/>
+    <col min="14862" max="14862" width="11.42578125" style="214"/>
     <col min="14863" max="14863" width="22" style="214" customWidth="1"/>
-    <col min="14864" max="14865" width="11.44140625" style="214"/>
+    <col min="14864" max="14865" width="11.42578125" style="214"/>
     <col min="14866" max="14867" width="6" style="214" customWidth="1"/>
-    <col min="14868" max="15098" width="11.44140625" style="214"/>
+    <col min="14868" max="15098" width="11.42578125" style="214"/>
     <col min="15099" max="15100" width="20" style="214" customWidth="1"/>
-    <col min="15101" max="15101" width="11.44140625" style="214"/>
-    <col min="15102" max="15103" width="6.109375" style="214" customWidth="1"/>
+    <col min="15101" max="15101" width="11.42578125" style="214"/>
+    <col min="15102" max="15103" width="6.140625" style="214" customWidth="1"/>
     <col min="15104" max="15104" width="14" style="214" customWidth="1"/>
-    <col min="15105" max="15105" width="4.44140625" style="214" customWidth="1"/>
-    <col min="15106" max="15106" width="20.88671875" style="214" customWidth="1"/>
-    <col min="15107" max="15108" width="11.44140625" style="214"/>
-    <col min="15109" max="15110" width="4.109375" style="214" customWidth="1"/>
-    <col min="15111" max="15111" width="11.44140625" style="214"/>
-    <col min="15112" max="15112" width="19.109375" style="214" customWidth="1"/>
-    <col min="15113" max="15114" width="11.44140625" style="214"/>
-    <col min="15115" max="15116" width="4.88671875" style="214" customWidth="1"/>
-    <col min="15117" max="15117" width="10.88671875" style="214" customWidth="1"/>
-    <col min="15118" max="15118" width="11.44140625" style="214"/>
+    <col min="15105" max="15105" width="4.42578125" style="214" customWidth="1"/>
+    <col min="15106" max="15106" width="20.85546875" style="214" customWidth="1"/>
+    <col min="15107" max="15108" width="11.42578125" style="214"/>
+    <col min="15109" max="15110" width="4.140625" style="214" customWidth="1"/>
+    <col min="15111" max="15111" width="11.42578125" style="214"/>
+    <col min="15112" max="15112" width="19.140625" style="214" customWidth="1"/>
+    <col min="15113" max="15114" width="11.42578125" style="214"/>
+    <col min="15115" max="15116" width="4.85546875" style="214" customWidth="1"/>
+    <col min="15117" max="15117" width="10.85546875" style="214" customWidth="1"/>
+    <col min="15118" max="15118" width="11.42578125" style="214"/>
     <col min="15119" max="15119" width="22" style="214" customWidth="1"/>
-    <col min="15120" max="15121" width="11.44140625" style="214"/>
+    <col min="15120" max="15121" width="11.42578125" style="214"/>
     <col min="15122" max="15123" width="6" style="214" customWidth="1"/>
-    <col min="15124" max="15354" width="11.44140625" style="214"/>
+    <col min="15124" max="15354" width="11.42578125" style="214"/>
     <col min="15355" max="15356" width="20" style="214" customWidth="1"/>
-    <col min="15357" max="15357" width="11.44140625" style="214"/>
-    <col min="15358" max="15359" width="6.109375" style="214" customWidth="1"/>
+    <col min="15357" max="15357" width="11.42578125" style="214"/>
+    <col min="15358" max="15359" width="6.140625" style="214" customWidth="1"/>
     <col min="15360" max="15360" width="14" style="214" customWidth="1"/>
-    <col min="15361" max="15361" width="4.44140625" style="214" customWidth="1"/>
-    <col min="15362" max="15362" width="20.88671875" style="214" customWidth="1"/>
-    <col min="15363" max="15364" width="11.44140625" style="214"/>
-    <col min="15365" max="15366" width="4.109375" style="214" customWidth="1"/>
-    <col min="15367" max="15367" width="11.44140625" style="214"/>
-    <col min="15368" max="15368" width="19.109375" style="214" customWidth="1"/>
-    <col min="15369" max="15370" width="11.44140625" style="214"/>
-    <col min="15371" max="15372" width="4.88671875" style="214" customWidth="1"/>
-    <col min="15373" max="15373" width="10.88671875" style="214" customWidth="1"/>
-    <col min="15374" max="15374" width="11.44140625" style="214"/>
+    <col min="15361" max="15361" width="4.42578125" style="214" customWidth="1"/>
+    <col min="15362" max="15362" width="20.85546875" style="214" customWidth="1"/>
+    <col min="15363" max="15364" width="11.42578125" style="214"/>
+    <col min="15365" max="15366" width="4.140625" style="214" customWidth="1"/>
+    <col min="15367" max="15367" width="11.42578125" style="214"/>
+    <col min="15368" max="15368" width="19.140625" style="214" customWidth="1"/>
+    <col min="15369" max="15370" width="11.42578125" style="214"/>
+    <col min="15371" max="15372" width="4.85546875" style="214" customWidth="1"/>
+    <col min="15373" max="15373" width="10.85546875" style="214" customWidth="1"/>
+    <col min="15374" max="15374" width="11.42578125" style="214"/>
     <col min="15375" max="15375" width="22" style="214" customWidth="1"/>
-    <col min="15376" max="15377" width="11.44140625" style="214"/>
+    <col min="15376" max="15377" width="11.42578125" style="214"/>
     <col min="15378" max="15379" width="6" style="214" customWidth="1"/>
-    <col min="15380" max="15610" width="11.44140625" style="214"/>
+    <col min="15380" max="15610" width="11.42578125" style="214"/>
     <col min="15611" max="15612" width="20" style="214" customWidth="1"/>
-    <col min="15613" max="15613" width="11.44140625" style="214"/>
-    <col min="15614" max="15615" width="6.109375" style="214" customWidth="1"/>
+    <col min="15613" max="15613" width="11.42578125" style="214"/>
+    <col min="15614" max="15615" width="6.140625" style="214" customWidth="1"/>
     <col min="15616" max="15616" width="14" style="214" customWidth="1"/>
-    <col min="15617" max="15617" width="4.44140625" style="214" customWidth="1"/>
-    <col min="15618" max="15618" width="20.88671875" style="214" customWidth="1"/>
-    <col min="15619" max="15620" width="11.44140625" style="214"/>
-    <col min="15621" max="15622" width="4.109375" style="214" customWidth="1"/>
-    <col min="15623" max="15623" width="11.44140625" style="214"/>
-    <col min="15624" max="15624" width="19.109375" style="214" customWidth="1"/>
-    <col min="15625" max="15626" width="11.44140625" style="214"/>
-    <col min="15627" max="15628" width="4.88671875" style="214" customWidth="1"/>
-    <col min="15629" max="15629" width="10.88671875" style="214" customWidth="1"/>
-    <col min="15630" max="15630" width="11.44140625" style="214"/>
+    <col min="15617" max="15617" width="4.42578125" style="214" customWidth="1"/>
+    <col min="15618" max="15618" width="20.85546875" style="214" customWidth="1"/>
+    <col min="15619" max="15620" width="11.42578125" style="214"/>
+    <col min="15621" max="15622" width="4.140625" style="214" customWidth="1"/>
+    <col min="15623" max="15623" width="11.42578125" style="214"/>
+    <col min="15624" max="15624" width="19.140625" style="214" customWidth="1"/>
+    <col min="15625" max="15626" width="11.42578125" style="214"/>
+    <col min="15627" max="15628" width="4.85546875" style="214" customWidth="1"/>
+    <col min="15629" max="15629" width="10.85546875" style="214" customWidth="1"/>
+    <col min="15630" max="15630" width="11.42578125" style="214"/>
     <col min="15631" max="15631" width="22" style="214" customWidth="1"/>
-    <col min="15632" max="15633" width="11.44140625" style="214"/>
+    <col min="15632" max="15633" width="11.42578125" style="214"/>
     <col min="15634" max="15635" width="6" style="214" customWidth="1"/>
-    <col min="15636" max="15866" width="11.44140625" style="214"/>
+    <col min="15636" max="15866" width="11.42578125" style="214"/>
     <col min="15867" max="15868" width="20" style="214" customWidth="1"/>
-    <col min="15869" max="15869" width="11.44140625" style="214"/>
-    <col min="15870" max="15871" width="6.109375" style="214" customWidth="1"/>
+    <col min="15869" max="15869" width="11.42578125" style="214"/>
+    <col min="15870" max="15871" width="6.140625" style="214" customWidth="1"/>
     <col min="15872" max="15872" width="14" style="214" customWidth="1"/>
-    <col min="15873" max="15873" width="4.44140625" style="214" customWidth="1"/>
-    <col min="15874" max="15874" width="20.88671875" style="214" customWidth="1"/>
-    <col min="15875" max="15876" width="11.44140625" style="214"/>
-    <col min="15877" max="15878" width="4.109375" style="214" customWidth="1"/>
-    <col min="15879" max="15879" width="11.44140625" style="214"/>
-    <col min="15880" max="15880" width="19.109375" style="214" customWidth="1"/>
-    <col min="15881" max="15882" width="11.44140625" style="214"/>
-    <col min="15883" max="15884" width="4.88671875" style="214" customWidth="1"/>
-    <col min="15885" max="15885" width="10.88671875" style="214" customWidth="1"/>
-    <col min="15886" max="15886" width="11.44140625" style="214"/>
+    <col min="15873" max="15873" width="4.42578125" style="214" customWidth="1"/>
+    <col min="15874" max="15874" width="20.85546875" style="214" customWidth="1"/>
+    <col min="15875" max="15876" width="11.42578125" style="214"/>
+    <col min="15877" max="15878" width="4.140625" style="214" customWidth="1"/>
+    <col min="15879" max="15879" width="11.42578125" style="214"/>
+    <col min="15880" max="15880" width="19.140625" style="214" customWidth="1"/>
+    <col min="15881" max="15882" width="11.42578125" style="214"/>
+    <col min="15883" max="15884" width="4.85546875" style="214" customWidth="1"/>
+    <col min="15885" max="15885" width="10.85546875" style="214" customWidth="1"/>
+    <col min="15886" max="15886" width="11.42578125" style="214"/>
     <col min="15887" max="15887" width="22" style="214" customWidth="1"/>
-    <col min="15888" max="15889" width="11.44140625" style="214"/>
+    <col min="15888" max="15889" width="11.42578125" style="214"/>
     <col min="15890" max="15891" width="6" style="214" customWidth="1"/>
-    <col min="15892" max="16122" width="11.44140625" style="214"/>
+    <col min="15892" max="16122" width="11.42578125" style="214"/>
     <col min="16123" max="16124" width="20" style="214" customWidth="1"/>
-    <col min="16125" max="16125" width="11.44140625" style="214"/>
-    <col min="16126" max="16127" width="6.109375" style="214" customWidth="1"/>
+    <col min="16125" max="16125" width="11.42578125" style="214"/>
+    <col min="16126" max="16127" width="6.140625" style="214" customWidth="1"/>
     <col min="16128" max="16128" width="14" style="214" customWidth="1"/>
-    <col min="16129" max="16129" width="4.44140625" style="214" customWidth="1"/>
-    <col min="16130" max="16130" width="20.88671875" style="214" customWidth="1"/>
-    <col min="16131" max="16132" width="11.44140625" style="214"/>
-    <col min="16133" max="16134" width="4.109375" style="214" customWidth="1"/>
-    <col min="16135" max="16135" width="11.44140625" style="214"/>
-    <col min="16136" max="16136" width="19.109375" style="214" customWidth="1"/>
-    <col min="16137" max="16138" width="11.44140625" style="214"/>
-    <col min="16139" max="16140" width="4.88671875" style="214" customWidth="1"/>
-    <col min="16141" max="16141" width="10.88671875" style="214" customWidth="1"/>
-    <col min="16142" max="16142" width="11.44140625" style="214"/>
+    <col min="16129" max="16129" width="4.42578125" style="214" customWidth="1"/>
+    <col min="16130" max="16130" width="20.85546875" style="214" customWidth="1"/>
+    <col min="16131" max="16132" width="11.42578125" style="214"/>
+    <col min="16133" max="16134" width="4.140625" style="214" customWidth="1"/>
+    <col min="16135" max="16135" width="11.42578125" style="214"/>
+    <col min="16136" max="16136" width="19.140625" style="214" customWidth="1"/>
+    <col min="16137" max="16138" width="11.42578125" style="214"/>
+    <col min="16139" max="16140" width="4.85546875" style="214" customWidth="1"/>
+    <col min="16141" max="16141" width="10.85546875" style="214" customWidth="1"/>
+    <col min="16142" max="16142" width="11.42578125" style="214"/>
     <col min="16143" max="16143" width="22" style="214" customWidth="1"/>
-    <col min="16144" max="16145" width="11.44140625" style="214"/>
+    <col min="16144" max="16145" width="11.42578125" style="214"/>
     <col min="16146" max="16147" width="6" style="214" customWidth="1"/>
-    <col min="16148" max="16384" width="11.44140625" style="214"/>
+    <col min="16148" max="16384" width="11.42578125" style="214"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="1:19" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="215"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="216" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -14631,30 +14630,30 @@
       <c r="B6" s="217"/>
     </row>
     <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="462" t="s">
+      <c r="A7" s="459" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="462"/>
-      <c r="C7" s="462"/>
-      <c r="D7" s="462"/>
-      <c r="F7" s="462" t="s">
+      <c r="B7" s="459"/>
+      <c r="C7" s="459"/>
+      <c r="D7" s="459"/>
+      <c r="F7" s="459" t="s">
         <v>125</v>
       </c>
-      <c r="G7" s="462"/>
-      <c r="H7" s="462"/>
-      <c r="I7" s="462"/>
-      <c r="K7" s="462" t="s">
+      <c r="G7" s="459"/>
+      <c r="H7" s="459"/>
+      <c r="I7" s="459"/>
+      <c r="K7" s="459" t="s">
         <v>126</v>
       </c>
-      <c r="L7" s="462"/>
-      <c r="M7" s="462"/>
-      <c r="N7" s="462"/>
-      <c r="P7" s="462" t="s">
+      <c r="L7" s="459"/>
+      <c r="M7" s="459"/>
+      <c r="N7" s="459"/>
+      <c r="P7" s="459" t="s">
         <v>127</v>
       </c>
-      <c r="Q7" s="462"/>
-      <c r="R7" s="462"/>
-      <c r="S7" s="462"/>
+      <c r="Q7" s="459"/>
+      <c r="R7" s="459"/>
+      <c r="S7" s="459"/>
     </row>
     <row r="8" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="219"/>
@@ -14678,573 +14677,573 @@
       <c r="A9" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="463" t="e">
+      <c r="B9" s="460" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="C9" s="463"/>
-      <c r="D9" s="463"/>
+      <c r="C9" s="460"/>
+      <c r="D9" s="460"/>
       <c r="F9" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="G9" s="463" t="e">
+      <c r="G9" s="460" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H9" s="463"/>
-      <c r="I9" s="463"/>
+      <c r="H9" s="460"/>
+      <c r="I9" s="460"/>
       <c r="K9" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="L9" s="463" t="e">
+      <c r="L9" s="460" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="M9" s="463"/>
-      <c r="N9" s="463"/>
+      <c r="M9" s="460"/>
+      <c r="N9" s="460"/>
       <c r="P9" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" s="455" t="e">
+      <c r="Q9" s="452" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="R9" s="456"/>
-      <c r="S9" s="457"/>
+      <c r="R9" s="453"/>
+      <c r="S9" s="454"/>
     </row>
     <row r="10" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="463" t="e">
+      <c r="B10" s="460" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="463"/>
-      <c r="D10" s="463"/>
+      <c r="C10" s="460"/>
+      <c r="D10" s="460"/>
       <c r="F10" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="463" t="e">
+      <c r="G10" s="460" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="H10" s="463"/>
-      <c r="I10" s="463"/>
+      <c r="H10" s="460"/>
+      <c r="I10" s="460"/>
       <c r="K10" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="L10" s="463" t="e">
+      <c r="L10" s="460" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="M10" s="463"/>
-      <c r="N10" s="463"/>
+      <c r="M10" s="460"/>
+      <c r="N10" s="460"/>
       <c r="P10" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="Q10" s="455" t="e">
+      <c r="Q10" s="452" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="R10" s="456"/>
-      <c r="S10" s="457"/>
+      <c r="R10" s="453"/>
+      <c r="S10" s="454"/>
     </row>
     <row r="11" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="220" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="463" t="e">
+      <c r="B11" s="460" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="C11" s="463"/>
-      <c r="D11" s="463"/>
+      <c r="C11" s="460"/>
+      <c r="D11" s="460"/>
       <c r="F11" s="220" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="463" t="e">
+      <c r="G11" s="460" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="H11" s="463"/>
-      <c r="I11" s="463"/>
+      <c r="H11" s="460"/>
+      <c r="I11" s="460"/>
       <c r="K11" s="220" t="s">
         <v>130</v>
       </c>
-      <c r="L11" s="463" t="e">
+      <c r="L11" s="460" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="M11" s="463"/>
-      <c r="N11" s="463"/>
+      <c r="M11" s="460"/>
+      <c r="N11" s="460"/>
       <c r="P11" s="220" t="s">
         <v>130</v>
       </c>
-      <c r="Q11" s="455" t="e">
+      <c r="Q11" s="452" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R11" s="456"/>
-      <c r="S11" s="457"/>
+      <c r="R11" s="453"/>
+      <c r="S11" s="454"/>
     </row>
     <row r="12" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="220" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="463" t="e">
+      <c r="B12" s="460" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
       <c r="F12" s="220" t="s">
         <v>131</v>
       </c>
-      <c r="G12" s="463" t="e">
+      <c r="G12" s="460" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="H12" s="463"/>
-      <c r="I12" s="463"/>
+      <c r="H12" s="460"/>
+      <c r="I12" s="460"/>
       <c r="K12" s="220" t="s">
         <v>131</v>
       </c>
-      <c r="L12" s="463" t="e">
+      <c r="L12" s="460" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="M12" s="463"/>
-      <c r="N12" s="463"/>
+      <c r="M12" s="460"/>
+      <c r="N12" s="460"/>
       <c r="P12" s="220" t="s">
         <v>131</v>
       </c>
-      <c r="Q12" s="455" t="e">
+      <c r="Q12" s="452" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="R12" s="456"/>
-      <c r="S12" s="457"/>
+      <c r="R12" s="453"/>
+      <c r="S12" s="454"/>
     </row>
     <row r="13" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="220" t="s">
         <v>132</v>
       </c>
-      <c r="B13" s="461" t="e">
+      <c r="B13" s="458" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="461"/>
-      <c r="D13" s="461"/>
+      <c r="C13" s="458"/>
+      <c r="D13" s="458"/>
       <c r="F13" s="220" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="461" t="e">
+      <c r="G13" s="458" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="H13" s="461"/>
-      <c r="I13" s="461"/>
+      <c r="H13" s="458"/>
+      <c r="I13" s="458"/>
       <c r="K13" s="220" t="s">
         <v>132</v>
       </c>
-      <c r="L13" s="461" t="e">
+      <c r="L13" s="458" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="M13" s="461"/>
-      <c r="N13" s="461"/>
+      <c r="M13" s="458"/>
+      <c r="N13" s="458"/>
       <c r="P13" s="220" t="s">
         <v>132</v>
       </c>
-      <c r="Q13" s="458" t="e">
+      <c r="Q13" s="455" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R13" s="459"/>
-      <c r="S13" s="460"/>
+      <c r="R13" s="456"/>
+      <c r="S13" s="457"/>
     </row>
     <row r="14" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="218" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="461" t="e">
+      <c r="B14" s="458" t="e">
         <f>ABS((B13/(B11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="C14" s="461"/>
-      <c r="D14" s="461"/>
+      <c r="C14" s="458"/>
+      <c r="D14" s="458"/>
       <c r="F14" s="218" t="s">
         <v>133</v>
       </c>
-      <c r="G14" s="461" t="e">
+      <c r="G14" s="458" t="e">
         <f>ABS((G13/(G11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="H14" s="461"/>
-      <c r="I14" s="461"/>
+      <c r="H14" s="458"/>
+      <c r="I14" s="458"/>
       <c r="K14" s="218" t="s">
         <v>133</v>
       </c>
-      <c r="L14" s="461" t="e">
+      <c r="L14" s="458" t="e">
         <f>ABS((L13/(L11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="M14" s="461"/>
-      <c r="N14" s="461"/>
+      <c r="M14" s="458"/>
+      <c r="N14" s="458"/>
       <c r="P14" s="218" t="s">
         <v>133</v>
       </c>
-      <c r="Q14" s="458" t="e">
+      <c r="Q14" s="455" t="e">
         <f>ABS((Q13/(Q11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="R14" s="459"/>
-      <c r="S14" s="460"/>
+      <c r="R14" s="456"/>
+      <c r="S14" s="457"/>
     </row>
     <row r="15" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="218" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="461" t="e">
+      <c r="B15" s="458" t="e">
         <f>ABS((((B10*B11-(B9^2))/(B11*(#REF!-1)))-(B14))*((B11*(#REF!-1))/((B11^2)-B12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="C15" s="461"/>
-      <c r="D15" s="461"/>
+      <c r="C15" s="458"/>
+      <c r="D15" s="458"/>
       <c r="F15" s="218" t="s">
         <v>134</v>
       </c>
-      <c r="G15" s="461" t="e">
+      <c r="G15" s="458" t="e">
         <f>ABS((((G10*G11-(G9^2))/(G11*(#REF!-1)))-(G14))*((G11*(#REF!-1))/((G11^2)-G12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="461"/>
-      <c r="I15" s="461"/>
+      <c r="H15" s="458"/>
+      <c r="I15" s="458"/>
       <c r="K15" s="218" t="s">
         <v>134</v>
       </c>
-      <c r="L15" s="461" t="e">
+      <c r="L15" s="458" t="e">
         <f>ABS((((L10*L11-(L9^2))/(L11*(#REF!-1)))-(L14))*((L11*(#REF!-1))/((L11^2)-L12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="M15" s="461"/>
-      <c r="N15" s="461"/>
+      <c r="M15" s="458"/>
+      <c r="N15" s="458"/>
       <c r="P15" s="218" t="s">
         <v>134</v>
       </c>
-      <c r="Q15" s="461" t="e">
+      <c r="Q15" s="458" t="e">
         <f>ABS((((Q10*Q11-(Q9^2))/(Q11*(#REF!-1)))-(Q14))*((Q11*(#REF!-1))/((Q11^2)-Q12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="R15" s="461"/>
-      <c r="S15" s="461"/>
+      <c r="R15" s="458"/>
+      <c r="S15" s="458"/>
     </row>
     <row r="16" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="218" t="s">
         <v>135</v>
       </c>
-      <c r="B16" s="461" t="e">
+      <c r="B16" s="458" t="e">
         <f>(B14+B15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="C16" s="461"/>
-      <c r="D16" s="461"/>
+      <c r="C16" s="458"/>
+      <c r="D16" s="458"/>
       <c r="F16" s="218" t="s">
         <v>135</v>
       </c>
-      <c r="G16" s="461" t="e">
+      <c r="G16" s="458" t="e">
         <f>(G14+G15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="H16" s="461"/>
-      <c r="I16" s="461"/>
+      <c r="H16" s="458"/>
+      <c r="I16" s="458"/>
       <c r="K16" s="218" t="s">
         <v>135</v>
       </c>
-      <c r="L16" s="461" t="e">
+      <c r="L16" s="458" t="e">
         <f>(L14+L15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="M16" s="461"/>
-      <c r="N16" s="461"/>
+      <c r="M16" s="458"/>
+      <c r="N16" s="458"/>
       <c r="P16" s="218" t="s">
         <v>135</v>
       </c>
-      <c r="Q16" s="458" t="e">
+      <c r="Q16" s="455" t="e">
         <f>(Q14+Q15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="R16" s="459"/>
-      <c r="S16" s="460"/>
+      <c r="R16" s="456"/>
+      <c r="S16" s="457"/>
     </row>
     <row r="17" spans="1:25" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="218" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="461" t="e">
+      <c r="B17" s="458" t="e">
         <f>SQRT(B14)</f>
         <v>#REF!</v>
       </c>
-      <c r="C17" s="461"/>
-      <c r="D17" s="461"/>
+      <c r="C17" s="458"/>
+      <c r="D17" s="458"/>
       <c r="F17" s="218" t="s">
         <v>136</v>
       </c>
-      <c r="G17" s="461" t="e">
+      <c r="G17" s="458" t="e">
         <f>SQRT(G14)</f>
         <v>#REF!</v>
       </c>
-      <c r="H17" s="461"/>
-      <c r="I17" s="461"/>
+      <c r="H17" s="458"/>
+      <c r="I17" s="458"/>
       <c r="K17" s="218" t="s">
         <v>136</v>
       </c>
-      <c r="L17" s="461" t="e">
+      <c r="L17" s="458" t="e">
         <f>SQRT(L14)</f>
         <v>#REF!</v>
       </c>
-      <c r="M17" s="461"/>
-      <c r="N17" s="461"/>
+      <c r="M17" s="458"/>
+      <c r="N17" s="458"/>
       <c r="P17" s="218" t="s">
         <v>136</v>
       </c>
-      <c r="Q17" s="458" t="e">
+      <c r="Q17" s="455" t="e">
         <f>SQRT(Q14)</f>
         <v>#REF!</v>
       </c>
-      <c r="R17" s="459"/>
-      <c r="S17" s="460"/>
-      <c r="V17" s="464"/>
-      <c r="W17" s="464"/>
-      <c r="X17" s="464"/>
-      <c r="Y17" s="464"/>
+      <c r="R17" s="456"/>
+      <c r="S17" s="457"/>
+      <c r="V17" s="461"/>
+      <c r="W17" s="461"/>
+      <c r="X17" s="461"/>
+      <c r="Y17" s="461"/>
     </row>
     <row r="18" spans="1:25" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="218" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="461" t="e">
+      <c r="B18" s="458" t="e">
         <f>+SQRT(B14+B15)</f>
         <v>#REF!</v>
       </c>
-      <c r="C18" s="461"/>
-      <c r="D18" s="461"/>
+      <c r="C18" s="458"/>
+      <c r="D18" s="458"/>
       <c r="F18" s="218" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="461" t="e">
+      <c r="G18" s="458" t="e">
         <f>+SQRT(G14+G15)</f>
         <v>#REF!</v>
       </c>
-      <c r="H18" s="461"/>
-      <c r="I18" s="461"/>
+      <c r="H18" s="458"/>
+      <c r="I18" s="458"/>
       <c r="K18" s="218" t="s">
         <v>137</v>
       </c>
-      <c r="L18" s="461" t="e">
+      <c r="L18" s="458" t="e">
         <f>+SQRT(L14+L15)</f>
         <v>#REF!</v>
       </c>
-      <c r="M18" s="461"/>
-      <c r="N18" s="461"/>
+      <c r="M18" s="458"/>
+      <c r="N18" s="458"/>
       <c r="P18" s="218" t="s">
         <v>137</v>
       </c>
-      <c r="Q18" s="458" t="e">
+      <c r="Q18" s="455" t="e">
         <f>+SQRT(Q14+Q15)</f>
         <v>#REF!</v>
       </c>
-      <c r="R18" s="459"/>
-      <c r="S18" s="460"/>
-      <c r="V18" s="464"/>
-      <c r="W18" s="464"/>
-      <c r="X18" s="464"/>
-      <c r="Y18" s="464"/>
-    </row>
-    <row r="19" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="380" t="s">
+      <c r="R18" s="456"/>
+      <c r="S18" s="457"/>
+      <c r="V18" s="461"/>
+      <c r="W18" s="461"/>
+      <c r="X18" s="461"/>
+      <c r="Y18" s="461"/>
+    </row>
+    <row r="19" spans="1:25" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="377" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="451">
+        <v>7.6899555698759737E-3</v>
+      </c>
+      <c r="C19" s="451"/>
+      <c r="D19" s="451"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="377" t="s">
+        <v>220</v>
+      </c>
+      <c r="G19" s="451">
+        <v>6.454972243679062E-3</v>
+      </c>
+      <c r="H19" s="451"/>
+      <c r="I19" s="451"/>
+      <c r="J19" s="378"/>
+      <c r="K19" s="377" t="s">
+        <v>220</v>
+      </c>
+      <c r="L19" s="451">
+        <v>6.4718943646096755E-3</v>
+      </c>
+      <c r="M19" s="451"/>
+      <c r="N19" s="451"/>
+      <c r="O19" s="378"/>
+      <c r="P19" s="377" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q19" s="451">
+        <v>9.1503642914731384E-2</v>
+      </c>
+      <c r="R19" s="451"/>
+      <c r="S19" s="451"/>
+      <c r="V19" s="461"/>
+      <c r="W19" s="461"/>
+      <c r="X19" s="461"/>
+      <c r="Y19" s="461"/>
+    </row>
+    <row r="20" spans="1:25" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="377" t="s">
         <v>221</v>
       </c>
-      <c r="B19" s="454">
-        <v>7.6899555698759737E-3</v>
-      </c>
-      <c r="C19" s="454"/>
-      <c r="D19" s="454"/>
-      <c r="E19" s="381"/>
-      <c r="F19" s="380" t="s">
+      <c r="B20" s="451">
+        <v>7.734845547824153E-3</v>
+      </c>
+      <c r="C20" s="451"/>
+      <c r="D20" s="451"/>
+      <c r="E20" s="378"/>
+      <c r="F20" s="377" t="s">
         <v>221</v>
       </c>
-      <c r="G19" s="454">
-        <v>6.454972243679062E-3</v>
-      </c>
-      <c r="H19" s="454"/>
-      <c r="I19" s="454"/>
-      <c r="J19" s="381"/>
-      <c r="K19" s="380" t="s">
+      <c r="G20" s="451">
+        <v>6.6157779978408861E-3</v>
+      </c>
+      <c r="H20" s="451"/>
+      <c r="I20" s="451"/>
+      <c r="J20" s="378"/>
+      <c r="K20" s="377" t="s">
         <v>221</v>
       </c>
-      <c r="L19" s="454">
-        <v>6.4718943646096755E-3</v>
-      </c>
-      <c r="M19" s="454"/>
-      <c r="N19" s="454"/>
-      <c r="O19" s="381"/>
-      <c r="P19" s="380" t="s">
+      <c r="L20" s="451">
+        <v>6.5331464330420554E-3</v>
+      </c>
+      <c r="M20" s="451"/>
+      <c r="N20" s="451"/>
+      <c r="O20" s="378"/>
+      <c r="P20" s="377" t="s">
         <v>221</v>
       </c>
-      <c r="Q19" s="454">
-        <v>9.1503642914731384E-2</v>
-      </c>
-      <c r="R19" s="454"/>
-      <c r="S19" s="454"/>
-      <c r="V19" s="464"/>
-      <c r="W19" s="464"/>
-      <c r="X19" s="464"/>
-      <c r="Y19" s="464"/>
-    </row>
-    <row r="20" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="380" t="s">
-        <v>222</v>
-      </c>
-      <c r="B20" s="454">
-        <v>7.734845547824153E-3</v>
-      </c>
-      <c r="C20" s="454"/>
-      <c r="D20" s="454"/>
-      <c r="E20" s="381"/>
-      <c r="F20" s="380" t="s">
-        <v>222</v>
-      </c>
-      <c r="G20" s="454">
-        <v>6.6157779978408861E-3</v>
-      </c>
-      <c r="H20" s="454"/>
-      <c r="I20" s="454"/>
-      <c r="J20" s="381"/>
-      <c r="K20" s="380" t="s">
-        <v>222</v>
-      </c>
-      <c r="L20" s="454">
-        <v>6.5331464330420554E-3</v>
-      </c>
-      <c r="M20" s="454"/>
-      <c r="N20" s="454"/>
-      <c r="O20" s="381"/>
-      <c r="P20" s="380" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q20" s="454">
+      <c r="Q20" s="451">
         <v>0.1067108740857599</v>
       </c>
-      <c r="R20" s="454"/>
-      <c r="S20" s="454"/>
-      <c r="V20" s="464"/>
-      <c r="W20" s="464"/>
-      <c r="X20" s="464"/>
-      <c r="Y20" s="464"/>
+      <c r="R20" s="451"/>
+      <c r="S20" s="451"/>
+      <c r="V20" s="461"/>
+      <c r="W20" s="461"/>
+      <c r="X20" s="461"/>
+      <c r="Y20" s="461"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V21" s="464"/>
-      <c r="W21" s="464"/>
-      <c r="X21" s="464"/>
-      <c r="Y21" s="464"/>
+      <c r="V21" s="461"/>
+      <c r="W21" s="461"/>
+      <c r="X21" s="461"/>
+      <c r="Y21" s="461"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V22" s="464"/>
-      <c r="W22" s="464"/>
-      <c r="X22" s="464"/>
-      <c r="Y22" s="464"/>
+      <c r="V22" s="461"/>
+      <c r="W22" s="461"/>
+      <c r="X22" s="461"/>
+      <c r="Y22" s="461"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V23" s="464"/>
-      <c r="W23" s="464"/>
-      <c r="X23" s="464"/>
-      <c r="Y23" s="464"/>
+      <c r="V23" s="461"/>
+      <c r="W23" s="461"/>
+      <c r="X23" s="461"/>
+      <c r="Y23" s="461"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V24" s="464"/>
-      <c r="W24" s="464"/>
-      <c r="X24" s="464"/>
-      <c r="Y24" s="464"/>
+      <c r="V24" s="461"/>
+      <c r="W24" s="461"/>
+      <c r="X24" s="461"/>
+      <c r="Y24" s="461"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V25" s="464"/>
-      <c r="W25" s="464"/>
-      <c r="X25" s="464"/>
-      <c r="Y25" s="464"/>
+      <c r="V25" s="461"/>
+      <c r="W25" s="461"/>
+      <c r="X25" s="461"/>
+      <c r="Y25" s="461"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V26" s="464"/>
-      <c r="W26" s="464"/>
-      <c r="X26" s="464"/>
-      <c r="Y26" s="464"/>
+      <c r="V26" s="461"/>
+      <c r="W26" s="461"/>
+      <c r="X26" s="461"/>
+      <c r="Y26" s="461"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V27" s="464"/>
-      <c r="W27" s="464"/>
-      <c r="X27" s="464"/>
-      <c r="Y27" s="464"/>
+      <c r="V27" s="461"/>
+      <c r="W27" s="461"/>
+      <c r="X27" s="461"/>
+      <c r="Y27" s="461"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V28" s="464"/>
-      <c r="W28" s="464"/>
-      <c r="X28" s="464"/>
-      <c r="Y28" s="464"/>
+      <c r="V28" s="461"/>
+      <c r="W28" s="461"/>
+      <c r="X28" s="461"/>
+      <c r="Y28" s="461"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V29" s="464"/>
-      <c r="W29" s="464"/>
-      <c r="X29" s="464"/>
-      <c r="Y29" s="464"/>
+      <c r="V29" s="461"/>
+      <c r="W29" s="461"/>
+      <c r="X29" s="461"/>
+      <c r="Y29" s="461"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V30" s="464"/>
-      <c r="W30" s="464"/>
-      <c r="X30" s="464"/>
-      <c r="Y30" s="464"/>
+      <c r="V30" s="461"/>
+      <c r="W30" s="461"/>
+      <c r="X30" s="461"/>
+      <c r="Y30" s="461"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V31" s="464"/>
-      <c r="W31" s="464"/>
-      <c r="X31" s="464"/>
-      <c r="Y31" s="464"/>
+      <c r="V31" s="461"/>
+      <c r="W31" s="461"/>
+      <c r="X31" s="461"/>
+      <c r="Y31" s="461"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V32" s="464"/>
-      <c r="W32" s="464"/>
-      <c r="X32" s="464"/>
-      <c r="Y32" s="464"/>
+      <c r="V32" s="461"/>
+      <c r="W32" s="461"/>
+      <c r="X32" s="461"/>
+      <c r="Y32" s="461"/>
     </row>
     <row r="33" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V33" s="464"/>
-      <c r="W33" s="464"/>
-      <c r="X33" s="464"/>
-      <c r="Y33" s="464"/>
+      <c r="V33" s="461"/>
+      <c r="W33" s="461"/>
+      <c r="X33" s="461"/>
+      <c r="Y33" s="461"/>
     </row>
     <row r="34" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V34" s="464"/>
-      <c r="W34" s="464"/>
-      <c r="X34" s="464"/>
-      <c r="Y34" s="464"/>
+      <c r="V34" s="461"/>
+      <c r="W34" s="461"/>
+      <c r="X34" s="461"/>
+      <c r="Y34" s="461"/>
     </row>
     <row r="35" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V35" s="464"/>
-      <c r="W35" s="464"/>
-      <c r="X35" s="464"/>
-      <c r="Y35" s="464"/>
+      <c r="V35" s="461"/>
+      <c r="W35" s="461"/>
+      <c r="X35" s="461"/>
+      <c r="Y35" s="461"/>
     </row>
     <row r="36" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V36" s="464"/>
-      <c r="W36" s="464"/>
-      <c r="X36" s="464"/>
-      <c r="Y36" s="464"/>
+      <c r="V36" s="461"/>
+      <c r="W36" s="461"/>
+      <c r="X36" s="461"/>
+      <c r="Y36" s="461"/>
     </row>
     <row r="37" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V37" s="464"/>
-      <c r="W37" s="464"/>
-      <c r="X37" s="464"/>
-      <c r="Y37" s="464"/>
+      <c r="V37" s="461"/>
+      <c r="W37" s="461"/>
+      <c r="X37" s="461"/>
+      <c r="Y37" s="461"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F7BNTbSy/WaNWXDdT6W94NKCeKyHLn/2tkk/4quJIvd3p+J7bDJlNkQREHsu55RDSjMZ5YiRTRqr/fG8D9Qggw==" saltValue="uAZ5OYTao9E+LNIA/ZL2vQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -15312,22 +15311,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A2:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="1" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="465" t="s">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="462" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="465"/>
+      <c r="B2" s="462"/>
       <c r="C2" s="5" t="s">
         <v>139</v>
       </c>
@@ -15362,7 +15361,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>4400</v>
       </c>
@@ -15408,7 +15407,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="6" t="str">
@@ -15445,7 +15444,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f>+B3+1</f>
         <v>4402</v>
@@ -15488,7 +15487,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="6" t="str">
@@ -15525,7 +15524,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f>+B5+1</f>
         <v>4404</v>
@@ -15568,7 +15567,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="6" t="str">
@@ -15605,7 +15604,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
